--- a/projects/02-pnl-dashboard/templates/bloomberg_prices.xlsx
+++ b/projects/02-pnl-dashboard/templates/bloomberg_prices.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Live MTM" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Static" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="History" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,10 +33,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00555555"/>
     </font>
   </fonts>
   <fills count="3">
@@ -65,13 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +435,7 @@
   <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -449,7 +444,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CUSIP</t>
+          <t>BBG Ticker</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -470,701 +465,701 @@
     </row>
     <row r="2">
       <c r="B2">
-        <f>BDP(A2&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A2,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C2">
-        <f>BDP(A2&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A2,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D2">
-        <f>BDP(A2&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A2,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="B3">
-        <f>BDP(A3&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A3,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C3">
-        <f>BDP(A3&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A3,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D3">
-        <f>BDP(A3&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A3,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="B4">
-        <f>BDP(A4&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A4,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C4">
-        <f>BDP(A4&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A4,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D4">
-        <f>BDP(A4&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A4,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="B5">
-        <f>BDP(A5&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A5,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C5">
-        <f>BDP(A5&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A5,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D5">
-        <f>BDP(A5&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A5,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="B6">
-        <f>BDP(A6&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A6,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C6">
-        <f>BDP(A6&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A6,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D6">
-        <f>BDP(A6&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A6,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="B7">
-        <f>BDP(A7&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A7,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C7">
-        <f>BDP(A7&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A7,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D7">
-        <f>BDP(A7&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A7,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="B8">
-        <f>BDP(A8&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A8,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C8">
-        <f>BDP(A8&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A8,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D8">
-        <f>BDP(A8&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A8,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="B9">
-        <f>BDP(A9&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A9,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C9">
-        <f>BDP(A9&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A9,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D9">
-        <f>BDP(A9&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A9,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="B10">
-        <f>BDP(A10&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A10,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C10">
-        <f>BDP(A10&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A10,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D10">
-        <f>BDP(A10&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A10,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="B11">
-        <f>BDP(A11&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A11,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C11">
-        <f>BDP(A11&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A11,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D11">
-        <f>BDP(A11&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A11,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="B12">
-        <f>BDP(A12&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A12,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C12">
-        <f>BDP(A12&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A12,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D12">
-        <f>BDP(A12&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A12,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="B13">
-        <f>BDP(A13&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A13,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C13">
-        <f>BDP(A13&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A13,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D13">
-        <f>BDP(A13&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A13,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="B14">
-        <f>BDP(A14&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A14,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C14">
-        <f>BDP(A14&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A14,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D14">
-        <f>BDP(A14&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A14,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="B15">
-        <f>BDP(A15&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A15,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C15">
-        <f>BDP(A15&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A15,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D15">
-        <f>BDP(A15&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A15,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="B16">
-        <f>BDP(A16&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A16,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C16">
-        <f>BDP(A16&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A16,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D16">
-        <f>BDP(A16&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A16,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="B17">
-        <f>BDP(A17&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A17,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C17">
-        <f>BDP(A17&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A17,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D17">
-        <f>BDP(A17&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A17,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="B18">
-        <f>BDP(A18&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A18,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C18">
-        <f>BDP(A18&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A18,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D18">
-        <f>BDP(A18&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A18,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="B19">
-        <f>BDP(A19&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A19,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C19">
-        <f>BDP(A19&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A19,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D19">
-        <f>BDP(A19&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A19,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="B20">
-        <f>BDP(A20&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A20,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C20">
-        <f>BDP(A20&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A20,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D20">
-        <f>BDP(A20&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A20,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="B21">
-        <f>BDP(A21&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A21,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C21">
-        <f>BDP(A21&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A21,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D21">
-        <f>BDP(A21&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A21,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="B22">
-        <f>BDP(A22&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A22,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C22">
-        <f>BDP(A22&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A22,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D22">
-        <f>BDP(A22&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A22,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23">
-        <f>BDP(A23&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A23,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C23">
-        <f>BDP(A23&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A23,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D23">
-        <f>BDP(A23&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A23,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24">
-        <f>BDP(A24&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A24,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C24">
-        <f>BDP(A24&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A24,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D24">
-        <f>BDP(A24&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A24,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="B25">
-        <f>BDP(A25&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A25,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C25">
-        <f>BDP(A25&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A25,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D25">
-        <f>BDP(A25&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A25,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="B26">
-        <f>BDP(A26&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A26,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C26">
-        <f>BDP(A26&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A26,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D26">
-        <f>BDP(A26&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A26,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="B27">
-        <f>BDP(A27&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A27,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C27">
-        <f>BDP(A27&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A27,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D27">
-        <f>BDP(A27&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A27,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="B28">
-        <f>BDP(A28&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A28,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C28">
-        <f>BDP(A28&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A28,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D28">
-        <f>BDP(A28&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A28,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="B29">
-        <f>BDP(A29&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A29,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C29">
-        <f>BDP(A29&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A29,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D29">
-        <f>BDP(A29&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A29,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="B30">
-        <f>BDP(A30&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A30,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C30">
-        <f>BDP(A30&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A30,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D30">
-        <f>BDP(A30&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A30,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="B31">
-        <f>BDP(A31&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A31,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C31">
-        <f>BDP(A31&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A31,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D31">
-        <f>BDP(A31&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A31,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="B32">
-        <f>BDP(A32&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A32,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C32">
-        <f>BDP(A32&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A32,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D32">
-        <f>BDP(A32&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A32,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="B33">
-        <f>BDP(A33&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A33,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C33">
-        <f>BDP(A33&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A33,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D33">
-        <f>BDP(A33&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A33,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="B34">
-        <f>BDP(A34&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A34,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C34">
-        <f>BDP(A34&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A34,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D34">
-        <f>BDP(A34&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A34,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="B35">
-        <f>BDP(A35&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A35,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C35">
-        <f>BDP(A35&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A35,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D35">
-        <f>BDP(A35&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A35,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="B36">
-        <f>BDP(A36&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A36,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C36">
-        <f>BDP(A36&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A36,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D36">
-        <f>BDP(A36&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A36,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="B37">
-        <f>BDP(A37&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A37,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C37">
-        <f>BDP(A37&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A37,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D37">
-        <f>BDP(A37&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A37,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="B38">
-        <f>BDP(A38&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A38,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C38">
-        <f>BDP(A38&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A38,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D38">
-        <f>BDP(A38&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A38,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="B39">
-        <f>BDP(A39&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A39,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C39">
-        <f>BDP(A39&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A39,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D39">
-        <f>BDP(A39&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A39,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="B40">
-        <f>BDP(A40&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A40,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C40">
-        <f>BDP(A40&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A40,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D40">
-        <f>BDP(A40&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A40,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="B41">
-        <f>BDP(A41&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A41,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C41">
-        <f>BDP(A41&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A41,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D41">
-        <f>BDP(A41&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A41,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42">
-        <f>BDP(A42&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A42,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C42">
-        <f>BDP(A42&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A42,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D42">
-        <f>BDP(A42&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A42,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43">
-        <f>BDP(A43&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A43,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C43">
-        <f>BDP(A43&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A43,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D43">
-        <f>BDP(A43&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A43,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44">
-        <f>BDP(A44&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A44,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C44">
-        <f>BDP(A44&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A44,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D44">
-        <f>BDP(A44&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A44,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45">
-        <f>BDP(A45&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A45,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C45">
-        <f>BDP(A45&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A45,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D45">
-        <f>BDP(A45&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A45,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46">
-        <f>BDP(A46&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A46,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C46">
-        <f>BDP(A46&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A46,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D46">
-        <f>BDP(A46&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A46,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="B47">
-        <f>BDP(A47&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A47,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C47">
-        <f>BDP(A47&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A47,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D47">
-        <f>BDP(A47&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A47,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="B48">
-        <f>BDP(A48&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A48,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C48">
-        <f>BDP(A48&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A48,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D48">
-        <f>BDP(A48&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A48,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="B49">
-        <f>BDP(A49&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A49,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C49">
-        <f>BDP(A49&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A49,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D49">
-        <f>BDP(A49&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A49,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="B50">
-        <f>BDP(A50&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A50,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C50">
-        <f>BDP(A50&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A50,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D50">
-        <f>BDP(A50&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A50,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="B51">
-        <f>BDP(A51&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A51,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C51">
-        <f>BDP(A51&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A51,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D51">
-        <f>BDP(A51&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A51,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
@@ -1182,7 +1177,7 @@
   <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -1196,7 +1191,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>cusip</t>
+          <t>bbg_ticker</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1242,1701 +1237,1701 @@
     </row>
     <row r="2">
       <c r="B2">
-        <f>BDP(A2&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A2,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C2">
-        <f>BDP(A2&amp;" Corp","CRNCY")</f>
+        <f>BDP(A2,"CRNCY")</f>
         <v/>
       </c>
       <c r="D2">
-        <f>BDP(A2&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A2,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E2">
-        <f>BDP(A2&amp;" Corp","CPN")/100</f>
+        <f>BDP(A2,"CPN")/100</f>
         <v/>
       </c>
       <c r="F2">
-        <f>BDP(A2&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A2,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G2">
-        <f>BDP(A2&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A2,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H2">
-        <f>BDP(A2&amp;" Corp","MATURITY")</f>
+        <f>BDP(A2,"MATURITY")</f>
         <v/>
       </c>
       <c r="I2">
-        <f>BDP(A2&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A2,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="B3">
-        <f>BDP(A3&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A3,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C3">
-        <f>BDP(A3&amp;" Corp","CRNCY")</f>
+        <f>BDP(A3,"CRNCY")</f>
         <v/>
       </c>
       <c r="D3">
-        <f>BDP(A3&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A3,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E3">
-        <f>BDP(A3&amp;" Corp","CPN")/100</f>
+        <f>BDP(A3,"CPN")/100</f>
         <v/>
       </c>
       <c r="F3">
-        <f>BDP(A3&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A3,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G3">
-        <f>BDP(A3&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A3,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H3">
-        <f>BDP(A3&amp;" Corp","MATURITY")</f>
+        <f>BDP(A3,"MATURITY")</f>
         <v/>
       </c>
       <c r="I3">
-        <f>BDP(A3&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A3,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="B4">
-        <f>BDP(A4&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A4,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C4">
-        <f>BDP(A4&amp;" Corp","CRNCY")</f>
+        <f>BDP(A4,"CRNCY")</f>
         <v/>
       </c>
       <c r="D4">
-        <f>BDP(A4&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A4,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E4">
-        <f>BDP(A4&amp;" Corp","CPN")/100</f>
+        <f>BDP(A4,"CPN")/100</f>
         <v/>
       </c>
       <c r="F4">
-        <f>BDP(A4&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A4,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G4">
-        <f>BDP(A4&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A4,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H4">
-        <f>BDP(A4&amp;" Corp","MATURITY")</f>
+        <f>BDP(A4,"MATURITY")</f>
         <v/>
       </c>
       <c r="I4">
-        <f>BDP(A4&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A4,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="B5">
-        <f>BDP(A5&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A5,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C5">
-        <f>BDP(A5&amp;" Corp","CRNCY")</f>
+        <f>BDP(A5,"CRNCY")</f>
         <v/>
       </c>
       <c r="D5">
-        <f>BDP(A5&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A5,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E5">
-        <f>BDP(A5&amp;" Corp","CPN")/100</f>
+        <f>BDP(A5,"CPN")/100</f>
         <v/>
       </c>
       <c r="F5">
-        <f>BDP(A5&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A5,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G5">
-        <f>BDP(A5&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A5,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H5">
-        <f>BDP(A5&amp;" Corp","MATURITY")</f>
+        <f>BDP(A5,"MATURITY")</f>
         <v/>
       </c>
       <c r="I5">
-        <f>BDP(A5&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A5,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="B6">
-        <f>BDP(A6&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A6,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C6">
-        <f>BDP(A6&amp;" Corp","CRNCY")</f>
+        <f>BDP(A6,"CRNCY")</f>
         <v/>
       </c>
       <c r="D6">
-        <f>BDP(A6&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A6,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E6">
-        <f>BDP(A6&amp;" Corp","CPN")/100</f>
+        <f>BDP(A6,"CPN")/100</f>
         <v/>
       </c>
       <c r="F6">
-        <f>BDP(A6&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A6,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G6">
-        <f>BDP(A6&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A6,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H6">
-        <f>BDP(A6&amp;" Corp","MATURITY")</f>
+        <f>BDP(A6,"MATURITY")</f>
         <v/>
       </c>
       <c r="I6">
-        <f>BDP(A6&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A6,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="B7">
-        <f>BDP(A7&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A7,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C7">
-        <f>BDP(A7&amp;" Corp","CRNCY")</f>
+        <f>BDP(A7,"CRNCY")</f>
         <v/>
       </c>
       <c r="D7">
-        <f>BDP(A7&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A7,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E7">
-        <f>BDP(A7&amp;" Corp","CPN")/100</f>
+        <f>BDP(A7,"CPN")/100</f>
         <v/>
       </c>
       <c r="F7">
-        <f>BDP(A7&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A7,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G7">
-        <f>BDP(A7&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A7,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H7">
-        <f>BDP(A7&amp;" Corp","MATURITY")</f>
+        <f>BDP(A7,"MATURITY")</f>
         <v/>
       </c>
       <c r="I7">
-        <f>BDP(A7&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A7,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="B8">
-        <f>BDP(A8&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A8,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C8">
-        <f>BDP(A8&amp;" Corp","CRNCY")</f>
+        <f>BDP(A8,"CRNCY")</f>
         <v/>
       </c>
       <c r="D8">
-        <f>BDP(A8&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A8,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E8">
-        <f>BDP(A8&amp;" Corp","CPN")/100</f>
+        <f>BDP(A8,"CPN")/100</f>
         <v/>
       </c>
       <c r="F8">
-        <f>BDP(A8&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A8,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G8">
-        <f>BDP(A8&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A8,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H8">
-        <f>BDP(A8&amp;" Corp","MATURITY")</f>
+        <f>BDP(A8,"MATURITY")</f>
         <v/>
       </c>
       <c r="I8">
-        <f>BDP(A8&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A8,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="B9">
-        <f>BDP(A9&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A9,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C9">
-        <f>BDP(A9&amp;" Corp","CRNCY")</f>
+        <f>BDP(A9,"CRNCY")</f>
         <v/>
       </c>
       <c r="D9">
-        <f>BDP(A9&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A9,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E9">
-        <f>BDP(A9&amp;" Corp","CPN")/100</f>
+        <f>BDP(A9,"CPN")/100</f>
         <v/>
       </c>
       <c r="F9">
-        <f>BDP(A9&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A9,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G9">
-        <f>BDP(A9&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A9,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H9">
-        <f>BDP(A9&amp;" Corp","MATURITY")</f>
+        <f>BDP(A9,"MATURITY")</f>
         <v/>
       </c>
       <c r="I9">
-        <f>BDP(A9&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A9,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="B10">
-        <f>BDP(A10&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A10,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C10">
-        <f>BDP(A10&amp;" Corp","CRNCY")</f>
+        <f>BDP(A10,"CRNCY")</f>
         <v/>
       </c>
       <c r="D10">
-        <f>BDP(A10&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A10,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E10">
-        <f>BDP(A10&amp;" Corp","CPN")/100</f>
+        <f>BDP(A10,"CPN")/100</f>
         <v/>
       </c>
       <c r="F10">
-        <f>BDP(A10&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A10,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G10">
-        <f>BDP(A10&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A10,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H10">
-        <f>BDP(A10&amp;" Corp","MATURITY")</f>
+        <f>BDP(A10,"MATURITY")</f>
         <v/>
       </c>
       <c r="I10">
-        <f>BDP(A10&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A10,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="B11">
-        <f>BDP(A11&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A11,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C11">
-        <f>BDP(A11&amp;" Corp","CRNCY")</f>
+        <f>BDP(A11,"CRNCY")</f>
         <v/>
       </c>
       <c r="D11">
-        <f>BDP(A11&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A11,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E11">
-        <f>BDP(A11&amp;" Corp","CPN")/100</f>
+        <f>BDP(A11,"CPN")/100</f>
         <v/>
       </c>
       <c r="F11">
-        <f>BDP(A11&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A11,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G11">
-        <f>BDP(A11&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A11,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H11">
-        <f>BDP(A11&amp;" Corp","MATURITY")</f>
+        <f>BDP(A11,"MATURITY")</f>
         <v/>
       </c>
       <c r="I11">
-        <f>BDP(A11&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A11,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="B12">
-        <f>BDP(A12&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A12,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C12">
-        <f>BDP(A12&amp;" Corp","CRNCY")</f>
+        <f>BDP(A12,"CRNCY")</f>
         <v/>
       </c>
       <c r="D12">
-        <f>BDP(A12&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A12,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E12">
-        <f>BDP(A12&amp;" Corp","CPN")/100</f>
+        <f>BDP(A12,"CPN")/100</f>
         <v/>
       </c>
       <c r="F12">
-        <f>BDP(A12&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A12,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G12">
-        <f>BDP(A12&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A12,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H12">
-        <f>BDP(A12&amp;" Corp","MATURITY")</f>
+        <f>BDP(A12,"MATURITY")</f>
         <v/>
       </c>
       <c r="I12">
-        <f>BDP(A12&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A12,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="B13">
-        <f>BDP(A13&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A13,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C13">
-        <f>BDP(A13&amp;" Corp","CRNCY")</f>
+        <f>BDP(A13,"CRNCY")</f>
         <v/>
       </c>
       <c r="D13">
-        <f>BDP(A13&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A13,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E13">
-        <f>BDP(A13&amp;" Corp","CPN")/100</f>
+        <f>BDP(A13,"CPN")/100</f>
         <v/>
       </c>
       <c r="F13">
-        <f>BDP(A13&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A13,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G13">
-        <f>BDP(A13&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A13,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H13">
-        <f>BDP(A13&amp;" Corp","MATURITY")</f>
+        <f>BDP(A13,"MATURITY")</f>
         <v/>
       </c>
       <c r="I13">
-        <f>BDP(A13&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A13,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="B14">
-        <f>BDP(A14&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A14,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C14">
-        <f>BDP(A14&amp;" Corp","CRNCY")</f>
+        <f>BDP(A14,"CRNCY")</f>
         <v/>
       </c>
       <c r="D14">
-        <f>BDP(A14&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A14,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E14">
-        <f>BDP(A14&amp;" Corp","CPN")/100</f>
+        <f>BDP(A14,"CPN")/100</f>
         <v/>
       </c>
       <c r="F14">
-        <f>BDP(A14&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A14,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G14">
-        <f>BDP(A14&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A14,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H14">
-        <f>BDP(A14&amp;" Corp","MATURITY")</f>
+        <f>BDP(A14,"MATURITY")</f>
         <v/>
       </c>
       <c r="I14">
-        <f>BDP(A14&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A14,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="B15">
-        <f>BDP(A15&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A15,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C15">
-        <f>BDP(A15&amp;" Corp","CRNCY")</f>
+        <f>BDP(A15,"CRNCY")</f>
         <v/>
       </c>
       <c r="D15">
-        <f>BDP(A15&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A15,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E15">
-        <f>BDP(A15&amp;" Corp","CPN")/100</f>
+        <f>BDP(A15,"CPN")/100</f>
         <v/>
       </c>
       <c r="F15">
-        <f>BDP(A15&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A15,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G15">
-        <f>BDP(A15&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A15,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H15">
-        <f>BDP(A15&amp;" Corp","MATURITY")</f>
+        <f>BDP(A15,"MATURITY")</f>
         <v/>
       </c>
       <c r="I15">
-        <f>BDP(A15&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A15,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="B16">
-        <f>BDP(A16&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A16,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C16">
-        <f>BDP(A16&amp;" Corp","CRNCY")</f>
+        <f>BDP(A16,"CRNCY")</f>
         <v/>
       </c>
       <c r="D16">
-        <f>BDP(A16&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A16,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E16">
-        <f>BDP(A16&amp;" Corp","CPN")/100</f>
+        <f>BDP(A16,"CPN")/100</f>
         <v/>
       </c>
       <c r="F16">
-        <f>BDP(A16&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A16,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G16">
-        <f>BDP(A16&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A16,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H16">
-        <f>BDP(A16&amp;" Corp","MATURITY")</f>
+        <f>BDP(A16,"MATURITY")</f>
         <v/>
       </c>
       <c r="I16">
-        <f>BDP(A16&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A16,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="B17">
-        <f>BDP(A17&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A17,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C17">
-        <f>BDP(A17&amp;" Corp","CRNCY")</f>
+        <f>BDP(A17,"CRNCY")</f>
         <v/>
       </c>
       <c r="D17">
-        <f>BDP(A17&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A17,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E17">
-        <f>BDP(A17&amp;" Corp","CPN")/100</f>
+        <f>BDP(A17,"CPN")/100</f>
         <v/>
       </c>
       <c r="F17">
-        <f>BDP(A17&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A17,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G17">
-        <f>BDP(A17&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A17,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H17">
-        <f>BDP(A17&amp;" Corp","MATURITY")</f>
+        <f>BDP(A17,"MATURITY")</f>
         <v/>
       </c>
       <c r="I17">
-        <f>BDP(A17&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A17,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="B18">
-        <f>BDP(A18&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A18,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C18">
-        <f>BDP(A18&amp;" Corp","CRNCY")</f>
+        <f>BDP(A18,"CRNCY")</f>
         <v/>
       </c>
       <c r="D18">
-        <f>BDP(A18&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A18,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E18">
-        <f>BDP(A18&amp;" Corp","CPN")/100</f>
+        <f>BDP(A18,"CPN")/100</f>
         <v/>
       </c>
       <c r="F18">
-        <f>BDP(A18&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A18,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G18">
-        <f>BDP(A18&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A18,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H18">
-        <f>BDP(A18&amp;" Corp","MATURITY")</f>
+        <f>BDP(A18,"MATURITY")</f>
         <v/>
       </c>
       <c r="I18">
-        <f>BDP(A18&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A18,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="B19">
-        <f>BDP(A19&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A19,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C19">
-        <f>BDP(A19&amp;" Corp","CRNCY")</f>
+        <f>BDP(A19,"CRNCY")</f>
         <v/>
       </c>
       <c r="D19">
-        <f>BDP(A19&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A19,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E19">
-        <f>BDP(A19&amp;" Corp","CPN")/100</f>
+        <f>BDP(A19,"CPN")/100</f>
         <v/>
       </c>
       <c r="F19">
-        <f>BDP(A19&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A19,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G19">
-        <f>BDP(A19&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A19,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H19">
-        <f>BDP(A19&amp;" Corp","MATURITY")</f>
+        <f>BDP(A19,"MATURITY")</f>
         <v/>
       </c>
       <c r="I19">
-        <f>BDP(A19&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A19,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="B20">
-        <f>BDP(A20&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A20,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C20">
-        <f>BDP(A20&amp;" Corp","CRNCY")</f>
+        <f>BDP(A20,"CRNCY")</f>
         <v/>
       </c>
       <c r="D20">
-        <f>BDP(A20&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A20,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E20">
-        <f>BDP(A20&amp;" Corp","CPN")/100</f>
+        <f>BDP(A20,"CPN")/100</f>
         <v/>
       </c>
       <c r="F20">
-        <f>BDP(A20&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A20,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G20">
-        <f>BDP(A20&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A20,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H20">
-        <f>BDP(A20&amp;" Corp","MATURITY")</f>
+        <f>BDP(A20,"MATURITY")</f>
         <v/>
       </c>
       <c r="I20">
-        <f>BDP(A20&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A20,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="B21">
-        <f>BDP(A21&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A21,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C21">
-        <f>BDP(A21&amp;" Corp","CRNCY")</f>
+        <f>BDP(A21,"CRNCY")</f>
         <v/>
       </c>
       <c r="D21">
-        <f>BDP(A21&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A21,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E21">
-        <f>BDP(A21&amp;" Corp","CPN")/100</f>
+        <f>BDP(A21,"CPN")/100</f>
         <v/>
       </c>
       <c r="F21">
-        <f>BDP(A21&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A21,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G21">
-        <f>BDP(A21&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A21,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H21">
-        <f>BDP(A21&amp;" Corp","MATURITY")</f>
+        <f>BDP(A21,"MATURITY")</f>
         <v/>
       </c>
       <c r="I21">
-        <f>BDP(A21&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A21,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="B22">
-        <f>BDP(A22&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A22,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C22">
-        <f>BDP(A22&amp;" Corp","CRNCY")</f>
+        <f>BDP(A22,"CRNCY")</f>
         <v/>
       </c>
       <c r="D22">
-        <f>BDP(A22&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A22,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E22">
-        <f>BDP(A22&amp;" Corp","CPN")/100</f>
+        <f>BDP(A22,"CPN")/100</f>
         <v/>
       </c>
       <c r="F22">
-        <f>BDP(A22&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A22,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G22">
-        <f>BDP(A22&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A22,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H22">
-        <f>BDP(A22&amp;" Corp","MATURITY")</f>
+        <f>BDP(A22,"MATURITY")</f>
         <v/>
       </c>
       <c r="I22">
-        <f>BDP(A22&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A22,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23">
-        <f>BDP(A23&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A23,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C23">
-        <f>BDP(A23&amp;" Corp","CRNCY")</f>
+        <f>BDP(A23,"CRNCY")</f>
         <v/>
       </c>
       <c r="D23">
-        <f>BDP(A23&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A23,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E23">
-        <f>BDP(A23&amp;" Corp","CPN")/100</f>
+        <f>BDP(A23,"CPN")/100</f>
         <v/>
       </c>
       <c r="F23">
-        <f>BDP(A23&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A23,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G23">
-        <f>BDP(A23&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A23,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H23">
-        <f>BDP(A23&amp;" Corp","MATURITY")</f>
+        <f>BDP(A23,"MATURITY")</f>
         <v/>
       </c>
       <c r="I23">
-        <f>BDP(A23&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A23,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24">
-        <f>BDP(A24&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A24,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C24">
-        <f>BDP(A24&amp;" Corp","CRNCY")</f>
+        <f>BDP(A24,"CRNCY")</f>
         <v/>
       </c>
       <c r="D24">
-        <f>BDP(A24&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A24,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E24">
-        <f>BDP(A24&amp;" Corp","CPN")/100</f>
+        <f>BDP(A24,"CPN")/100</f>
         <v/>
       </c>
       <c r="F24">
-        <f>BDP(A24&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A24,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G24">
-        <f>BDP(A24&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A24,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H24">
-        <f>BDP(A24&amp;" Corp","MATURITY")</f>
+        <f>BDP(A24,"MATURITY")</f>
         <v/>
       </c>
       <c r="I24">
-        <f>BDP(A24&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A24,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="B25">
-        <f>BDP(A25&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A25,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C25">
-        <f>BDP(A25&amp;" Corp","CRNCY")</f>
+        <f>BDP(A25,"CRNCY")</f>
         <v/>
       </c>
       <c r="D25">
-        <f>BDP(A25&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A25,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E25">
-        <f>BDP(A25&amp;" Corp","CPN")/100</f>
+        <f>BDP(A25,"CPN")/100</f>
         <v/>
       </c>
       <c r="F25">
-        <f>BDP(A25&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A25,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G25">
-        <f>BDP(A25&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A25,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H25">
-        <f>BDP(A25&amp;" Corp","MATURITY")</f>
+        <f>BDP(A25,"MATURITY")</f>
         <v/>
       </c>
       <c r="I25">
-        <f>BDP(A25&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A25,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="B26">
-        <f>BDP(A26&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A26,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C26">
-        <f>BDP(A26&amp;" Corp","CRNCY")</f>
+        <f>BDP(A26,"CRNCY")</f>
         <v/>
       </c>
       <c r="D26">
-        <f>BDP(A26&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A26,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E26">
-        <f>BDP(A26&amp;" Corp","CPN")/100</f>
+        <f>BDP(A26,"CPN")/100</f>
         <v/>
       </c>
       <c r="F26">
-        <f>BDP(A26&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A26,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G26">
-        <f>BDP(A26&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A26,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H26">
-        <f>BDP(A26&amp;" Corp","MATURITY")</f>
+        <f>BDP(A26,"MATURITY")</f>
         <v/>
       </c>
       <c r="I26">
-        <f>BDP(A26&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A26,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="B27">
-        <f>BDP(A27&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A27,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C27">
-        <f>BDP(A27&amp;" Corp","CRNCY")</f>
+        <f>BDP(A27,"CRNCY")</f>
         <v/>
       </c>
       <c r="D27">
-        <f>BDP(A27&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A27,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E27">
-        <f>BDP(A27&amp;" Corp","CPN")/100</f>
+        <f>BDP(A27,"CPN")/100</f>
         <v/>
       </c>
       <c r="F27">
-        <f>BDP(A27&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A27,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G27">
-        <f>BDP(A27&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A27,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H27">
-        <f>BDP(A27&amp;" Corp","MATURITY")</f>
+        <f>BDP(A27,"MATURITY")</f>
         <v/>
       </c>
       <c r="I27">
-        <f>BDP(A27&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A27,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="B28">
-        <f>BDP(A28&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A28,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C28">
-        <f>BDP(A28&amp;" Corp","CRNCY")</f>
+        <f>BDP(A28,"CRNCY")</f>
         <v/>
       </c>
       <c r="D28">
-        <f>BDP(A28&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A28,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E28">
-        <f>BDP(A28&amp;" Corp","CPN")/100</f>
+        <f>BDP(A28,"CPN")/100</f>
         <v/>
       </c>
       <c r="F28">
-        <f>BDP(A28&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A28,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G28">
-        <f>BDP(A28&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A28,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H28">
-        <f>BDP(A28&amp;" Corp","MATURITY")</f>
+        <f>BDP(A28,"MATURITY")</f>
         <v/>
       </c>
       <c r="I28">
-        <f>BDP(A28&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A28,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="B29">
-        <f>BDP(A29&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A29,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C29">
-        <f>BDP(A29&amp;" Corp","CRNCY")</f>
+        <f>BDP(A29,"CRNCY")</f>
         <v/>
       </c>
       <c r="D29">
-        <f>BDP(A29&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A29,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E29">
-        <f>BDP(A29&amp;" Corp","CPN")/100</f>
+        <f>BDP(A29,"CPN")/100</f>
         <v/>
       </c>
       <c r="F29">
-        <f>BDP(A29&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A29,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G29">
-        <f>BDP(A29&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A29,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H29">
-        <f>BDP(A29&amp;" Corp","MATURITY")</f>
+        <f>BDP(A29,"MATURITY")</f>
         <v/>
       </c>
       <c r="I29">
-        <f>BDP(A29&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A29,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="B30">
-        <f>BDP(A30&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A30,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C30">
-        <f>BDP(A30&amp;" Corp","CRNCY")</f>
+        <f>BDP(A30,"CRNCY")</f>
         <v/>
       </c>
       <c r="D30">
-        <f>BDP(A30&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A30,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E30">
-        <f>BDP(A30&amp;" Corp","CPN")/100</f>
+        <f>BDP(A30,"CPN")/100</f>
         <v/>
       </c>
       <c r="F30">
-        <f>BDP(A30&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A30,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G30">
-        <f>BDP(A30&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A30,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H30">
-        <f>BDP(A30&amp;" Corp","MATURITY")</f>
+        <f>BDP(A30,"MATURITY")</f>
         <v/>
       </c>
       <c r="I30">
-        <f>BDP(A30&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A30,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="B31">
-        <f>BDP(A31&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A31,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C31">
-        <f>BDP(A31&amp;" Corp","CRNCY")</f>
+        <f>BDP(A31,"CRNCY")</f>
         <v/>
       </c>
       <c r="D31">
-        <f>BDP(A31&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A31,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E31">
-        <f>BDP(A31&amp;" Corp","CPN")/100</f>
+        <f>BDP(A31,"CPN")/100</f>
         <v/>
       </c>
       <c r="F31">
-        <f>BDP(A31&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A31,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G31">
-        <f>BDP(A31&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A31,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H31">
-        <f>BDP(A31&amp;" Corp","MATURITY")</f>
+        <f>BDP(A31,"MATURITY")</f>
         <v/>
       </c>
       <c r="I31">
-        <f>BDP(A31&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A31,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="B32">
-        <f>BDP(A32&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A32,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C32">
-        <f>BDP(A32&amp;" Corp","CRNCY")</f>
+        <f>BDP(A32,"CRNCY")</f>
         <v/>
       </c>
       <c r="D32">
-        <f>BDP(A32&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A32,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E32">
-        <f>BDP(A32&amp;" Corp","CPN")/100</f>
+        <f>BDP(A32,"CPN")/100</f>
         <v/>
       </c>
       <c r="F32">
-        <f>BDP(A32&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A32,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G32">
-        <f>BDP(A32&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A32,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H32">
-        <f>BDP(A32&amp;" Corp","MATURITY")</f>
+        <f>BDP(A32,"MATURITY")</f>
         <v/>
       </c>
       <c r="I32">
-        <f>BDP(A32&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A32,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="B33">
-        <f>BDP(A33&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A33,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C33">
-        <f>BDP(A33&amp;" Corp","CRNCY")</f>
+        <f>BDP(A33,"CRNCY")</f>
         <v/>
       </c>
       <c r="D33">
-        <f>BDP(A33&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A33,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E33">
-        <f>BDP(A33&amp;" Corp","CPN")/100</f>
+        <f>BDP(A33,"CPN")/100</f>
         <v/>
       </c>
       <c r="F33">
-        <f>BDP(A33&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A33,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G33">
-        <f>BDP(A33&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A33,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H33">
-        <f>BDP(A33&amp;" Corp","MATURITY")</f>
+        <f>BDP(A33,"MATURITY")</f>
         <v/>
       </c>
       <c r="I33">
-        <f>BDP(A33&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A33,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="B34">
-        <f>BDP(A34&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A34,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C34">
-        <f>BDP(A34&amp;" Corp","CRNCY")</f>
+        <f>BDP(A34,"CRNCY")</f>
         <v/>
       </c>
       <c r="D34">
-        <f>BDP(A34&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A34,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E34">
-        <f>BDP(A34&amp;" Corp","CPN")/100</f>
+        <f>BDP(A34,"CPN")/100</f>
         <v/>
       </c>
       <c r="F34">
-        <f>BDP(A34&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A34,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G34">
-        <f>BDP(A34&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A34,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H34">
-        <f>BDP(A34&amp;" Corp","MATURITY")</f>
+        <f>BDP(A34,"MATURITY")</f>
         <v/>
       </c>
       <c r="I34">
-        <f>BDP(A34&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A34,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="B35">
-        <f>BDP(A35&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A35,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C35">
-        <f>BDP(A35&amp;" Corp","CRNCY")</f>
+        <f>BDP(A35,"CRNCY")</f>
         <v/>
       </c>
       <c r="D35">
-        <f>BDP(A35&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A35,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E35">
-        <f>BDP(A35&amp;" Corp","CPN")/100</f>
+        <f>BDP(A35,"CPN")/100</f>
         <v/>
       </c>
       <c r="F35">
-        <f>BDP(A35&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A35,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G35">
-        <f>BDP(A35&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A35,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H35">
-        <f>BDP(A35&amp;" Corp","MATURITY")</f>
+        <f>BDP(A35,"MATURITY")</f>
         <v/>
       </c>
       <c r="I35">
-        <f>BDP(A35&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A35,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="B36">
-        <f>BDP(A36&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A36,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C36">
-        <f>BDP(A36&amp;" Corp","CRNCY")</f>
+        <f>BDP(A36,"CRNCY")</f>
         <v/>
       </c>
       <c r="D36">
-        <f>BDP(A36&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A36,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E36">
-        <f>BDP(A36&amp;" Corp","CPN")/100</f>
+        <f>BDP(A36,"CPN")/100</f>
         <v/>
       </c>
       <c r="F36">
-        <f>BDP(A36&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A36,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G36">
-        <f>BDP(A36&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A36,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H36">
-        <f>BDP(A36&amp;" Corp","MATURITY")</f>
+        <f>BDP(A36,"MATURITY")</f>
         <v/>
       </c>
       <c r="I36">
-        <f>BDP(A36&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A36,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="B37">
-        <f>BDP(A37&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A37,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C37">
-        <f>BDP(A37&amp;" Corp","CRNCY")</f>
+        <f>BDP(A37,"CRNCY")</f>
         <v/>
       </c>
       <c r="D37">
-        <f>BDP(A37&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A37,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E37">
-        <f>BDP(A37&amp;" Corp","CPN")/100</f>
+        <f>BDP(A37,"CPN")/100</f>
         <v/>
       </c>
       <c r="F37">
-        <f>BDP(A37&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A37,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G37">
-        <f>BDP(A37&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A37,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H37">
-        <f>BDP(A37&amp;" Corp","MATURITY")</f>
+        <f>BDP(A37,"MATURITY")</f>
         <v/>
       </c>
       <c r="I37">
-        <f>BDP(A37&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A37,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="B38">
-        <f>BDP(A38&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A38,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C38">
-        <f>BDP(A38&amp;" Corp","CRNCY")</f>
+        <f>BDP(A38,"CRNCY")</f>
         <v/>
       </c>
       <c r="D38">
-        <f>BDP(A38&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A38,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E38">
-        <f>BDP(A38&amp;" Corp","CPN")/100</f>
+        <f>BDP(A38,"CPN")/100</f>
         <v/>
       </c>
       <c r="F38">
-        <f>BDP(A38&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A38,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G38">
-        <f>BDP(A38&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A38,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H38">
-        <f>BDP(A38&amp;" Corp","MATURITY")</f>
+        <f>BDP(A38,"MATURITY")</f>
         <v/>
       </c>
       <c r="I38">
-        <f>BDP(A38&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A38,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="B39">
-        <f>BDP(A39&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A39,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C39">
-        <f>BDP(A39&amp;" Corp","CRNCY")</f>
+        <f>BDP(A39,"CRNCY")</f>
         <v/>
       </c>
       <c r="D39">
-        <f>BDP(A39&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A39,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E39">
-        <f>BDP(A39&amp;" Corp","CPN")/100</f>
+        <f>BDP(A39,"CPN")/100</f>
         <v/>
       </c>
       <c r="F39">
-        <f>BDP(A39&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A39,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G39">
-        <f>BDP(A39&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A39,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H39">
-        <f>BDP(A39&amp;" Corp","MATURITY")</f>
+        <f>BDP(A39,"MATURITY")</f>
         <v/>
       </c>
       <c r="I39">
-        <f>BDP(A39&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A39,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="B40">
-        <f>BDP(A40&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A40,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C40">
-        <f>BDP(A40&amp;" Corp","CRNCY")</f>
+        <f>BDP(A40,"CRNCY")</f>
         <v/>
       </c>
       <c r="D40">
-        <f>BDP(A40&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A40,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E40">
-        <f>BDP(A40&amp;" Corp","CPN")/100</f>
+        <f>BDP(A40,"CPN")/100</f>
         <v/>
       </c>
       <c r="F40">
-        <f>BDP(A40&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A40,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G40">
-        <f>BDP(A40&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A40,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H40">
-        <f>BDP(A40&amp;" Corp","MATURITY")</f>
+        <f>BDP(A40,"MATURITY")</f>
         <v/>
       </c>
       <c r="I40">
-        <f>BDP(A40&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A40,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="B41">
-        <f>BDP(A41&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A41,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C41">
-        <f>BDP(A41&amp;" Corp","CRNCY")</f>
+        <f>BDP(A41,"CRNCY")</f>
         <v/>
       </c>
       <c r="D41">
-        <f>BDP(A41&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A41,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E41">
-        <f>BDP(A41&amp;" Corp","CPN")/100</f>
+        <f>BDP(A41,"CPN")/100</f>
         <v/>
       </c>
       <c r="F41">
-        <f>BDP(A41&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A41,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G41">
-        <f>BDP(A41&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A41,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H41">
-        <f>BDP(A41&amp;" Corp","MATURITY")</f>
+        <f>BDP(A41,"MATURITY")</f>
         <v/>
       </c>
       <c r="I41">
-        <f>BDP(A41&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A41,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42">
-        <f>BDP(A42&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A42,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C42">
-        <f>BDP(A42&amp;" Corp","CRNCY")</f>
+        <f>BDP(A42,"CRNCY")</f>
         <v/>
       </c>
       <c r="D42">
-        <f>BDP(A42&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A42,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E42">
-        <f>BDP(A42&amp;" Corp","CPN")/100</f>
+        <f>BDP(A42,"CPN")/100</f>
         <v/>
       </c>
       <c r="F42">
-        <f>BDP(A42&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A42,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G42">
-        <f>BDP(A42&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A42,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H42">
-        <f>BDP(A42&amp;" Corp","MATURITY")</f>
+        <f>BDP(A42,"MATURITY")</f>
         <v/>
       </c>
       <c r="I42">
-        <f>BDP(A42&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A42,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43">
-        <f>BDP(A43&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A43,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C43">
-        <f>BDP(A43&amp;" Corp","CRNCY")</f>
+        <f>BDP(A43,"CRNCY")</f>
         <v/>
       </c>
       <c r="D43">
-        <f>BDP(A43&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A43,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E43">
-        <f>BDP(A43&amp;" Corp","CPN")/100</f>
+        <f>BDP(A43,"CPN")/100</f>
         <v/>
       </c>
       <c r="F43">
-        <f>BDP(A43&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A43,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G43">
-        <f>BDP(A43&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A43,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H43">
-        <f>BDP(A43&amp;" Corp","MATURITY")</f>
+        <f>BDP(A43,"MATURITY")</f>
         <v/>
       </c>
       <c r="I43">
-        <f>BDP(A43&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A43,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44">
-        <f>BDP(A44&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A44,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C44">
-        <f>BDP(A44&amp;" Corp","CRNCY")</f>
+        <f>BDP(A44,"CRNCY")</f>
         <v/>
       </c>
       <c r="D44">
-        <f>BDP(A44&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A44,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E44">
-        <f>BDP(A44&amp;" Corp","CPN")/100</f>
+        <f>BDP(A44,"CPN")/100</f>
         <v/>
       </c>
       <c r="F44">
-        <f>BDP(A44&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A44,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G44">
-        <f>BDP(A44&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A44,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H44">
-        <f>BDP(A44&amp;" Corp","MATURITY")</f>
+        <f>BDP(A44,"MATURITY")</f>
         <v/>
       </c>
       <c r="I44">
-        <f>BDP(A44&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A44,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45">
-        <f>BDP(A45&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A45,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C45">
-        <f>BDP(A45&amp;" Corp","CRNCY")</f>
+        <f>BDP(A45,"CRNCY")</f>
         <v/>
       </c>
       <c r="D45">
-        <f>BDP(A45&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A45,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E45">
-        <f>BDP(A45&amp;" Corp","CPN")/100</f>
+        <f>BDP(A45,"CPN")/100</f>
         <v/>
       </c>
       <c r="F45">
-        <f>BDP(A45&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A45,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G45">
-        <f>BDP(A45&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A45,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H45">
-        <f>BDP(A45&amp;" Corp","MATURITY")</f>
+        <f>BDP(A45,"MATURITY")</f>
         <v/>
       </c>
       <c r="I45">
-        <f>BDP(A45&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A45,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46">
-        <f>BDP(A46&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A46,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C46">
-        <f>BDP(A46&amp;" Corp","CRNCY")</f>
+        <f>BDP(A46,"CRNCY")</f>
         <v/>
       </c>
       <c r="D46">
-        <f>BDP(A46&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A46,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E46">
-        <f>BDP(A46&amp;" Corp","CPN")/100</f>
+        <f>BDP(A46,"CPN")/100</f>
         <v/>
       </c>
       <c r="F46">
-        <f>BDP(A46&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A46,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G46">
-        <f>BDP(A46&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A46,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H46">
-        <f>BDP(A46&amp;" Corp","MATURITY")</f>
+        <f>BDP(A46,"MATURITY")</f>
         <v/>
       </c>
       <c r="I46">
-        <f>BDP(A46&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A46,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="B47">
-        <f>BDP(A47&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A47,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C47">
-        <f>BDP(A47&amp;" Corp","CRNCY")</f>
+        <f>BDP(A47,"CRNCY")</f>
         <v/>
       </c>
       <c r="D47">
-        <f>BDP(A47&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A47,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E47">
-        <f>BDP(A47&amp;" Corp","CPN")/100</f>
+        <f>BDP(A47,"CPN")/100</f>
         <v/>
       </c>
       <c r="F47">
-        <f>BDP(A47&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A47,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G47">
-        <f>BDP(A47&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A47,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H47">
-        <f>BDP(A47&amp;" Corp","MATURITY")</f>
+        <f>BDP(A47,"MATURITY")</f>
         <v/>
       </c>
       <c r="I47">
-        <f>BDP(A47&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A47,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="B48">
-        <f>BDP(A48&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A48,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C48">
-        <f>BDP(A48&amp;" Corp","CRNCY")</f>
+        <f>BDP(A48,"CRNCY")</f>
         <v/>
       </c>
       <c r="D48">
-        <f>BDP(A48&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A48,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E48">
-        <f>BDP(A48&amp;" Corp","CPN")/100</f>
+        <f>BDP(A48,"CPN")/100</f>
         <v/>
       </c>
       <c r="F48">
-        <f>BDP(A48&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A48,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G48">
-        <f>BDP(A48&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A48,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H48">
-        <f>BDP(A48&amp;" Corp","MATURITY")</f>
+        <f>BDP(A48,"MATURITY")</f>
         <v/>
       </c>
       <c r="I48">
-        <f>BDP(A48&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A48,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="B49">
-        <f>BDP(A49&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A49,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C49">
-        <f>BDP(A49&amp;" Corp","CRNCY")</f>
+        <f>BDP(A49,"CRNCY")</f>
         <v/>
       </c>
       <c r="D49">
-        <f>BDP(A49&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A49,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E49">
-        <f>BDP(A49&amp;" Corp","CPN")/100</f>
+        <f>BDP(A49,"CPN")/100</f>
         <v/>
       </c>
       <c r="F49">
-        <f>BDP(A49&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A49,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G49">
-        <f>BDP(A49&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A49,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H49">
-        <f>BDP(A49&amp;" Corp","MATURITY")</f>
+        <f>BDP(A49,"MATURITY")</f>
         <v/>
       </c>
       <c r="I49">
-        <f>BDP(A49&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A49,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="B50">
-        <f>BDP(A50&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A50,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C50">
-        <f>BDP(A50&amp;" Corp","CRNCY")</f>
+        <f>BDP(A50,"CRNCY")</f>
         <v/>
       </c>
       <c r="D50">
-        <f>BDP(A50&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A50,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E50">
-        <f>BDP(A50&amp;" Corp","CPN")/100</f>
+        <f>BDP(A50,"CPN")/100</f>
         <v/>
       </c>
       <c r="F50">
-        <f>BDP(A50&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A50,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G50">
-        <f>BDP(A50&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A50,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H50">
-        <f>BDP(A50&amp;" Corp","MATURITY")</f>
+        <f>BDP(A50,"MATURITY")</f>
         <v/>
       </c>
       <c r="I50">
-        <f>BDP(A50&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A50,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="B51">
-        <f>BDP(A51&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A51,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C51">
-        <f>BDP(A51&amp;" Corp","CRNCY")</f>
+        <f>BDP(A51,"CRNCY")</f>
         <v/>
       </c>
       <c r="D51">
-        <f>BDP(A51&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A51,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E51">
-        <f>BDP(A51&amp;" Corp","CPN")/100</f>
+        <f>BDP(A51,"CPN")/100</f>
         <v/>
       </c>
       <c r="F51">
-        <f>BDP(A51&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A51,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G51">
-        <f>BDP(A51&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A51,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H51">
-        <f>BDP(A51&amp;" Corp","MATURITY")</f>
+        <f>BDP(A51,"MATURITY")</f>
         <v/>
       </c>
       <c r="I51">
-        <f>BDP(A51&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A51,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
@@ -2951,35 +2946,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>BBG Ticker</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>PX_LAST</t>
+          <t>Start (YYYYMMDD)</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>End</t>
+          <t>End (YYYYMMDD)</t>
         </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3">
-        <f>BDH(A1,"PX_LAST",B1,C1,"Fill","0","Dates","1")</f>
-        <v/>
       </c>
     </row>
   </sheetData>

--- a/projects/02-pnl-dashboard/templates/bloomberg_prices.xlsx
+++ b/projects/02-pnl-dashboard/templates/bloomberg_prices.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Live MTM" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Static" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="History" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +33,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
     </font>
   </fonts>
   <fills count="3">
@@ -61,12 +65,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +440,7 @@
   <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -444,7 +449,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BBG Ticker</t>
+          <t>CUSIP</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -465,701 +470,701 @@
     </row>
     <row r="2">
       <c r="B2">
-        <f>BDP(A2,"PX_LAST")</f>
+        <f>BDP(A2&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C2">
-        <f>BDP(A2,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A2&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D2">
-        <f>BDP(A2,"YLD_YTM_MID")</f>
+        <f>BDP(A2&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="B3">
-        <f>BDP(A3,"PX_LAST")</f>
+        <f>BDP(A3&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C3">
-        <f>BDP(A3,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A3&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D3">
-        <f>BDP(A3,"YLD_YTM_MID")</f>
+        <f>BDP(A3&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="B4">
-        <f>BDP(A4,"PX_LAST")</f>
+        <f>BDP(A4&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C4">
-        <f>BDP(A4,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A4&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D4">
-        <f>BDP(A4,"YLD_YTM_MID")</f>
+        <f>BDP(A4&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="B5">
-        <f>BDP(A5,"PX_LAST")</f>
+        <f>BDP(A5&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C5">
-        <f>BDP(A5,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A5&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D5">
-        <f>BDP(A5,"YLD_YTM_MID")</f>
+        <f>BDP(A5&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="B6">
-        <f>BDP(A6,"PX_LAST")</f>
+        <f>BDP(A6&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C6">
-        <f>BDP(A6,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A6&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D6">
-        <f>BDP(A6,"YLD_YTM_MID")</f>
+        <f>BDP(A6&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="B7">
-        <f>BDP(A7,"PX_LAST")</f>
+        <f>BDP(A7&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C7">
-        <f>BDP(A7,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A7&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D7">
-        <f>BDP(A7,"YLD_YTM_MID")</f>
+        <f>BDP(A7&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="B8">
-        <f>BDP(A8,"PX_LAST")</f>
+        <f>BDP(A8&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C8">
-        <f>BDP(A8,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A8&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D8">
-        <f>BDP(A8,"YLD_YTM_MID")</f>
+        <f>BDP(A8&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="B9">
-        <f>BDP(A9,"PX_LAST")</f>
+        <f>BDP(A9&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C9">
-        <f>BDP(A9,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A9&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D9">
-        <f>BDP(A9,"YLD_YTM_MID")</f>
+        <f>BDP(A9&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="B10">
-        <f>BDP(A10,"PX_LAST")</f>
+        <f>BDP(A10&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C10">
-        <f>BDP(A10,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A10&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D10">
-        <f>BDP(A10,"YLD_YTM_MID")</f>
+        <f>BDP(A10&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="B11">
-        <f>BDP(A11,"PX_LAST")</f>
+        <f>BDP(A11&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C11">
-        <f>BDP(A11,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A11&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D11">
-        <f>BDP(A11,"YLD_YTM_MID")</f>
+        <f>BDP(A11&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="B12">
-        <f>BDP(A12,"PX_LAST")</f>
+        <f>BDP(A12&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C12">
-        <f>BDP(A12,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A12&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D12">
-        <f>BDP(A12,"YLD_YTM_MID")</f>
+        <f>BDP(A12&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="B13">
-        <f>BDP(A13,"PX_LAST")</f>
+        <f>BDP(A13&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C13">
-        <f>BDP(A13,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A13&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D13">
-        <f>BDP(A13,"YLD_YTM_MID")</f>
+        <f>BDP(A13&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="B14">
-        <f>BDP(A14,"PX_LAST")</f>
+        <f>BDP(A14&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C14">
-        <f>BDP(A14,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A14&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D14">
-        <f>BDP(A14,"YLD_YTM_MID")</f>
+        <f>BDP(A14&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="B15">
-        <f>BDP(A15,"PX_LAST")</f>
+        <f>BDP(A15&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C15">
-        <f>BDP(A15,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A15&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D15">
-        <f>BDP(A15,"YLD_YTM_MID")</f>
+        <f>BDP(A15&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="B16">
-        <f>BDP(A16,"PX_LAST")</f>
+        <f>BDP(A16&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C16">
-        <f>BDP(A16,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A16&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D16">
-        <f>BDP(A16,"YLD_YTM_MID")</f>
+        <f>BDP(A16&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="B17">
-        <f>BDP(A17,"PX_LAST")</f>
+        <f>BDP(A17&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C17">
-        <f>BDP(A17,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A17&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D17">
-        <f>BDP(A17,"YLD_YTM_MID")</f>
+        <f>BDP(A17&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="B18">
-        <f>BDP(A18,"PX_LAST")</f>
+        <f>BDP(A18&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C18">
-        <f>BDP(A18,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A18&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D18">
-        <f>BDP(A18,"YLD_YTM_MID")</f>
+        <f>BDP(A18&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="B19">
-        <f>BDP(A19,"PX_LAST")</f>
+        <f>BDP(A19&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C19">
-        <f>BDP(A19,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A19&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D19">
-        <f>BDP(A19,"YLD_YTM_MID")</f>
+        <f>BDP(A19&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="B20">
-        <f>BDP(A20,"PX_LAST")</f>
+        <f>BDP(A20&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C20">
-        <f>BDP(A20,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A20&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D20">
-        <f>BDP(A20,"YLD_YTM_MID")</f>
+        <f>BDP(A20&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="B21">
-        <f>BDP(A21,"PX_LAST")</f>
+        <f>BDP(A21&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C21">
-        <f>BDP(A21,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A21&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D21">
-        <f>BDP(A21,"YLD_YTM_MID")</f>
+        <f>BDP(A21&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="B22">
-        <f>BDP(A22,"PX_LAST")</f>
+        <f>BDP(A22&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C22">
-        <f>BDP(A22,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A22&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D22">
-        <f>BDP(A22,"YLD_YTM_MID")</f>
+        <f>BDP(A22&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23">
-        <f>BDP(A23,"PX_LAST")</f>
+        <f>BDP(A23&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C23">
-        <f>BDP(A23,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A23&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D23">
-        <f>BDP(A23,"YLD_YTM_MID")</f>
+        <f>BDP(A23&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24">
-        <f>BDP(A24,"PX_LAST")</f>
+        <f>BDP(A24&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C24">
-        <f>BDP(A24,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A24&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D24">
-        <f>BDP(A24,"YLD_YTM_MID")</f>
+        <f>BDP(A24&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="B25">
-        <f>BDP(A25,"PX_LAST")</f>
+        <f>BDP(A25&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C25">
-        <f>BDP(A25,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A25&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D25">
-        <f>BDP(A25,"YLD_YTM_MID")</f>
+        <f>BDP(A25&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="B26">
-        <f>BDP(A26,"PX_LAST")</f>
+        <f>BDP(A26&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C26">
-        <f>BDP(A26,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A26&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D26">
-        <f>BDP(A26,"YLD_YTM_MID")</f>
+        <f>BDP(A26&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="B27">
-        <f>BDP(A27,"PX_LAST")</f>
+        <f>BDP(A27&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C27">
-        <f>BDP(A27,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A27&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D27">
-        <f>BDP(A27,"YLD_YTM_MID")</f>
+        <f>BDP(A27&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="B28">
-        <f>BDP(A28,"PX_LAST")</f>
+        <f>BDP(A28&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C28">
-        <f>BDP(A28,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A28&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D28">
-        <f>BDP(A28,"YLD_YTM_MID")</f>
+        <f>BDP(A28&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="B29">
-        <f>BDP(A29,"PX_LAST")</f>
+        <f>BDP(A29&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C29">
-        <f>BDP(A29,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A29&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D29">
-        <f>BDP(A29,"YLD_YTM_MID")</f>
+        <f>BDP(A29&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="B30">
-        <f>BDP(A30,"PX_LAST")</f>
+        <f>BDP(A30&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C30">
-        <f>BDP(A30,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A30&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D30">
-        <f>BDP(A30,"YLD_YTM_MID")</f>
+        <f>BDP(A30&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="B31">
-        <f>BDP(A31,"PX_LAST")</f>
+        <f>BDP(A31&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C31">
-        <f>BDP(A31,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A31&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D31">
-        <f>BDP(A31,"YLD_YTM_MID")</f>
+        <f>BDP(A31&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="B32">
-        <f>BDP(A32,"PX_LAST")</f>
+        <f>BDP(A32&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C32">
-        <f>BDP(A32,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A32&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D32">
-        <f>BDP(A32,"YLD_YTM_MID")</f>
+        <f>BDP(A32&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="B33">
-        <f>BDP(A33,"PX_LAST")</f>
+        <f>BDP(A33&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C33">
-        <f>BDP(A33,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A33&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D33">
-        <f>BDP(A33,"YLD_YTM_MID")</f>
+        <f>BDP(A33&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="B34">
-        <f>BDP(A34,"PX_LAST")</f>
+        <f>BDP(A34&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C34">
-        <f>BDP(A34,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A34&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D34">
-        <f>BDP(A34,"YLD_YTM_MID")</f>
+        <f>BDP(A34&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="B35">
-        <f>BDP(A35,"PX_LAST")</f>
+        <f>BDP(A35&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C35">
-        <f>BDP(A35,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A35&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D35">
-        <f>BDP(A35,"YLD_YTM_MID")</f>
+        <f>BDP(A35&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="B36">
-        <f>BDP(A36,"PX_LAST")</f>
+        <f>BDP(A36&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C36">
-        <f>BDP(A36,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A36&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D36">
-        <f>BDP(A36,"YLD_YTM_MID")</f>
+        <f>BDP(A36&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="B37">
-        <f>BDP(A37,"PX_LAST")</f>
+        <f>BDP(A37&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C37">
-        <f>BDP(A37,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A37&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D37">
-        <f>BDP(A37,"YLD_YTM_MID")</f>
+        <f>BDP(A37&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="B38">
-        <f>BDP(A38,"PX_LAST")</f>
+        <f>BDP(A38&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C38">
-        <f>BDP(A38,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A38&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D38">
-        <f>BDP(A38,"YLD_YTM_MID")</f>
+        <f>BDP(A38&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="B39">
-        <f>BDP(A39,"PX_LAST")</f>
+        <f>BDP(A39&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C39">
-        <f>BDP(A39,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A39&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D39">
-        <f>BDP(A39,"YLD_YTM_MID")</f>
+        <f>BDP(A39&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="B40">
-        <f>BDP(A40,"PX_LAST")</f>
+        <f>BDP(A40&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C40">
-        <f>BDP(A40,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A40&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D40">
-        <f>BDP(A40,"YLD_YTM_MID")</f>
+        <f>BDP(A40&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="B41">
-        <f>BDP(A41,"PX_LAST")</f>
+        <f>BDP(A41&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C41">
-        <f>BDP(A41,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A41&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D41">
-        <f>BDP(A41,"YLD_YTM_MID")</f>
+        <f>BDP(A41&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42">
-        <f>BDP(A42,"PX_LAST")</f>
+        <f>BDP(A42&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C42">
-        <f>BDP(A42,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A42&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D42">
-        <f>BDP(A42,"YLD_YTM_MID")</f>
+        <f>BDP(A42&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43">
-        <f>BDP(A43,"PX_LAST")</f>
+        <f>BDP(A43&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C43">
-        <f>BDP(A43,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A43&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D43">
-        <f>BDP(A43,"YLD_YTM_MID")</f>
+        <f>BDP(A43&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44">
-        <f>BDP(A44,"PX_LAST")</f>
+        <f>BDP(A44&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C44">
-        <f>BDP(A44,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A44&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D44">
-        <f>BDP(A44,"YLD_YTM_MID")</f>
+        <f>BDP(A44&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45">
-        <f>BDP(A45,"PX_LAST")</f>
+        <f>BDP(A45&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C45">
-        <f>BDP(A45,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A45&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D45">
-        <f>BDP(A45,"YLD_YTM_MID")</f>
+        <f>BDP(A45&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46">
-        <f>BDP(A46,"PX_LAST")</f>
+        <f>BDP(A46&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C46">
-        <f>BDP(A46,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A46&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D46">
-        <f>BDP(A46,"YLD_YTM_MID")</f>
+        <f>BDP(A46&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="B47">
-        <f>BDP(A47,"PX_LAST")</f>
+        <f>BDP(A47&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C47">
-        <f>BDP(A47,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A47&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D47">
-        <f>BDP(A47,"YLD_YTM_MID")</f>
+        <f>BDP(A47&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="B48">
-        <f>BDP(A48,"PX_LAST")</f>
+        <f>BDP(A48&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C48">
-        <f>BDP(A48,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A48&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D48">
-        <f>BDP(A48,"YLD_YTM_MID")</f>
+        <f>BDP(A48&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="B49">
-        <f>BDP(A49,"PX_LAST")</f>
+        <f>BDP(A49&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C49">
-        <f>BDP(A49,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A49&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D49">
-        <f>BDP(A49,"YLD_YTM_MID")</f>
+        <f>BDP(A49&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="B50">
-        <f>BDP(A50,"PX_LAST")</f>
+        <f>BDP(A50&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C50">
-        <f>BDP(A50,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A50&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D50">
-        <f>BDP(A50,"YLD_YTM_MID")</f>
+        <f>BDP(A50&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="B51">
-        <f>BDP(A51,"PX_LAST")</f>
+        <f>BDP(A51&amp;" Corp","PX_LAST")</f>
         <v/>
       </c>
       <c r="C51">
-        <f>BDP(A51,"YAS_ASW_SPREAD")</f>
+        <f>BDP(A51&amp;" Corp","YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D51">
-        <f>BDP(A51,"YLD_YTM_MID")</f>
+        <f>BDP(A51&amp;" Corp","YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
@@ -1177,7 +1182,7 @@
   <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -1191,7 +1196,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>bbg_ticker</t>
+          <t>cusip</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1237,1701 +1242,1701 @@
     </row>
     <row r="2">
       <c r="B2">
-        <f>BDP(A2,"SECURITY_DES")</f>
+        <f>BDP(A2&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C2">
-        <f>BDP(A2,"CRNCY")</f>
+        <f>BDP(A2&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D2">
-        <f>BDP(A2,"CNTRY_OF_RISK")</f>
+        <f>BDP(A2&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E2">
-        <f>BDP(A2,"CPN")/100</f>
+        <f>BDP(A2&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F2">
-        <f>BDP(A2,"CPN_FREQ")</f>
+        <f>BDP(A2&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G2">
-        <f>BDP(A2,"DAY_CNT_DES")</f>
+        <f>BDP(A2&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H2">
-        <f>BDP(A2,"MATURITY")</f>
+        <f>BDP(A2&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I2">
-        <f>BDP(A2,"FIRST_CPN_DT")</f>
+        <f>BDP(A2&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="B3">
-        <f>BDP(A3,"SECURITY_DES")</f>
+        <f>BDP(A3&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C3">
-        <f>BDP(A3,"CRNCY")</f>
+        <f>BDP(A3&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D3">
-        <f>BDP(A3,"CNTRY_OF_RISK")</f>
+        <f>BDP(A3&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E3">
-        <f>BDP(A3,"CPN")/100</f>
+        <f>BDP(A3&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F3">
-        <f>BDP(A3,"CPN_FREQ")</f>
+        <f>BDP(A3&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G3">
-        <f>BDP(A3,"DAY_CNT_DES")</f>
+        <f>BDP(A3&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H3">
-        <f>BDP(A3,"MATURITY")</f>
+        <f>BDP(A3&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I3">
-        <f>BDP(A3,"FIRST_CPN_DT")</f>
+        <f>BDP(A3&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="B4">
-        <f>BDP(A4,"SECURITY_DES")</f>
+        <f>BDP(A4&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C4">
-        <f>BDP(A4,"CRNCY")</f>
+        <f>BDP(A4&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D4">
-        <f>BDP(A4,"CNTRY_OF_RISK")</f>
+        <f>BDP(A4&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E4">
-        <f>BDP(A4,"CPN")/100</f>
+        <f>BDP(A4&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F4">
-        <f>BDP(A4,"CPN_FREQ")</f>
+        <f>BDP(A4&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G4">
-        <f>BDP(A4,"DAY_CNT_DES")</f>
+        <f>BDP(A4&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H4">
-        <f>BDP(A4,"MATURITY")</f>
+        <f>BDP(A4&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I4">
-        <f>BDP(A4,"FIRST_CPN_DT")</f>
+        <f>BDP(A4&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="B5">
-        <f>BDP(A5,"SECURITY_DES")</f>
+        <f>BDP(A5&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C5">
-        <f>BDP(A5,"CRNCY")</f>
+        <f>BDP(A5&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D5">
-        <f>BDP(A5,"CNTRY_OF_RISK")</f>
+        <f>BDP(A5&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E5">
-        <f>BDP(A5,"CPN")/100</f>
+        <f>BDP(A5&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F5">
-        <f>BDP(A5,"CPN_FREQ")</f>
+        <f>BDP(A5&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G5">
-        <f>BDP(A5,"DAY_CNT_DES")</f>
+        <f>BDP(A5&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H5">
-        <f>BDP(A5,"MATURITY")</f>
+        <f>BDP(A5&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I5">
-        <f>BDP(A5,"FIRST_CPN_DT")</f>
+        <f>BDP(A5&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="B6">
-        <f>BDP(A6,"SECURITY_DES")</f>
+        <f>BDP(A6&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C6">
-        <f>BDP(A6,"CRNCY")</f>
+        <f>BDP(A6&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D6">
-        <f>BDP(A6,"CNTRY_OF_RISK")</f>
+        <f>BDP(A6&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E6">
-        <f>BDP(A6,"CPN")/100</f>
+        <f>BDP(A6&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F6">
-        <f>BDP(A6,"CPN_FREQ")</f>
+        <f>BDP(A6&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G6">
-        <f>BDP(A6,"DAY_CNT_DES")</f>
+        <f>BDP(A6&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H6">
-        <f>BDP(A6,"MATURITY")</f>
+        <f>BDP(A6&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I6">
-        <f>BDP(A6,"FIRST_CPN_DT")</f>
+        <f>BDP(A6&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="B7">
-        <f>BDP(A7,"SECURITY_DES")</f>
+        <f>BDP(A7&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C7">
-        <f>BDP(A7,"CRNCY")</f>
+        <f>BDP(A7&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D7">
-        <f>BDP(A7,"CNTRY_OF_RISK")</f>
+        <f>BDP(A7&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E7">
-        <f>BDP(A7,"CPN")/100</f>
+        <f>BDP(A7&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F7">
-        <f>BDP(A7,"CPN_FREQ")</f>
+        <f>BDP(A7&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G7">
-        <f>BDP(A7,"DAY_CNT_DES")</f>
+        <f>BDP(A7&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H7">
-        <f>BDP(A7,"MATURITY")</f>
+        <f>BDP(A7&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I7">
-        <f>BDP(A7,"FIRST_CPN_DT")</f>
+        <f>BDP(A7&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="B8">
-        <f>BDP(A8,"SECURITY_DES")</f>
+        <f>BDP(A8&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C8">
-        <f>BDP(A8,"CRNCY")</f>
+        <f>BDP(A8&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D8">
-        <f>BDP(A8,"CNTRY_OF_RISK")</f>
+        <f>BDP(A8&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E8">
-        <f>BDP(A8,"CPN")/100</f>
+        <f>BDP(A8&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F8">
-        <f>BDP(A8,"CPN_FREQ")</f>
+        <f>BDP(A8&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G8">
-        <f>BDP(A8,"DAY_CNT_DES")</f>
+        <f>BDP(A8&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H8">
-        <f>BDP(A8,"MATURITY")</f>
+        <f>BDP(A8&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I8">
-        <f>BDP(A8,"FIRST_CPN_DT")</f>
+        <f>BDP(A8&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="B9">
-        <f>BDP(A9,"SECURITY_DES")</f>
+        <f>BDP(A9&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C9">
-        <f>BDP(A9,"CRNCY")</f>
+        <f>BDP(A9&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D9">
-        <f>BDP(A9,"CNTRY_OF_RISK")</f>
+        <f>BDP(A9&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E9">
-        <f>BDP(A9,"CPN")/100</f>
+        <f>BDP(A9&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F9">
-        <f>BDP(A9,"CPN_FREQ")</f>
+        <f>BDP(A9&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G9">
-        <f>BDP(A9,"DAY_CNT_DES")</f>
+        <f>BDP(A9&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H9">
-        <f>BDP(A9,"MATURITY")</f>
+        <f>BDP(A9&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I9">
-        <f>BDP(A9,"FIRST_CPN_DT")</f>
+        <f>BDP(A9&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="B10">
-        <f>BDP(A10,"SECURITY_DES")</f>
+        <f>BDP(A10&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C10">
-        <f>BDP(A10,"CRNCY")</f>
+        <f>BDP(A10&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D10">
-        <f>BDP(A10,"CNTRY_OF_RISK")</f>
+        <f>BDP(A10&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E10">
-        <f>BDP(A10,"CPN")/100</f>
+        <f>BDP(A10&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F10">
-        <f>BDP(A10,"CPN_FREQ")</f>
+        <f>BDP(A10&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G10">
-        <f>BDP(A10,"DAY_CNT_DES")</f>
+        <f>BDP(A10&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H10">
-        <f>BDP(A10,"MATURITY")</f>
+        <f>BDP(A10&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I10">
-        <f>BDP(A10,"FIRST_CPN_DT")</f>
+        <f>BDP(A10&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="B11">
-        <f>BDP(A11,"SECURITY_DES")</f>
+        <f>BDP(A11&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C11">
-        <f>BDP(A11,"CRNCY")</f>
+        <f>BDP(A11&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D11">
-        <f>BDP(A11,"CNTRY_OF_RISK")</f>
+        <f>BDP(A11&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E11">
-        <f>BDP(A11,"CPN")/100</f>
+        <f>BDP(A11&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F11">
-        <f>BDP(A11,"CPN_FREQ")</f>
+        <f>BDP(A11&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G11">
-        <f>BDP(A11,"DAY_CNT_DES")</f>
+        <f>BDP(A11&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H11">
-        <f>BDP(A11,"MATURITY")</f>
+        <f>BDP(A11&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I11">
-        <f>BDP(A11,"FIRST_CPN_DT")</f>
+        <f>BDP(A11&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="B12">
-        <f>BDP(A12,"SECURITY_DES")</f>
+        <f>BDP(A12&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C12">
-        <f>BDP(A12,"CRNCY")</f>
+        <f>BDP(A12&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D12">
-        <f>BDP(A12,"CNTRY_OF_RISK")</f>
+        <f>BDP(A12&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E12">
-        <f>BDP(A12,"CPN")/100</f>
+        <f>BDP(A12&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F12">
-        <f>BDP(A12,"CPN_FREQ")</f>
+        <f>BDP(A12&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G12">
-        <f>BDP(A12,"DAY_CNT_DES")</f>
+        <f>BDP(A12&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H12">
-        <f>BDP(A12,"MATURITY")</f>
+        <f>BDP(A12&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I12">
-        <f>BDP(A12,"FIRST_CPN_DT")</f>
+        <f>BDP(A12&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="B13">
-        <f>BDP(A13,"SECURITY_DES")</f>
+        <f>BDP(A13&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C13">
-        <f>BDP(A13,"CRNCY")</f>
+        <f>BDP(A13&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D13">
-        <f>BDP(A13,"CNTRY_OF_RISK")</f>
+        <f>BDP(A13&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E13">
-        <f>BDP(A13,"CPN")/100</f>
+        <f>BDP(A13&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F13">
-        <f>BDP(A13,"CPN_FREQ")</f>
+        <f>BDP(A13&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G13">
-        <f>BDP(A13,"DAY_CNT_DES")</f>
+        <f>BDP(A13&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H13">
-        <f>BDP(A13,"MATURITY")</f>
+        <f>BDP(A13&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I13">
-        <f>BDP(A13,"FIRST_CPN_DT")</f>
+        <f>BDP(A13&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="B14">
-        <f>BDP(A14,"SECURITY_DES")</f>
+        <f>BDP(A14&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C14">
-        <f>BDP(A14,"CRNCY")</f>
+        <f>BDP(A14&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D14">
-        <f>BDP(A14,"CNTRY_OF_RISK")</f>
+        <f>BDP(A14&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E14">
-        <f>BDP(A14,"CPN")/100</f>
+        <f>BDP(A14&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F14">
-        <f>BDP(A14,"CPN_FREQ")</f>
+        <f>BDP(A14&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G14">
-        <f>BDP(A14,"DAY_CNT_DES")</f>
+        <f>BDP(A14&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H14">
-        <f>BDP(A14,"MATURITY")</f>
+        <f>BDP(A14&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I14">
-        <f>BDP(A14,"FIRST_CPN_DT")</f>
+        <f>BDP(A14&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="B15">
-        <f>BDP(A15,"SECURITY_DES")</f>
+        <f>BDP(A15&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C15">
-        <f>BDP(A15,"CRNCY")</f>
+        <f>BDP(A15&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D15">
-        <f>BDP(A15,"CNTRY_OF_RISK")</f>
+        <f>BDP(A15&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E15">
-        <f>BDP(A15,"CPN")/100</f>
+        <f>BDP(A15&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F15">
-        <f>BDP(A15,"CPN_FREQ")</f>
+        <f>BDP(A15&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G15">
-        <f>BDP(A15,"DAY_CNT_DES")</f>
+        <f>BDP(A15&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H15">
-        <f>BDP(A15,"MATURITY")</f>
+        <f>BDP(A15&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I15">
-        <f>BDP(A15,"FIRST_CPN_DT")</f>
+        <f>BDP(A15&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="B16">
-        <f>BDP(A16,"SECURITY_DES")</f>
+        <f>BDP(A16&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C16">
-        <f>BDP(A16,"CRNCY")</f>
+        <f>BDP(A16&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D16">
-        <f>BDP(A16,"CNTRY_OF_RISK")</f>
+        <f>BDP(A16&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E16">
-        <f>BDP(A16,"CPN")/100</f>
+        <f>BDP(A16&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F16">
-        <f>BDP(A16,"CPN_FREQ")</f>
+        <f>BDP(A16&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G16">
-        <f>BDP(A16,"DAY_CNT_DES")</f>
+        <f>BDP(A16&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H16">
-        <f>BDP(A16,"MATURITY")</f>
+        <f>BDP(A16&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I16">
-        <f>BDP(A16,"FIRST_CPN_DT")</f>
+        <f>BDP(A16&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="B17">
-        <f>BDP(A17,"SECURITY_DES")</f>
+        <f>BDP(A17&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C17">
-        <f>BDP(A17,"CRNCY")</f>
+        <f>BDP(A17&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D17">
-        <f>BDP(A17,"CNTRY_OF_RISK")</f>
+        <f>BDP(A17&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E17">
-        <f>BDP(A17,"CPN")/100</f>
+        <f>BDP(A17&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F17">
-        <f>BDP(A17,"CPN_FREQ")</f>
+        <f>BDP(A17&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G17">
-        <f>BDP(A17,"DAY_CNT_DES")</f>
+        <f>BDP(A17&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H17">
-        <f>BDP(A17,"MATURITY")</f>
+        <f>BDP(A17&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I17">
-        <f>BDP(A17,"FIRST_CPN_DT")</f>
+        <f>BDP(A17&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="B18">
-        <f>BDP(A18,"SECURITY_DES")</f>
+        <f>BDP(A18&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C18">
-        <f>BDP(A18,"CRNCY")</f>
+        <f>BDP(A18&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D18">
-        <f>BDP(A18,"CNTRY_OF_RISK")</f>
+        <f>BDP(A18&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E18">
-        <f>BDP(A18,"CPN")/100</f>
+        <f>BDP(A18&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F18">
-        <f>BDP(A18,"CPN_FREQ")</f>
+        <f>BDP(A18&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G18">
-        <f>BDP(A18,"DAY_CNT_DES")</f>
+        <f>BDP(A18&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H18">
-        <f>BDP(A18,"MATURITY")</f>
+        <f>BDP(A18&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I18">
-        <f>BDP(A18,"FIRST_CPN_DT")</f>
+        <f>BDP(A18&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="B19">
-        <f>BDP(A19,"SECURITY_DES")</f>
+        <f>BDP(A19&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C19">
-        <f>BDP(A19,"CRNCY")</f>
+        <f>BDP(A19&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D19">
-        <f>BDP(A19,"CNTRY_OF_RISK")</f>
+        <f>BDP(A19&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E19">
-        <f>BDP(A19,"CPN")/100</f>
+        <f>BDP(A19&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F19">
-        <f>BDP(A19,"CPN_FREQ")</f>
+        <f>BDP(A19&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G19">
-        <f>BDP(A19,"DAY_CNT_DES")</f>
+        <f>BDP(A19&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H19">
-        <f>BDP(A19,"MATURITY")</f>
+        <f>BDP(A19&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I19">
-        <f>BDP(A19,"FIRST_CPN_DT")</f>
+        <f>BDP(A19&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="B20">
-        <f>BDP(A20,"SECURITY_DES")</f>
+        <f>BDP(A20&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C20">
-        <f>BDP(A20,"CRNCY")</f>
+        <f>BDP(A20&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D20">
-        <f>BDP(A20,"CNTRY_OF_RISK")</f>
+        <f>BDP(A20&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E20">
-        <f>BDP(A20,"CPN")/100</f>
+        <f>BDP(A20&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F20">
-        <f>BDP(A20,"CPN_FREQ")</f>
+        <f>BDP(A20&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G20">
-        <f>BDP(A20,"DAY_CNT_DES")</f>
+        <f>BDP(A20&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H20">
-        <f>BDP(A20,"MATURITY")</f>
+        <f>BDP(A20&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I20">
-        <f>BDP(A20,"FIRST_CPN_DT")</f>
+        <f>BDP(A20&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="B21">
-        <f>BDP(A21,"SECURITY_DES")</f>
+        <f>BDP(A21&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C21">
-        <f>BDP(A21,"CRNCY")</f>
+        <f>BDP(A21&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D21">
-        <f>BDP(A21,"CNTRY_OF_RISK")</f>
+        <f>BDP(A21&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E21">
-        <f>BDP(A21,"CPN")/100</f>
+        <f>BDP(A21&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F21">
-        <f>BDP(A21,"CPN_FREQ")</f>
+        <f>BDP(A21&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G21">
-        <f>BDP(A21,"DAY_CNT_DES")</f>
+        <f>BDP(A21&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H21">
-        <f>BDP(A21,"MATURITY")</f>
+        <f>BDP(A21&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I21">
-        <f>BDP(A21,"FIRST_CPN_DT")</f>
+        <f>BDP(A21&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="B22">
-        <f>BDP(A22,"SECURITY_DES")</f>
+        <f>BDP(A22&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C22">
-        <f>BDP(A22,"CRNCY")</f>
+        <f>BDP(A22&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D22">
-        <f>BDP(A22,"CNTRY_OF_RISK")</f>
+        <f>BDP(A22&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E22">
-        <f>BDP(A22,"CPN")/100</f>
+        <f>BDP(A22&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F22">
-        <f>BDP(A22,"CPN_FREQ")</f>
+        <f>BDP(A22&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G22">
-        <f>BDP(A22,"DAY_CNT_DES")</f>
+        <f>BDP(A22&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H22">
-        <f>BDP(A22,"MATURITY")</f>
+        <f>BDP(A22&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I22">
-        <f>BDP(A22,"FIRST_CPN_DT")</f>
+        <f>BDP(A22&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23">
-        <f>BDP(A23,"SECURITY_DES")</f>
+        <f>BDP(A23&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C23">
-        <f>BDP(A23,"CRNCY")</f>
+        <f>BDP(A23&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D23">
-        <f>BDP(A23,"CNTRY_OF_RISK")</f>
+        <f>BDP(A23&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E23">
-        <f>BDP(A23,"CPN")/100</f>
+        <f>BDP(A23&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F23">
-        <f>BDP(A23,"CPN_FREQ")</f>
+        <f>BDP(A23&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G23">
-        <f>BDP(A23,"DAY_CNT_DES")</f>
+        <f>BDP(A23&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H23">
-        <f>BDP(A23,"MATURITY")</f>
+        <f>BDP(A23&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I23">
-        <f>BDP(A23,"FIRST_CPN_DT")</f>
+        <f>BDP(A23&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24">
-        <f>BDP(A24,"SECURITY_DES")</f>
+        <f>BDP(A24&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C24">
-        <f>BDP(A24,"CRNCY")</f>
+        <f>BDP(A24&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D24">
-        <f>BDP(A24,"CNTRY_OF_RISK")</f>
+        <f>BDP(A24&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E24">
-        <f>BDP(A24,"CPN")/100</f>
+        <f>BDP(A24&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F24">
-        <f>BDP(A24,"CPN_FREQ")</f>
+        <f>BDP(A24&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G24">
-        <f>BDP(A24,"DAY_CNT_DES")</f>
+        <f>BDP(A24&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H24">
-        <f>BDP(A24,"MATURITY")</f>
+        <f>BDP(A24&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I24">
-        <f>BDP(A24,"FIRST_CPN_DT")</f>
+        <f>BDP(A24&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="B25">
-        <f>BDP(A25,"SECURITY_DES")</f>
+        <f>BDP(A25&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C25">
-        <f>BDP(A25,"CRNCY")</f>
+        <f>BDP(A25&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D25">
-        <f>BDP(A25,"CNTRY_OF_RISK")</f>
+        <f>BDP(A25&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E25">
-        <f>BDP(A25,"CPN")/100</f>
+        <f>BDP(A25&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F25">
-        <f>BDP(A25,"CPN_FREQ")</f>
+        <f>BDP(A25&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G25">
-        <f>BDP(A25,"DAY_CNT_DES")</f>
+        <f>BDP(A25&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H25">
-        <f>BDP(A25,"MATURITY")</f>
+        <f>BDP(A25&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I25">
-        <f>BDP(A25,"FIRST_CPN_DT")</f>
+        <f>BDP(A25&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="B26">
-        <f>BDP(A26,"SECURITY_DES")</f>
+        <f>BDP(A26&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C26">
-        <f>BDP(A26,"CRNCY")</f>
+        <f>BDP(A26&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D26">
-        <f>BDP(A26,"CNTRY_OF_RISK")</f>
+        <f>BDP(A26&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E26">
-        <f>BDP(A26,"CPN")/100</f>
+        <f>BDP(A26&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F26">
-        <f>BDP(A26,"CPN_FREQ")</f>
+        <f>BDP(A26&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G26">
-        <f>BDP(A26,"DAY_CNT_DES")</f>
+        <f>BDP(A26&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H26">
-        <f>BDP(A26,"MATURITY")</f>
+        <f>BDP(A26&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I26">
-        <f>BDP(A26,"FIRST_CPN_DT")</f>
+        <f>BDP(A26&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="B27">
-        <f>BDP(A27,"SECURITY_DES")</f>
+        <f>BDP(A27&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C27">
-        <f>BDP(A27,"CRNCY")</f>
+        <f>BDP(A27&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D27">
-        <f>BDP(A27,"CNTRY_OF_RISK")</f>
+        <f>BDP(A27&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E27">
-        <f>BDP(A27,"CPN")/100</f>
+        <f>BDP(A27&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F27">
-        <f>BDP(A27,"CPN_FREQ")</f>
+        <f>BDP(A27&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G27">
-        <f>BDP(A27,"DAY_CNT_DES")</f>
+        <f>BDP(A27&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H27">
-        <f>BDP(A27,"MATURITY")</f>
+        <f>BDP(A27&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I27">
-        <f>BDP(A27,"FIRST_CPN_DT")</f>
+        <f>BDP(A27&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="B28">
-        <f>BDP(A28,"SECURITY_DES")</f>
+        <f>BDP(A28&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C28">
-        <f>BDP(A28,"CRNCY")</f>
+        <f>BDP(A28&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D28">
-        <f>BDP(A28,"CNTRY_OF_RISK")</f>
+        <f>BDP(A28&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E28">
-        <f>BDP(A28,"CPN")/100</f>
+        <f>BDP(A28&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F28">
-        <f>BDP(A28,"CPN_FREQ")</f>
+        <f>BDP(A28&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G28">
-        <f>BDP(A28,"DAY_CNT_DES")</f>
+        <f>BDP(A28&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H28">
-        <f>BDP(A28,"MATURITY")</f>
+        <f>BDP(A28&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I28">
-        <f>BDP(A28,"FIRST_CPN_DT")</f>
+        <f>BDP(A28&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="B29">
-        <f>BDP(A29,"SECURITY_DES")</f>
+        <f>BDP(A29&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C29">
-        <f>BDP(A29,"CRNCY")</f>
+        <f>BDP(A29&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D29">
-        <f>BDP(A29,"CNTRY_OF_RISK")</f>
+        <f>BDP(A29&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E29">
-        <f>BDP(A29,"CPN")/100</f>
+        <f>BDP(A29&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F29">
-        <f>BDP(A29,"CPN_FREQ")</f>
+        <f>BDP(A29&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G29">
-        <f>BDP(A29,"DAY_CNT_DES")</f>
+        <f>BDP(A29&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H29">
-        <f>BDP(A29,"MATURITY")</f>
+        <f>BDP(A29&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I29">
-        <f>BDP(A29,"FIRST_CPN_DT")</f>
+        <f>BDP(A29&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="B30">
-        <f>BDP(A30,"SECURITY_DES")</f>
+        <f>BDP(A30&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C30">
-        <f>BDP(A30,"CRNCY")</f>
+        <f>BDP(A30&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D30">
-        <f>BDP(A30,"CNTRY_OF_RISK")</f>
+        <f>BDP(A30&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E30">
-        <f>BDP(A30,"CPN")/100</f>
+        <f>BDP(A30&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F30">
-        <f>BDP(A30,"CPN_FREQ")</f>
+        <f>BDP(A30&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G30">
-        <f>BDP(A30,"DAY_CNT_DES")</f>
+        <f>BDP(A30&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H30">
-        <f>BDP(A30,"MATURITY")</f>
+        <f>BDP(A30&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I30">
-        <f>BDP(A30,"FIRST_CPN_DT")</f>
+        <f>BDP(A30&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="B31">
-        <f>BDP(A31,"SECURITY_DES")</f>
+        <f>BDP(A31&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C31">
-        <f>BDP(A31,"CRNCY")</f>
+        <f>BDP(A31&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D31">
-        <f>BDP(A31,"CNTRY_OF_RISK")</f>
+        <f>BDP(A31&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E31">
-        <f>BDP(A31,"CPN")/100</f>
+        <f>BDP(A31&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F31">
-        <f>BDP(A31,"CPN_FREQ")</f>
+        <f>BDP(A31&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G31">
-        <f>BDP(A31,"DAY_CNT_DES")</f>
+        <f>BDP(A31&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H31">
-        <f>BDP(A31,"MATURITY")</f>
+        <f>BDP(A31&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I31">
-        <f>BDP(A31,"FIRST_CPN_DT")</f>
+        <f>BDP(A31&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="B32">
-        <f>BDP(A32,"SECURITY_DES")</f>
+        <f>BDP(A32&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C32">
-        <f>BDP(A32,"CRNCY")</f>
+        <f>BDP(A32&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D32">
-        <f>BDP(A32,"CNTRY_OF_RISK")</f>
+        <f>BDP(A32&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E32">
-        <f>BDP(A32,"CPN")/100</f>
+        <f>BDP(A32&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F32">
-        <f>BDP(A32,"CPN_FREQ")</f>
+        <f>BDP(A32&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G32">
-        <f>BDP(A32,"DAY_CNT_DES")</f>
+        <f>BDP(A32&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H32">
-        <f>BDP(A32,"MATURITY")</f>
+        <f>BDP(A32&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I32">
-        <f>BDP(A32,"FIRST_CPN_DT")</f>
+        <f>BDP(A32&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="B33">
-        <f>BDP(A33,"SECURITY_DES")</f>
+        <f>BDP(A33&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C33">
-        <f>BDP(A33,"CRNCY")</f>
+        <f>BDP(A33&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D33">
-        <f>BDP(A33,"CNTRY_OF_RISK")</f>
+        <f>BDP(A33&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E33">
-        <f>BDP(A33,"CPN")/100</f>
+        <f>BDP(A33&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F33">
-        <f>BDP(A33,"CPN_FREQ")</f>
+        <f>BDP(A33&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G33">
-        <f>BDP(A33,"DAY_CNT_DES")</f>
+        <f>BDP(A33&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H33">
-        <f>BDP(A33,"MATURITY")</f>
+        <f>BDP(A33&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I33">
-        <f>BDP(A33,"FIRST_CPN_DT")</f>
+        <f>BDP(A33&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="B34">
-        <f>BDP(A34,"SECURITY_DES")</f>
+        <f>BDP(A34&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C34">
-        <f>BDP(A34,"CRNCY")</f>
+        <f>BDP(A34&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D34">
-        <f>BDP(A34,"CNTRY_OF_RISK")</f>
+        <f>BDP(A34&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E34">
-        <f>BDP(A34,"CPN")/100</f>
+        <f>BDP(A34&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F34">
-        <f>BDP(A34,"CPN_FREQ")</f>
+        <f>BDP(A34&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G34">
-        <f>BDP(A34,"DAY_CNT_DES")</f>
+        <f>BDP(A34&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H34">
-        <f>BDP(A34,"MATURITY")</f>
+        <f>BDP(A34&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I34">
-        <f>BDP(A34,"FIRST_CPN_DT")</f>
+        <f>BDP(A34&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="B35">
-        <f>BDP(A35,"SECURITY_DES")</f>
+        <f>BDP(A35&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C35">
-        <f>BDP(A35,"CRNCY")</f>
+        <f>BDP(A35&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D35">
-        <f>BDP(A35,"CNTRY_OF_RISK")</f>
+        <f>BDP(A35&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E35">
-        <f>BDP(A35,"CPN")/100</f>
+        <f>BDP(A35&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F35">
-        <f>BDP(A35,"CPN_FREQ")</f>
+        <f>BDP(A35&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G35">
-        <f>BDP(A35,"DAY_CNT_DES")</f>
+        <f>BDP(A35&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H35">
-        <f>BDP(A35,"MATURITY")</f>
+        <f>BDP(A35&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I35">
-        <f>BDP(A35,"FIRST_CPN_DT")</f>
+        <f>BDP(A35&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="B36">
-        <f>BDP(A36,"SECURITY_DES")</f>
+        <f>BDP(A36&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C36">
-        <f>BDP(A36,"CRNCY")</f>
+        <f>BDP(A36&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D36">
-        <f>BDP(A36,"CNTRY_OF_RISK")</f>
+        <f>BDP(A36&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E36">
-        <f>BDP(A36,"CPN")/100</f>
+        <f>BDP(A36&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F36">
-        <f>BDP(A36,"CPN_FREQ")</f>
+        <f>BDP(A36&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G36">
-        <f>BDP(A36,"DAY_CNT_DES")</f>
+        <f>BDP(A36&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H36">
-        <f>BDP(A36,"MATURITY")</f>
+        <f>BDP(A36&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I36">
-        <f>BDP(A36,"FIRST_CPN_DT")</f>
+        <f>BDP(A36&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="B37">
-        <f>BDP(A37,"SECURITY_DES")</f>
+        <f>BDP(A37&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C37">
-        <f>BDP(A37,"CRNCY")</f>
+        <f>BDP(A37&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D37">
-        <f>BDP(A37,"CNTRY_OF_RISK")</f>
+        <f>BDP(A37&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E37">
-        <f>BDP(A37,"CPN")/100</f>
+        <f>BDP(A37&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F37">
-        <f>BDP(A37,"CPN_FREQ")</f>
+        <f>BDP(A37&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G37">
-        <f>BDP(A37,"DAY_CNT_DES")</f>
+        <f>BDP(A37&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H37">
-        <f>BDP(A37,"MATURITY")</f>
+        <f>BDP(A37&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I37">
-        <f>BDP(A37,"FIRST_CPN_DT")</f>
+        <f>BDP(A37&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="B38">
-        <f>BDP(A38,"SECURITY_DES")</f>
+        <f>BDP(A38&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C38">
-        <f>BDP(A38,"CRNCY")</f>
+        <f>BDP(A38&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D38">
-        <f>BDP(A38,"CNTRY_OF_RISK")</f>
+        <f>BDP(A38&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E38">
-        <f>BDP(A38,"CPN")/100</f>
+        <f>BDP(A38&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F38">
-        <f>BDP(A38,"CPN_FREQ")</f>
+        <f>BDP(A38&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G38">
-        <f>BDP(A38,"DAY_CNT_DES")</f>
+        <f>BDP(A38&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H38">
-        <f>BDP(A38,"MATURITY")</f>
+        <f>BDP(A38&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I38">
-        <f>BDP(A38,"FIRST_CPN_DT")</f>
+        <f>BDP(A38&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="B39">
-        <f>BDP(A39,"SECURITY_DES")</f>
+        <f>BDP(A39&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C39">
-        <f>BDP(A39,"CRNCY")</f>
+        <f>BDP(A39&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D39">
-        <f>BDP(A39,"CNTRY_OF_RISK")</f>
+        <f>BDP(A39&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E39">
-        <f>BDP(A39,"CPN")/100</f>
+        <f>BDP(A39&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F39">
-        <f>BDP(A39,"CPN_FREQ")</f>
+        <f>BDP(A39&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G39">
-        <f>BDP(A39,"DAY_CNT_DES")</f>
+        <f>BDP(A39&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H39">
-        <f>BDP(A39,"MATURITY")</f>
+        <f>BDP(A39&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I39">
-        <f>BDP(A39,"FIRST_CPN_DT")</f>
+        <f>BDP(A39&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="B40">
-        <f>BDP(A40,"SECURITY_DES")</f>
+        <f>BDP(A40&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C40">
-        <f>BDP(A40,"CRNCY")</f>
+        <f>BDP(A40&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D40">
-        <f>BDP(A40,"CNTRY_OF_RISK")</f>
+        <f>BDP(A40&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E40">
-        <f>BDP(A40,"CPN")/100</f>
+        <f>BDP(A40&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F40">
-        <f>BDP(A40,"CPN_FREQ")</f>
+        <f>BDP(A40&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G40">
-        <f>BDP(A40,"DAY_CNT_DES")</f>
+        <f>BDP(A40&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H40">
-        <f>BDP(A40,"MATURITY")</f>
+        <f>BDP(A40&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I40">
-        <f>BDP(A40,"FIRST_CPN_DT")</f>
+        <f>BDP(A40&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="B41">
-        <f>BDP(A41,"SECURITY_DES")</f>
+        <f>BDP(A41&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C41">
-        <f>BDP(A41,"CRNCY")</f>
+        <f>BDP(A41&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D41">
-        <f>BDP(A41,"CNTRY_OF_RISK")</f>
+        <f>BDP(A41&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E41">
-        <f>BDP(A41,"CPN")/100</f>
+        <f>BDP(A41&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F41">
-        <f>BDP(A41,"CPN_FREQ")</f>
+        <f>BDP(A41&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G41">
-        <f>BDP(A41,"DAY_CNT_DES")</f>
+        <f>BDP(A41&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H41">
-        <f>BDP(A41,"MATURITY")</f>
+        <f>BDP(A41&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I41">
-        <f>BDP(A41,"FIRST_CPN_DT")</f>
+        <f>BDP(A41&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42">
-        <f>BDP(A42,"SECURITY_DES")</f>
+        <f>BDP(A42&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C42">
-        <f>BDP(A42,"CRNCY")</f>
+        <f>BDP(A42&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D42">
-        <f>BDP(A42,"CNTRY_OF_RISK")</f>
+        <f>BDP(A42&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E42">
-        <f>BDP(A42,"CPN")/100</f>
+        <f>BDP(A42&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F42">
-        <f>BDP(A42,"CPN_FREQ")</f>
+        <f>BDP(A42&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G42">
-        <f>BDP(A42,"DAY_CNT_DES")</f>
+        <f>BDP(A42&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H42">
-        <f>BDP(A42,"MATURITY")</f>
+        <f>BDP(A42&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I42">
-        <f>BDP(A42,"FIRST_CPN_DT")</f>
+        <f>BDP(A42&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43">
-        <f>BDP(A43,"SECURITY_DES")</f>
+        <f>BDP(A43&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C43">
-        <f>BDP(A43,"CRNCY")</f>
+        <f>BDP(A43&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D43">
-        <f>BDP(A43,"CNTRY_OF_RISK")</f>
+        <f>BDP(A43&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E43">
-        <f>BDP(A43,"CPN")/100</f>
+        <f>BDP(A43&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F43">
-        <f>BDP(A43,"CPN_FREQ")</f>
+        <f>BDP(A43&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G43">
-        <f>BDP(A43,"DAY_CNT_DES")</f>
+        <f>BDP(A43&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H43">
-        <f>BDP(A43,"MATURITY")</f>
+        <f>BDP(A43&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I43">
-        <f>BDP(A43,"FIRST_CPN_DT")</f>
+        <f>BDP(A43&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44">
-        <f>BDP(A44,"SECURITY_DES")</f>
+        <f>BDP(A44&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C44">
-        <f>BDP(A44,"CRNCY")</f>
+        <f>BDP(A44&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D44">
-        <f>BDP(A44,"CNTRY_OF_RISK")</f>
+        <f>BDP(A44&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E44">
-        <f>BDP(A44,"CPN")/100</f>
+        <f>BDP(A44&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F44">
-        <f>BDP(A44,"CPN_FREQ")</f>
+        <f>BDP(A44&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G44">
-        <f>BDP(A44,"DAY_CNT_DES")</f>
+        <f>BDP(A44&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H44">
-        <f>BDP(A44,"MATURITY")</f>
+        <f>BDP(A44&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I44">
-        <f>BDP(A44,"FIRST_CPN_DT")</f>
+        <f>BDP(A44&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45">
-        <f>BDP(A45,"SECURITY_DES")</f>
+        <f>BDP(A45&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C45">
-        <f>BDP(A45,"CRNCY")</f>
+        <f>BDP(A45&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D45">
-        <f>BDP(A45,"CNTRY_OF_RISK")</f>
+        <f>BDP(A45&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E45">
-        <f>BDP(A45,"CPN")/100</f>
+        <f>BDP(A45&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F45">
-        <f>BDP(A45,"CPN_FREQ")</f>
+        <f>BDP(A45&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G45">
-        <f>BDP(A45,"DAY_CNT_DES")</f>
+        <f>BDP(A45&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H45">
-        <f>BDP(A45,"MATURITY")</f>
+        <f>BDP(A45&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I45">
-        <f>BDP(A45,"FIRST_CPN_DT")</f>
+        <f>BDP(A45&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46">
-        <f>BDP(A46,"SECURITY_DES")</f>
+        <f>BDP(A46&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C46">
-        <f>BDP(A46,"CRNCY")</f>
+        <f>BDP(A46&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D46">
-        <f>BDP(A46,"CNTRY_OF_RISK")</f>
+        <f>BDP(A46&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E46">
-        <f>BDP(A46,"CPN")/100</f>
+        <f>BDP(A46&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F46">
-        <f>BDP(A46,"CPN_FREQ")</f>
+        <f>BDP(A46&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G46">
-        <f>BDP(A46,"DAY_CNT_DES")</f>
+        <f>BDP(A46&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H46">
-        <f>BDP(A46,"MATURITY")</f>
+        <f>BDP(A46&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I46">
-        <f>BDP(A46,"FIRST_CPN_DT")</f>
+        <f>BDP(A46&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="B47">
-        <f>BDP(A47,"SECURITY_DES")</f>
+        <f>BDP(A47&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C47">
-        <f>BDP(A47,"CRNCY")</f>
+        <f>BDP(A47&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D47">
-        <f>BDP(A47,"CNTRY_OF_RISK")</f>
+        <f>BDP(A47&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E47">
-        <f>BDP(A47,"CPN")/100</f>
+        <f>BDP(A47&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F47">
-        <f>BDP(A47,"CPN_FREQ")</f>
+        <f>BDP(A47&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G47">
-        <f>BDP(A47,"DAY_CNT_DES")</f>
+        <f>BDP(A47&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H47">
-        <f>BDP(A47,"MATURITY")</f>
+        <f>BDP(A47&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I47">
-        <f>BDP(A47,"FIRST_CPN_DT")</f>
+        <f>BDP(A47&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="B48">
-        <f>BDP(A48,"SECURITY_DES")</f>
+        <f>BDP(A48&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C48">
-        <f>BDP(A48,"CRNCY")</f>
+        <f>BDP(A48&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D48">
-        <f>BDP(A48,"CNTRY_OF_RISK")</f>
+        <f>BDP(A48&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E48">
-        <f>BDP(A48,"CPN")/100</f>
+        <f>BDP(A48&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F48">
-        <f>BDP(A48,"CPN_FREQ")</f>
+        <f>BDP(A48&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G48">
-        <f>BDP(A48,"DAY_CNT_DES")</f>
+        <f>BDP(A48&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H48">
-        <f>BDP(A48,"MATURITY")</f>
+        <f>BDP(A48&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I48">
-        <f>BDP(A48,"FIRST_CPN_DT")</f>
+        <f>BDP(A48&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="B49">
-        <f>BDP(A49,"SECURITY_DES")</f>
+        <f>BDP(A49&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C49">
-        <f>BDP(A49,"CRNCY")</f>
+        <f>BDP(A49&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D49">
-        <f>BDP(A49,"CNTRY_OF_RISK")</f>
+        <f>BDP(A49&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E49">
-        <f>BDP(A49,"CPN")/100</f>
+        <f>BDP(A49&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F49">
-        <f>BDP(A49,"CPN_FREQ")</f>
+        <f>BDP(A49&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G49">
-        <f>BDP(A49,"DAY_CNT_DES")</f>
+        <f>BDP(A49&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H49">
-        <f>BDP(A49,"MATURITY")</f>
+        <f>BDP(A49&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I49">
-        <f>BDP(A49,"FIRST_CPN_DT")</f>
+        <f>BDP(A49&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="B50">
-        <f>BDP(A50,"SECURITY_DES")</f>
+        <f>BDP(A50&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C50">
-        <f>BDP(A50,"CRNCY")</f>
+        <f>BDP(A50&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D50">
-        <f>BDP(A50,"CNTRY_OF_RISK")</f>
+        <f>BDP(A50&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E50">
-        <f>BDP(A50,"CPN")/100</f>
+        <f>BDP(A50&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F50">
-        <f>BDP(A50,"CPN_FREQ")</f>
+        <f>BDP(A50&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G50">
-        <f>BDP(A50,"DAY_CNT_DES")</f>
+        <f>BDP(A50&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H50">
-        <f>BDP(A50,"MATURITY")</f>
+        <f>BDP(A50&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I50">
-        <f>BDP(A50,"FIRST_CPN_DT")</f>
+        <f>BDP(A50&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="B51">
-        <f>BDP(A51,"SECURITY_DES")</f>
+        <f>BDP(A51&amp;" Corp","SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C51">
-        <f>BDP(A51,"CRNCY")</f>
+        <f>BDP(A51&amp;" Corp","CRNCY")</f>
         <v/>
       </c>
       <c r="D51">
-        <f>BDP(A51,"CNTRY_OF_RISK")</f>
+        <f>BDP(A51&amp;" Corp","CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E51">
-        <f>BDP(A51,"CPN")/100</f>
+        <f>BDP(A51&amp;" Corp","CPN")/100</f>
         <v/>
       </c>
       <c r="F51">
-        <f>BDP(A51,"CPN_FREQ")</f>
+        <f>BDP(A51&amp;" Corp","CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G51">
-        <f>BDP(A51,"DAY_CNT_DES")</f>
+        <f>BDP(A51&amp;" Corp","DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H51">
-        <f>BDP(A51,"MATURITY")</f>
+        <f>BDP(A51&amp;" Corp","MATURITY")</f>
         <v/>
       </c>
       <c r="I51">
-        <f>BDP(A51,"FIRST_CPN_DT")</f>
+        <f>BDP(A51&amp;" Corp","FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
@@ -2946,29 +2951,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BBG Ticker</t>
+          <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Start (YYYYMMDD)</t>
+          <t>PX_LAST</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>End (YYYYMMDD)</t>
+          <t>End</t>
         </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3">
+        <f>BDH(A1,"PX_LAST",B1,C1,"Fill","0","Dates","1")</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/projects/02-pnl-dashboard/templates/bloomberg_prices.xlsx
+++ b/projects/02-pnl-dashboard/templates/bloomberg_prices.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Live MTM" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Static" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="History" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,10 +33,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00555555"/>
     </font>
   </fonts>
   <fills count="3">
@@ -65,13 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +435,7 @@
   <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -449,7 +444,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CUSIP</t>
+          <t>BBG Ticker</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -470,701 +465,701 @@
     </row>
     <row r="2">
       <c r="B2">
-        <f>BDP(A2&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A2,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C2">
-        <f>BDP(A2&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A2,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D2">
-        <f>BDP(A2&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A2,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="B3">
-        <f>BDP(A3&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A3,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C3">
-        <f>BDP(A3&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A3,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D3">
-        <f>BDP(A3&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A3,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="B4">
-        <f>BDP(A4&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A4,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C4">
-        <f>BDP(A4&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A4,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D4">
-        <f>BDP(A4&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A4,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="B5">
-        <f>BDP(A5&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A5,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C5">
-        <f>BDP(A5&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A5,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D5">
-        <f>BDP(A5&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A5,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="B6">
-        <f>BDP(A6&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A6,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C6">
-        <f>BDP(A6&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A6,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D6">
-        <f>BDP(A6&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A6,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="B7">
-        <f>BDP(A7&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A7,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C7">
-        <f>BDP(A7&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A7,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D7">
-        <f>BDP(A7&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A7,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="B8">
-        <f>BDP(A8&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A8,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C8">
-        <f>BDP(A8&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A8,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D8">
-        <f>BDP(A8&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A8,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="B9">
-        <f>BDP(A9&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A9,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C9">
-        <f>BDP(A9&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A9,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D9">
-        <f>BDP(A9&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A9,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="B10">
-        <f>BDP(A10&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A10,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C10">
-        <f>BDP(A10&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A10,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D10">
-        <f>BDP(A10&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A10,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="B11">
-        <f>BDP(A11&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A11,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C11">
-        <f>BDP(A11&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A11,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D11">
-        <f>BDP(A11&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A11,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="B12">
-        <f>BDP(A12&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A12,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C12">
-        <f>BDP(A12&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A12,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D12">
-        <f>BDP(A12&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A12,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="B13">
-        <f>BDP(A13&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A13,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C13">
-        <f>BDP(A13&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A13,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D13">
-        <f>BDP(A13&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A13,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="B14">
-        <f>BDP(A14&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A14,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C14">
-        <f>BDP(A14&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A14,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D14">
-        <f>BDP(A14&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A14,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="B15">
-        <f>BDP(A15&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A15,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C15">
-        <f>BDP(A15&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A15,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D15">
-        <f>BDP(A15&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A15,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="B16">
-        <f>BDP(A16&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A16,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C16">
-        <f>BDP(A16&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A16,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D16">
-        <f>BDP(A16&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A16,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="B17">
-        <f>BDP(A17&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A17,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C17">
-        <f>BDP(A17&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A17,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D17">
-        <f>BDP(A17&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A17,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="B18">
-        <f>BDP(A18&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A18,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C18">
-        <f>BDP(A18&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A18,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D18">
-        <f>BDP(A18&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A18,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="B19">
-        <f>BDP(A19&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A19,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C19">
-        <f>BDP(A19&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A19,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D19">
-        <f>BDP(A19&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A19,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="B20">
-        <f>BDP(A20&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A20,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C20">
-        <f>BDP(A20&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A20,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D20">
-        <f>BDP(A20&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A20,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="B21">
-        <f>BDP(A21&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A21,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C21">
-        <f>BDP(A21&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A21,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D21">
-        <f>BDP(A21&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A21,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="B22">
-        <f>BDP(A22&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A22,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C22">
-        <f>BDP(A22&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A22,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D22">
-        <f>BDP(A22&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A22,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23">
-        <f>BDP(A23&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A23,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C23">
-        <f>BDP(A23&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A23,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D23">
-        <f>BDP(A23&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A23,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24">
-        <f>BDP(A24&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A24,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C24">
-        <f>BDP(A24&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A24,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D24">
-        <f>BDP(A24&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A24,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="B25">
-        <f>BDP(A25&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A25,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C25">
-        <f>BDP(A25&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A25,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D25">
-        <f>BDP(A25&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A25,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="B26">
-        <f>BDP(A26&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A26,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C26">
-        <f>BDP(A26&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A26,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D26">
-        <f>BDP(A26&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A26,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="B27">
-        <f>BDP(A27&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A27,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C27">
-        <f>BDP(A27&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A27,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D27">
-        <f>BDP(A27&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A27,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="B28">
-        <f>BDP(A28&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A28,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C28">
-        <f>BDP(A28&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A28,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D28">
-        <f>BDP(A28&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A28,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="B29">
-        <f>BDP(A29&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A29,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C29">
-        <f>BDP(A29&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A29,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D29">
-        <f>BDP(A29&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A29,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="B30">
-        <f>BDP(A30&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A30,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C30">
-        <f>BDP(A30&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A30,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D30">
-        <f>BDP(A30&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A30,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="B31">
-        <f>BDP(A31&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A31,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C31">
-        <f>BDP(A31&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A31,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D31">
-        <f>BDP(A31&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A31,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="B32">
-        <f>BDP(A32&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A32,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C32">
-        <f>BDP(A32&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A32,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D32">
-        <f>BDP(A32&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A32,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="B33">
-        <f>BDP(A33&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A33,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C33">
-        <f>BDP(A33&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A33,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D33">
-        <f>BDP(A33&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A33,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="B34">
-        <f>BDP(A34&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A34,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C34">
-        <f>BDP(A34&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A34,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D34">
-        <f>BDP(A34&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A34,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="B35">
-        <f>BDP(A35&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A35,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C35">
-        <f>BDP(A35&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A35,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D35">
-        <f>BDP(A35&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A35,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="B36">
-        <f>BDP(A36&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A36,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C36">
-        <f>BDP(A36&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A36,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D36">
-        <f>BDP(A36&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A36,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="B37">
-        <f>BDP(A37&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A37,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C37">
-        <f>BDP(A37&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A37,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D37">
-        <f>BDP(A37&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A37,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="B38">
-        <f>BDP(A38&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A38,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C38">
-        <f>BDP(A38&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A38,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D38">
-        <f>BDP(A38&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A38,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="B39">
-        <f>BDP(A39&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A39,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C39">
-        <f>BDP(A39&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A39,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D39">
-        <f>BDP(A39&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A39,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="B40">
-        <f>BDP(A40&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A40,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C40">
-        <f>BDP(A40&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A40,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D40">
-        <f>BDP(A40&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A40,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="B41">
-        <f>BDP(A41&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A41,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C41">
-        <f>BDP(A41&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A41,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D41">
-        <f>BDP(A41&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A41,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42">
-        <f>BDP(A42&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A42,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C42">
-        <f>BDP(A42&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A42,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D42">
-        <f>BDP(A42&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A42,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43">
-        <f>BDP(A43&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A43,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C43">
-        <f>BDP(A43&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A43,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D43">
-        <f>BDP(A43&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A43,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44">
-        <f>BDP(A44&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A44,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C44">
-        <f>BDP(A44&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A44,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D44">
-        <f>BDP(A44&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A44,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45">
-        <f>BDP(A45&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A45,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C45">
-        <f>BDP(A45&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A45,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D45">
-        <f>BDP(A45&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A45,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46">
-        <f>BDP(A46&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A46,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C46">
-        <f>BDP(A46&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A46,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D46">
-        <f>BDP(A46&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A46,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="B47">
-        <f>BDP(A47&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A47,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C47">
-        <f>BDP(A47&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A47,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D47">
-        <f>BDP(A47&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A47,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="B48">
-        <f>BDP(A48&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A48,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C48">
-        <f>BDP(A48&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A48,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D48">
-        <f>BDP(A48&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A48,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="B49">
-        <f>BDP(A49&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A49,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C49">
-        <f>BDP(A49&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A49,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D49">
-        <f>BDP(A49&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A49,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="B50">
-        <f>BDP(A50&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A50,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C50">
-        <f>BDP(A50&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A50,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D50">
-        <f>BDP(A50&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A50,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="B51">
-        <f>BDP(A51&amp;" Corp","PX_LAST")</f>
+        <f>BDP(A51,"PX_LAST")</f>
         <v/>
       </c>
       <c r="C51">
-        <f>BDP(A51&amp;" Corp","YAS_ASW_SPREAD")</f>
+        <f>BDP(A51,"YAS_ASW_SPREAD")</f>
         <v/>
       </c>
       <c r="D51">
-        <f>BDP(A51&amp;" Corp","YLD_YTM_MID")</f>
+        <f>BDP(A51,"YLD_YTM_MID")</f>
         <v/>
       </c>
     </row>
@@ -1182,7 +1177,7 @@
   <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -1196,7 +1191,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>cusip</t>
+          <t>bbg_ticker</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1242,1701 +1237,1701 @@
     </row>
     <row r="2">
       <c r="B2">
-        <f>BDP(A2&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A2,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C2">
-        <f>BDP(A2&amp;" Corp","CRNCY")</f>
+        <f>BDP(A2,"CRNCY")</f>
         <v/>
       </c>
       <c r="D2">
-        <f>BDP(A2&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A2,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E2">
-        <f>BDP(A2&amp;" Corp","CPN")/100</f>
+        <f>BDP(A2,"CPN")/100</f>
         <v/>
       </c>
       <c r="F2">
-        <f>BDP(A2&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A2,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G2">
-        <f>BDP(A2&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A2,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H2">
-        <f>BDP(A2&amp;" Corp","MATURITY")</f>
+        <f>BDP(A2,"MATURITY")</f>
         <v/>
       </c>
       <c r="I2">
-        <f>BDP(A2&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A2,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="B3">
-        <f>BDP(A3&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A3,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C3">
-        <f>BDP(A3&amp;" Corp","CRNCY")</f>
+        <f>BDP(A3,"CRNCY")</f>
         <v/>
       </c>
       <c r="D3">
-        <f>BDP(A3&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A3,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E3">
-        <f>BDP(A3&amp;" Corp","CPN")/100</f>
+        <f>BDP(A3,"CPN")/100</f>
         <v/>
       </c>
       <c r="F3">
-        <f>BDP(A3&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A3,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G3">
-        <f>BDP(A3&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A3,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H3">
-        <f>BDP(A3&amp;" Corp","MATURITY")</f>
+        <f>BDP(A3,"MATURITY")</f>
         <v/>
       </c>
       <c r="I3">
-        <f>BDP(A3&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A3,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="B4">
-        <f>BDP(A4&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A4,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C4">
-        <f>BDP(A4&amp;" Corp","CRNCY")</f>
+        <f>BDP(A4,"CRNCY")</f>
         <v/>
       </c>
       <c r="D4">
-        <f>BDP(A4&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A4,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E4">
-        <f>BDP(A4&amp;" Corp","CPN")/100</f>
+        <f>BDP(A4,"CPN")/100</f>
         <v/>
       </c>
       <c r="F4">
-        <f>BDP(A4&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A4,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G4">
-        <f>BDP(A4&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A4,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H4">
-        <f>BDP(A4&amp;" Corp","MATURITY")</f>
+        <f>BDP(A4,"MATURITY")</f>
         <v/>
       </c>
       <c r="I4">
-        <f>BDP(A4&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A4,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="B5">
-        <f>BDP(A5&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A5,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C5">
-        <f>BDP(A5&amp;" Corp","CRNCY")</f>
+        <f>BDP(A5,"CRNCY")</f>
         <v/>
       </c>
       <c r="D5">
-        <f>BDP(A5&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A5,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E5">
-        <f>BDP(A5&amp;" Corp","CPN")/100</f>
+        <f>BDP(A5,"CPN")/100</f>
         <v/>
       </c>
       <c r="F5">
-        <f>BDP(A5&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A5,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G5">
-        <f>BDP(A5&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A5,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H5">
-        <f>BDP(A5&amp;" Corp","MATURITY")</f>
+        <f>BDP(A5,"MATURITY")</f>
         <v/>
       </c>
       <c r="I5">
-        <f>BDP(A5&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A5,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="B6">
-        <f>BDP(A6&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A6,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C6">
-        <f>BDP(A6&amp;" Corp","CRNCY")</f>
+        <f>BDP(A6,"CRNCY")</f>
         <v/>
       </c>
       <c r="D6">
-        <f>BDP(A6&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A6,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E6">
-        <f>BDP(A6&amp;" Corp","CPN")/100</f>
+        <f>BDP(A6,"CPN")/100</f>
         <v/>
       </c>
       <c r="F6">
-        <f>BDP(A6&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A6,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G6">
-        <f>BDP(A6&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A6,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H6">
-        <f>BDP(A6&amp;" Corp","MATURITY")</f>
+        <f>BDP(A6,"MATURITY")</f>
         <v/>
       </c>
       <c r="I6">
-        <f>BDP(A6&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A6,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="B7">
-        <f>BDP(A7&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A7,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C7">
-        <f>BDP(A7&amp;" Corp","CRNCY")</f>
+        <f>BDP(A7,"CRNCY")</f>
         <v/>
       </c>
       <c r="D7">
-        <f>BDP(A7&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A7,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E7">
-        <f>BDP(A7&amp;" Corp","CPN")/100</f>
+        <f>BDP(A7,"CPN")/100</f>
         <v/>
       </c>
       <c r="F7">
-        <f>BDP(A7&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A7,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G7">
-        <f>BDP(A7&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A7,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H7">
-        <f>BDP(A7&amp;" Corp","MATURITY")</f>
+        <f>BDP(A7,"MATURITY")</f>
         <v/>
       </c>
       <c r="I7">
-        <f>BDP(A7&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A7,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="B8">
-        <f>BDP(A8&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A8,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C8">
-        <f>BDP(A8&amp;" Corp","CRNCY")</f>
+        <f>BDP(A8,"CRNCY")</f>
         <v/>
       </c>
       <c r="D8">
-        <f>BDP(A8&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A8,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E8">
-        <f>BDP(A8&amp;" Corp","CPN")/100</f>
+        <f>BDP(A8,"CPN")/100</f>
         <v/>
       </c>
       <c r="F8">
-        <f>BDP(A8&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A8,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G8">
-        <f>BDP(A8&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A8,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H8">
-        <f>BDP(A8&amp;" Corp","MATURITY")</f>
+        <f>BDP(A8,"MATURITY")</f>
         <v/>
       </c>
       <c r="I8">
-        <f>BDP(A8&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A8,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="B9">
-        <f>BDP(A9&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A9,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C9">
-        <f>BDP(A9&amp;" Corp","CRNCY")</f>
+        <f>BDP(A9,"CRNCY")</f>
         <v/>
       </c>
       <c r="D9">
-        <f>BDP(A9&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A9,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E9">
-        <f>BDP(A9&amp;" Corp","CPN")/100</f>
+        <f>BDP(A9,"CPN")/100</f>
         <v/>
       </c>
       <c r="F9">
-        <f>BDP(A9&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A9,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G9">
-        <f>BDP(A9&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A9,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H9">
-        <f>BDP(A9&amp;" Corp","MATURITY")</f>
+        <f>BDP(A9,"MATURITY")</f>
         <v/>
       </c>
       <c r="I9">
-        <f>BDP(A9&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A9,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="B10">
-        <f>BDP(A10&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A10,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C10">
-        <f>BDP(A10&amp;" Corp","CRNCY")</f>
+        <f>BDP(A10,"CRNCY")</f>
         <v/>
       </c>
       <c r="D10">
-        <f>BDP(A10&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A10,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E10">
-        <f>BDP(A10&amp;" Corp","CPN")/100</f>
+        <f>BDP(A10,"CPN")/100</f>
         <v/>
       </c>
       <c r="F10">
-        <f>BDP(A10&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A10,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G10">
-        <f>BDP(A10&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A10,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H10">
-        <f>BDP(A10&amp;" Corp","MATURITY")</f>
+        <f>BDP(A10,"MATURITY")</f>
         <v/>
       </c>
       <c r="I10">
-        <f>BDP(A10&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A10,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="B11">
-        <f>BDP(A11&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A11,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C11">
-        <f>BDP(A11&amp;" Corp","CRNCY")</f>
+        <f>BDP(A11,"CRNCY")</f>
         <v/>
       </c>
       <c r="D11">
-        <f>BDP(A11&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A11,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E11">
-        <f>BDP(A11&amp;" Corp","CPN")/100</f>
+        <f>BDP(A11,"CPN")/100</f>
         <v/>
       </c>
       <c r="F11">
-        <f>BDP(A11&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A11,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G11">
-        <f>BDP(A11&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A11,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H11">
-        <f>BDP(A11&amp;" Corp","MATURITY")</f>
+        <f>BDP(A11,"MATURITY")</f>
         <v/>
       </c>
       <c r="I11">
-        <f>BDP(A11&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A11,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="B12">
-        <f>BDP(A12&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A12,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C12">
-        <f>BDP(A12&amp;" Corp","CRNCY")</f>
+        <f>BDP(A12,"CRNCY")</f>
         <v/>
       </c>
       <c r="D12">
-        <f>BDP(A12&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A12,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E12">
-        <f>BDP(A12&amp;" Corp","CPN")/100</f>
+        <f>BDP(A12,"CPN")/100</f>
         <v/>
       </c>
       <c r="F12">
-        <f>BDP(A12&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A12,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G12">
-        <f>BDP(A12&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A12,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H12">
-        <f>BDP(A12&amp;" Corp","MATURITY")</f>
+        <f>BDP(A12,"MATURITY")</f>
         <v/>
       </c>
       <c r="I12">
-        <f>BDP(A12&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A12,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="B13">
-        <f>BDP(A13&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A13,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C13">
-        <f>BDP(A13&amp;" Corp","CRNCY")</f>
+        <f>BDP(A13,"CRNCY")</f>
         <v/>
       </c>
       <c r="D13">
-        <f>BDP(A13&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A13,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E13">
-        <f>BDP(A13&amp;" Corp","CPN")/100</f>
+        <f>BDP(A13,"CPN")/100</f>
         <v/>
       </c>
       <c r="F13">
-        <f>BDP(A13&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A13,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G13">
-        <f>BDP(A13&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A13,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H13">
-        <f>BDP(A13&amp;" Corp","MATURITY")</f>
+        <f>BDP(A13,"MATURITY")</f>
         <v/>
       </c>
       <c r="I13">
-        <f>BDP(A13&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A13,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="B14">
-        <f>BDP(A14&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A14,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C14">
-        <f>BDP(A14&amp;" Corp","CRNCY")</f>
+        <f>BDP(A14,"CRNCY")</f>
         <v/>
       </c>
       <c r="D14">
-        <f>BDP(A14&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A14,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E14">
-        <f>BDP(A14&amp;" Corp","CPN")/100</f>
+        <f>BDP(A14,"CPN")/100</f>
         <v/>
       </c>
       <c r="F14">
-        <f>BDP(A14&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A14,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G14">
-        <f>BDP(A14&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A14,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H14">
-        <f>BDP(A14&amp;" Corp","MATURITY")</f>
+        <f>BDP(A14,"MATURITY")</f>
         <v/>
       </c>
       <c r="I14">
-        <f>BDP(A14&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A14,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="B15">
-        <f>BDP(A15&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A15,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C15">
-        <f>BDP(A15&amp;" Corp","CRNCY")</f>
+        <f>BDP(A15,"CRNCY")</f>
         <v/>
       </c>
       <c r="D15">
-        <f>BDP(A15&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A15,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E15">
-        <f>BDP(A15&amp;" Corp","CPN")/100</f>
+        <f>BDP(A15,"CPN")/100</f>
         <v/>
       </c>
       <c r="F15">
-        <f>BDP(A15&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A15,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G15">
-        <f>BDP(A15&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A15,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H15">
-        <f>BDP(A15&amp;" Corp","MATURITY")</f>
+        <f>BDP(A15,"MATURITY")</f>
         <v/>
       </c>
       <c r="I15">
-        <f>BDP(A15&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A15,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="B16">
-        <f>BDP(A16&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A16,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C16">
-        <f>BDP(A16&amp;" Corp","CRNCY")</f>
+        <f>BDP(A16,"CRNCY")</f>
         <v/>
       </c>
       <c r="D16">
-        <f>BDP(A16&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A16,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E16">
-        <f>BDP(A16&amp;" Corp","CPN")/100</f>
+        <f>BDP(A16,"CPN")/100</f>
         <v/>
       </c>
       <c r="F16">
-        <f>BDP(A16&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A16,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G16">
-        <f>BDP(A16&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A16,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H16">
-        <f>BDP(A16&amp;" Corp","MATURITY")</f>
+        <f>BDP(A16,"MATURITY")</f>
         <v/>
       </c>
       <c r="I16">
-        <f>BDP(A16&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A16,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="B17">
-        <f>BDP(A17&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A17,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C17">
-        <f>BDP(A17&amp;" Corp","CRNCY")</f>
+        <f>BDP(A17,"CRNCY")</f>
         <v/>
       </c>
       <c r="D17">
-        <f>BDP(A17&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A17,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E17">
-        <f>BDP(A17&amp;" Corp","CPN")/100</f>
+        <f>BDP(A17,"CPN")/100</f>
         <v/>
       </c>
       <c r="F17">
-        <f>BDP(A17&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A17,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G17">
-        <f>BDP(A17&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A17,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H17">
-        <f>BDP(A17&amp;" Corp","MATURITY")</f>
+        <f>BDP(A17,"MATURITY")</f>
         <v/>
       </c>
       <c r="I17">
-        <f>BDP(A17&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A17,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="B18">
-        <f>BDP(A18&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A18,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C18">
-        <f>BDP(A18&amp;" Corp","CRNCY")</f>
+        <f>BDP(A18,"CRNCY")</f>
         <v/>
       </c>
       <c r="D18">
-        <f>BDP(A18&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A18,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E18">
-        <f>BDP(A18&amp;" Corp","CPN")/100</f>
+        <f>BDP(A18,"CPN")/100</f>
         <v/>
       </c>
       <c r="F18">
-        <f>BDP(A18&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A18,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G18">
-        <f>BDP(A18&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A18,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H18">
-        <f>BDP(A18&amp;" Corp","MATURITY")</f>
+        <f>BDP(A18,"MATURITY")</f>
         <v/>
       </c>
       <c r="I18">
-        <f>BDP(A18&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A18,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="B19">
-        <f>BDP(A19&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A19,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C19">
-        <f>BDP(A19&amp;" Corp","CRNCY")</f>
+        <f>BDP(A19,"CRNCY")</f>
         <v/>
       </c>
       <c r="D19">
-        <f>BDP(A19&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A19,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E19">
-        <f>BDP(A19&amp;" Corp","CPN")/100</f>
+        <f>BDP(A19,"CPN")/100</f>
         <v/>
       </c>
       <c r="F19">
-        <f>BDP(A19&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A19,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G19">
-        <f>BDP(A19&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A19,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H19">
-        <f>BDP(A19&amp;" Corp","MATURITY")</f>
+        <f>BDP(A19,"MATURITY")</f>
         <v/>
       </c>
       <c r="I19">
-        <f>BDP(A19&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A19,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="B20">
-        <f>BDP(A20&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A20,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C20">
-        <f>BDP(A20&amp;" Corp","CRNCY")</f>
+        <f>BDP(A20,"CRNCY")</f>
         <v/>
       </c>
       <c r="D20">
-        <f>BDP(A20&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A20,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E20">
-        <f>BDP(A20&amp;" Corp","CPN")/100</f>
+        <f>BDP(A20,"CPN")/100</f>
         <v/>
       </c>
       <c r="F20">
-        <f>BDP(A20&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A20,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G20">
-        <f>BDP(A20&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A20,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H20">
-        <f>BDP(A20&amp;" Corp","MATURITY")</f>
+        <f>BDP(A20,"MATURITY")</f>
         <v/>
       </c>
       <c r="I20">
-        <f>BDP(A20&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A20,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="B21">
-        <f>BDP(A21&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A21,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C21">
-        <f>BDP(A21&amp;" Corp","CRNCY")</f>
+        <f>BDP(A21,"CRNCY")</f>
         <v/>
       </c>
       <c r="D21">
-        <f>BDP(A21&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A21,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E21">
-        <f>BDP(A21&amp;" Corp","CPN")/100</f>
+        <f>BDP(A21,"CPN")/100</f>
         <v/>
       </c>
       <c r="F21">
-        <f>BDP(A21&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A21,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G21">
-        <f>BDP(A21&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A21,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H21">
-        <f>BDP(A21&amp;" Corp","MATURITY")</f>
+        <f>BDP(A21,"MATURITY")</f>
         <v/>
       </c>
       <c r="I21">
-        <f>BDP(A21&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A21,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="B22">
-        <f>BDP(A22&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A22,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C22">
-        <f>BDP(A22&amp;" Corp","CRNCY")</f>
+        <f>BDP(A22,"CRNCY")</f>
         <v/>
       </c>
       <c r="D22">
-        <f>BDP(A22&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A22,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E22">
-        <f>BDP(A22&amp;" Corp","CPN")/100</f>
+        <f>BDP(A22,"CPN")/100</f>
         <v/>
       </c>
       <c r="F22">
-        <f>BDP(A22&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A22,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G22">
-        <f>BDP(A22&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A22,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H22">
-        <f>BDP(A22&amp;" Corp","MATURITY")</f>
+        <f>BDP(A22,"MATURITY")</f>
         <v/>
       </c>
       <c r="I22">
-        <f>BDP(A22&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A22,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23">
-        <f>BDP(A23&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A23,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C23">
-        <f>BDP(A23&amp;" Corp","CRNCY")</f>
+        <f>BDP(A23,"CRNCY")</f>
         <v/>
       </c>
       <c r="D23">
-        <f>BDP(A23&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A23,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E23">
-        <f>BDP(A23&amp;" Corp","CPN")/100</f>
+        <f>BDP(A23,"CPN")/100</f>
         <v/>
       </c>
       <c r="F23">
-        <f>BDP(A23&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A23,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G23">
-        <f>BDP(A23&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A23,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H23">
-        <f>BDP(A23&amp;" Corp","MATURITY")</f>
+        <f>BDP(A23,"MATURITY")</f>
         <v/>
       </c>
       <c r="I23">
-        <f>BDP(A23&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A23,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24">
-        <f>BDP(A24&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A24,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C24">
-        <f>BDP(A24&amp;" Corp","CRNCY")</f>
+        <f>BDP(A24,"CRNCY")</f>
         <v/>
       </c>
       <c r="D24">
-        <f>BDP(A24&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A24,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E24">
-        <f>BDP(A24&amp;" Corp","CPN")/100</f>
+        <f>BDP(A24,"CPN")/100</f>
         <v/>
       </c>
       <c r="F24">
-        <f>BDP(A24&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A24,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G24">
-        <f>BDP(A24&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A24,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H24">
-        <f>BDP(A24&amp;" Corp","MATURITY")</f>
+        <f>BDP(A24,"MATURITY")</f>
         <v/>
       </c>
       <c r="I24">
-        <f>BDP(A24&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A24,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="B25">
-        <f>BDP(A25&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A25,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C25">
-        <f>BDP(A25&amp;" Corp","CRNCY")</f>
+        <f>BDP(A25,"CRNCY")</f>
         <v/>
       </c>
       <c r="D25">
-        <f>BDP(A25&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A25,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E25">
-        <f>BDP(A25&amp;" Corp","CPN")/100</f>
+        <f>BDP(A25,"CPN")/100</f>
         <v/>
       </c>
       <c r="F25">
-        <f>BDP(A25&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A25,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G25">
-        <f>BDP(A25&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A25,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H25">
-        <f>BDP(A25&amp;" Corp","MATURITY")</f>
+        <f>BDP(A25,"MATURITY")</f>
         <v/>
       </c>
       <c r="I25">
-        <f>BDP(A25&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A25,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="B26">
-        <f>BDP(A26&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A26,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C26">
-        <f>BDP(A26&amp;" Corp","CRNCY")</f>
+        <f>BDP(A26,"CRNCY")</f>
         <v/>
       </c>
       <c r="D26">
-        <f>BDP(A26&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A26,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E26">
-        <f>BDP(A26&amp;" Corp","CPN")/100</f>
+        <f>BDP(A26,"CPN")/100</f>
         <v/>
       </c>
       <c r="F26">
-        <f>BDP(A26&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A26,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G26">
-        <f>BDP(A26&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A26,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H26">
-        <f>BDP(A26&amp;" Corp","MATURITY")</f>
+        <f>BDP(A26,"MATURITY")</f>
         <v/>
       </c>
       <c r="I26">
-        <f>BDP(A26&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A26,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="B27">
-        <f>BDP(A27&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A27,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C27">
-        <f>BDP(A27&amp;" Corp","CRNCY")</f>
+        <f>BDP(A27,"CRNCY")</f>
         <v/>
       </c>
       <c r="D27">
-        <f>BDP(A27&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A27,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E27">
-        <f>BDP(A27&amp;" Corp","CPN")/100</f>
+        <f>BDP(A27,"CPN")/100</f>
         <v/>
       </c>
       <c r="F27">
-        <f>BDP(A27&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A27,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G27">
-        <f>BDP(A27&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A27,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H27">
-        <f>BDP(A27&amp;" Corp","MATURITY")</f>
+        <f>BDP(A27,"MATURITY")</f>
         <v/>
       </c>
       <c r="I27">
-        <f>BDP(A27&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A27,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="B28">
-        <f>BDP(A28&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A28,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C28">
-        <f>BDP(A28&amp;" Corp","CRNCY")</f>
+        <f>BDP(A28,"CRNCY")</f>
         <v/>
       </c>
       <c r="D28">
-        <f>BDP(A28&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A28,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E28">
-        <f>BDP(A28&amp;" Corp","CPN")/100</f>
+        <f>BDP(A28,"CPN")/100</f>
         <v/>
       </c>
       <c r="F28">
-        <f>BDP(A28&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A28,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G28">
-        <f>BDP(A28&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A28,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H28">
-        <f>BDP(A28&amp;" Corp","MATURITY")</f>
+        <f>BDP(A28,"MATURITY")</f>
         <v/>
       </c>
       <c r="I28">
-        <f>BDP(A28&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A28,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="B29">
-        <f>BDP(A29&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A29,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C29">
-        <f>BDP(A29&amp;" Corp","CRNCY")</f>
+        <f>BDP(A29,"CRNCY")</f>
         <v/>
       </c>
       <c r="D29">
-        <f>BDP(A29&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A29,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E29">
-        <f>BDP(A29&amp;" Corp","CPN")/100</f>
+        <f>BDP(A29,"CPN")/100</f>
         <v/>
       </c>
       <c r="F29">
-        <f>BDP(A29&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A29,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G29">
-        <f>BDP(A29&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A29,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H29">
-        <f>BDP(A29&amp;" Corp","MATURITY")</f>
+        <f>BDP(A29,"MATURITY")</f>
         <v/>
       </c>
       <c r="I29">
-        <f>BDP(A29&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A29,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="B30">
-        <f>BDP(A30&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A30,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C30">
-        <f>BDP(A30&amp;" Corp","CRNCY")</f>
+        <f>BDP(A30,"CRNCY")</f>
         <v/>
       </c>
       <c r="D30">
-        <f>BDP(A30&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A30,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E30">
-        <f>BDP(A30&amp;" Corp","CPN")/100</f>
+        <f>BDP(A30,"CPN")/100</f>
         <v/>
       </c>
       <c r="F30">
-        <f>BDP(A30&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A30,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G30">
-        <f>BDP(A30&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A30,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H30">
-        <f>BDP(A30&amp;" Corp","MATURITY")</f>
+        <f>BDP(A30,"MATURITY")</f>
         <v/>
       </c>
       <c r="I30">
-        <f>BDP(A30&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A30,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="B31">
-        <f>BDP(A31&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A31,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C31">
-        <f>BDP(A31&amp;" Corp","CRNCY")</f>
+        <f>BDP(A31,"CRNCY")</f>
         <v/>
       </c>
       <c r="D31">
-        <f>BDP(A31&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A31,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E31">
-        <f>BDP(A31&amp;" Corp","CPN")/100</f>
+        <f>BDP(A31,"CPN")/100</f>
         <v/>
       </c>
       <c r="F31">
-        <f>BDP(A31&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A31,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G31">
-        <f>BDP(A31&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A31,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H31">
-        <f>BDP(A31&amp;" Corp","MATURITY")</f>
+        <f>BDP(A31,"MATURITY")</f>
         <v/>
       </c>
       <c r="I31">
-        <f>BDP(A31&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A31,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="B32">
-        <f>BDP(A32&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A32,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C32">
-        <f>BDP(A32&amp;" Corp","CRNCY")</f>
+        <f>BDP(A32,"CRNCY")</f>
         <v/>
       </c>
       <c r="D32">
-        <f>BDP(A32&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A32,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E32">
-        <f>BDP(A32&amp;" Corp","CPN")/100</f>
+        <f>BDP(A32,"CPN")/100</f>
         <v/>
       </c>
       <c r="F32">
-        <f>BDP(A32&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A32,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G32">
-        <f>BDP(A32&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A32,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H32">
-        <f>BDP(A32&amp;" Corp","MATURITY")</f>
+        <f>BDP(A32,"MATURITY")</f>
         <v/>
       </c>
       <c r="I32">
-        <f>BDP(A32&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A32,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="B33">
-        <f>BDP(A33&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A33,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C33">
-        <f>BDP(A33&amp;" Corp","CRNCY")</f>
+        <f>BDP(A33,"CRNCY")</f>
         <v/>
       </c>
       <c r="D33">
-        <f>BDP(A33&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A33,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E33">
-        <f>BDP(A33&amp;" Corp","CPN")/100</f>
+        <f>BDP(A33,"CPN")/100</f>
         <v/>
       </c>
       <c r="F33">
-        <f>BDP(A33&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A33,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G33">
-        <f>BDP(A33&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A33,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H33">
-        <f>BDP(A33&amp;" Corp","MATURITY")</f>
+        <f>BDP(A33,"MATURITY")</f>
         <v/>
       </c>
       <c r="I33">
-        <f>BDP(A33&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A33,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="B34">
-        <f>BDP(A34&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A34,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C34">
-        <f>BDP(A34&amp;" Corp","CRNCY")</f>
+        <f>BDP(A34,"CRNCY")</f>
         <v/>
       </c>
       <c r="D34">
-        <f>BDP(A34&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A34,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E34">
-        <f>BDP(A34&amp;" Corp","CPN")/100</f>
+        <f>BDP(A34,"CPN")/100</f>
         <v/>
       </c>
       <c r="F34">
-        <f>BDP(A34&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A34,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G34">
-        <f>BDP(A34&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A34,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H34">
-        <f>BDP(A34&amp;" Corp","MATURITY")</f>
+        <f>BDP(A34,"MATURITY")</f>
         <v/>
       </c>
       <c r="I34">
-        <f>BDP(A34&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A34,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="B35">
-        <f>BDP(A35&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A35,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C35">
-        <f>BDP(A35&amp;" Corp","CRNCY")</f>
+        <f>BDP(A35,"CRNCY")</f>
         <v/>
       </c>
       <c r="D35">
-        <f>BDP(A35&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A35,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E35">
-        <f>BDP(A35&amp;" Corp","CPN")/100</f>
+        <f>BDP(A35,"CPN")/100</f>
         <v/>
       </c>
       <c r="F35">
-        <f>BDP(A35&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A35,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G35">
-        <f>BDP(A35&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A35,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H35">
-        <f>BDP(A35&amp;" Corp","MATURITY")</f>
+        <f>BDP(A35,"MATURITY")</f>
         <v/>
       </c>
       <c r="I35">
-        <f>BDP(A35&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A35,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="B36">
-        <f>BDP(A36&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A36,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C36">
-        <f>BDP(A36&amp;" Corp","CRNCY")</f>
+        <f>BDP(A36,"CRNCY")</f>
         <v/>
       </c>
       <c r="D36">
-        <f>BDP(A36&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A36,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E36">
-        <f>BDP(A36&amp;" Corp","CPN")/100</f>
+        <f>BDP(A36,"CPN")/100</f>
         <v/>
       </c>
       <c r="F36">
-        <f>BDP(A36&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A36,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G36">
-        <f>BDP(A36&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A36,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H36">
-        <f>BDP(A36&amp;" Corp","MATURITY")</f>
+        <f>BDP(A36,"MATURITY")</f>
         <v/>
       </c>
       <c r="I36">
-        <f>BDP(A36&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A36,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="B37">
-        <f>BDP(A37&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A37,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C37">
-        <f>BDP(A37&amp;" Corp","CRNCY")</f>
+        <f>BDP(A37,"CRNCY")</f>
         <v/>
       </c>
       <c r="D37">
-        <f>BDP(A37&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A37,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E37">
-        <f>BDP(A37&amp;" Corp","CPN")/100</f>
+        <f>BDP(A37,"CPN")/100</f>
         <v/>
       </c>
       <c r="F37">
-        <f>BDP(A37&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A37,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G37">
-        <f>BDP(A37&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A37,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H37">
-        <f>BDP(A37&amp;" Corp","MATURITY")</f>
+        <f>BDP(A37,"MATURITY")</f>
         <v/>
       </c>
       <c r="I37">
-        <f>BDP(A37&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A37,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="B38">
-        <f>BDP(A38&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A38,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C38">
-        <f>BDP(A38&amp;" Corp","CRNCY")</f>
+        <f>BDP(A38,"CRNCY")</f>
         <v/>
       </c>
       <c r="D38">
-        <f>BDP(A38&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A38,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E38">
-        <f>BDP(A38&amp;" Corp","CPN")/100</f>
+        <f>BDP(A38,"CPN")/100</f>
         <v/>
       </c>
       <c r="F38">
-        <f>BDP(A38&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A38,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G38">
-        <f>BDP(A38&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A38,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H38">
-        <f>BDP(A38&amp;" Corp","MATURITY")</f>
+        <f>BDP(A38,"MATURITY")</f>
         <v/>
       </c>
       <c r="I38">
-        <f>BDP(A38&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A38,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="B39">
-        <f>BDP(A39&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A39,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C39">
-        <f>BDP(A39&amp;" Corp","CRNCY")</f>
+        <f>BDP(A39,"CRNCY")</f>
         <v/>
       </c>
       <c r="D39">
-        <f>BDP(A39&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A39,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E39">
-        <f>BDP(A39&amp;" Corp","CPN")/100</f>
+        <f>BDP(A39,"CPN")/100</f>
         <v/>
       </c>
       <c r="F39">
-        <f>BDP(A39&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A39,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G39">
-        <f>BDP(A39&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A39,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H39">
-        <f>BDP(A39&amp;" Corp","MATURITY")</f>
+        <f>BDP(A39,"MATURITY")</f>
         <v/>
       </c>
       <c r="I39">
-        <f>BDP(A39&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A39,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="B40">
-        <f>BDP(A40&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A40,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C40">
-        <f>BDP(A40&amp;" Corp","CRNCY")</f>
+        <f>BDP(A40,"CRNCY")</f>
         <v/>
       </c>
       <c r="D40">
-        <f>BDP(A40&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A40,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E40">
-        <f>BDP(A40&amp;" Corp","CPN")/100</f>
+        <f>BDP(A40,"CPN")/100</f>
         <v/>
       </c>
       <c r="F40">
-        <f>BDP(A40&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A40,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G40">
-        <f>BDP(A40&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A40,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H40">
-        <f>BDP(A40&amp;" Corp","MATURITY")</f>
+        <f>BDP(A40,"MATURITY")</f>
         <v/>
       </c>
       <c r="I40">
-        <f>BDP(A40&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A40,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="B41">
-        <f>BDP(A41&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A41,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C41">
-        <f>BDP(A41&amp;" Corp","CRNCY")</f>
+        <f>BDP(A41,"CRNCY")</f>
         <v/>
       </c>
       <c r="D41">
-        <f>BDP(A41&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A41,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E41">
-        <f>BDP(A41&amp;" Corp","CPN")/100</f>
+        <f>BDP(A41,"CPN")/100</f>
         <v/>
       </c>
       <c r="F41">
-        <f>BDP(A41&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A41,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G41">
-        <f>BDP(A41&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A41,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H41">
-        <f>BDP(A41&amp;" Corp","MATURITY")</f>
+        <f>BDP(A41,"MATURITY")</f>
         <v/>
       </c>
       <c r="I41">
-        <f>BDP(A41&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A41,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42">
-        <f>BDP(A42&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A42,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C42">
-        <f>BDP(A42&amp;" Corp","CRNCY")</f>
+        <f>BDP(A42,"CRNCY")</f>
         <v/>
       </c>
       <c r="D42">
-        <f>BDP(A42&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A42,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E42">
-        <f>BDP(A42&amp;" Corp","CPN")/100</f>
+        <f>BDP(A42,"CPN")/100</f>
         <v/>
       </c>
       <c r="F42">
-        <f>BDP(A42&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A42,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G42">
-        <f>BDP(A42&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A42,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H42">
-        <f>BDP(A42&amp;" Corp","MATURITY")</f>
+        <f>BDP(A42,"MATURITY")</f>
         <v/>
       </c>
       <c r="I42">
-        <f>BDP(A42&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A42,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43">
-        <f>BDP(A43&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A43,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C43">
-        <f>BDP(A43&amp;" Corp","CRNCY")</f>
+        <f>BDP(A43,"CRNCY")</f>
         <v/>
       </c>
       <c r="D43">
-        <f>BDP(A43&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A43,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E43">
-        <f>BDP(A43&amp;" Corp","CPN")/100</f>
+        <f>BDP(A43,"CPN")/100</f>
         <v/>
       </c>
       <c r="F43">
-        <f>BDP(A43&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A43,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G43">
-        <f>BDP(A43&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A43,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H43">
-        <f>BDP(A43&amp;" Corp","MATURITY")</f>
+        <f>BDP(A43,"MATURITY")</f>
         <v/>
       </c>
       <c r="I43">
-        <f>BDP(A43&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A43,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44">
-        <f>BDP(A44&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A44,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C44">
-        <f>BDP(A44&amp;" Corp","CRNCY")</f>
+        <f>BDP(A44,"CRNCY")</f>
         <v/>
       </c>
       <c r="D44">
-        <f>BDP(A44&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A44,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E44">
-        <f>BDP(A44&amp;" Corp","CPN")/100</f>
+        <f>BDP(A44,"CPN")/100</f>
         <v/>
       </c>
       <c r="F44">
-        <f>BDP(A44&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A44,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G44">
-        <f>BDP(A44&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A44,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H44">
-        <f>BDP(A44&amp;" Corp","MATURITY")</f>
+        <f>BDP(A44,"MATURITY")</f>
         <v/>
       </c>
       <c r="I44">
-        <f>BDP(A44&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A44,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45">
-        <f>BDP(A45&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A45,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C45">
-        <f>BDP(A45&amp;" Corp","CRNCY")</f>
+        <f>BDP(A45,"CRNCY")</f>
         <v/>
       </c>
       <c r="D45">
-        <f>BDP(A45&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A45,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E45">
-        <f>BDP(A45&amp;" Corp","CPN")/100</f>
+        <f>BDP(A45,"CPN")/100</f>
         <v/>
       </c>
       <c r="F45">
-        <f>BDP(A45&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A45,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G45">
-        <f>BDP(A45&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A45,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H45">
-        <f>BDP(A45&amp;" Corp","MATURITY")</f>
+        <f>BDP(A45,"MATURITY")</f>
         <v/>
       </c>
       <c r="I45">
-        <f>BDP(A45&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A45,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46">
-        <f>BDP(A46&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A46,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C46">
-        <f>BDP(A46&amp;" Corp","CRNCY")</f>
+        <f>BDP(A46,"CRNCY")</f>
         <v/>
       </c>
       <c r="D46">
-        <f>BDP(A46&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A46,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E46">
-        <f>BDP(A46&amp;" Corp","CPN")/100</f>
+        <f>BDP(A46,"CPN")/100</f>
         <v/>
       </c>
       <c r="F46">
-        <f>BDP(A46&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A46,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G46">
-        <f>BDP(A46&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A46,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H46">
-        <f>BDP(A46&amp;" Corp","MATURITY")</f>
+        <f>BDP(A46,"MATURITY")</f>
         <v/>
       </c>
       <c r="I46">
-        <f>BDP(A46&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A46,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="B47">
-        <f>BDP(A47&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A47,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C47">
-        <f>BDP(A47&amp;" Corp","CRNCY")</f>
+        <f>BDP(A47,"CRNCY")</f>
         <v/>
       </c>
       <c r="D47">
-        <f>BDP(A47&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A47,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E47">
-        <f>BDP(A47&amp;" Corp","CPN")/100</f>
+        <f>BDP(A47,"CPN")/100</f>
         <v/>
       </c>
       <c r="F47">
-        <f>BDP(A47&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A47,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G47">
-        <f>BDP(A47&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A47,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H47">
-        <f>BDP(A47&amp;" Corp","MATURITY")</f>
+        <f>BDP(A47,"MATURITY")</f>
         <v/>
       </c>
       <c r="I47">
-        <f>BDP(A47&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A47,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="B48">
-        <f>BDP(A48&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A48,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C48">
-        <f>BDP(A48&amp;" Corp","CRNCY")</f>
+        <f>BDP(A48,"CRNCY")</f>
         <v/>
       </c>
       <c r="D48">
-        <f>BDP(A48&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A48,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E48">
-        <f>BDP(A48&amp;" Corp","CPN")/100</f>
+        <f>BDP(A48,"CPN")/100</f>
         <v/>
       </c>
       <c r="F48">
-        <f>BDP(A48&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A48,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G48">
-        <f>BDP(A48&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A48,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H48">
-        <f>BDP(A48&amp;" Corp","MATURITY")</f>
+        <f>BDP(A48,"MATURITY")</f>
         <v/>
       </c>
       <c r="I48">
-        <f>BDP(A48&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A48,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="B49">
-        <f>BDP(A49&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A49,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C49">
-        <f>BDP(A49&amp;" Corp","CRNCY")</f>
+        <f>BDP(A49,"CRNCY")</f>
         <v/>
       </c>
       <c r="D49">
-        <f>BDP(A49&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A49,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E49">
-        <f>BDP(A49&amp;" Corp","CPN")/100</f>
+        <f>BDP(A49,"CPN")/100</f>
         <v/>
       </c>
       <c r="F49">
-        <f>BDP(A49&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A49,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G49">
-        <f>BDP(A49&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A49,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H49">
-        <f>BDP(A49&amp;" Corp","MATURITY")</f>
+        <f>BDP(A49,"MATURITY")</f>
         <v/>
       </c>
       <c r="I49">
-        <f>BDP(A49&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A49,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="B50">
-        <f>BDP(A50&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A50,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C50">
-        <f>BDP(A50&amp;" Corp","CRNCY")</f>
+        <f>BDP(A50,"CRNCY")</f>
         <v/>
       </c>
       <c r="D50">
-        <f>BDP(A50&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A50,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E50">
-        <f>BDP(A50&amp;" Corp","CPN")/100</f>
+        <f>BDP(A50,"CPN")/100</f>
         <v/>
       </c>
       <c r="F50">
-        <f>BDP(A50&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A50,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G50">
-        <f>BDP(A50&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A50,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H50">
-        <f>BDP(A50&amp;" Corp","MATURITY")</f>
+        <f>BDP(A50,"MATURITY")</f>
         <v/>
       </c>
       <c r="I50">
-        <f>BDP(A50&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A50,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="B51">
-        <f>BDP(A51&amp;" Corp","SECURITY_DES")</f>
+        <f>BDP(A51,"SECURITY_DES")</f>
         <v/>
       </c>
       <c r="C51">
-        <f>BDP(A51&amp;" Corp","CRNCY")</f>
+        <f>BDP(A51,"CRNCY")</f>
         <v/>
       </c>
       <c r="D51">
-        <f>BDP(A51&amp;" Corp","CNTRY_OF_RISK")</f>
+        <f>BDP(A51,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
       <c r="E51">
-        <f>BDP(A51&amp;" Corp","CPN")/100</f>
+        <f>BDP(A51,"CPN")/100</f>
         <v/>
       </c>
       <c r="F51">
-        <f>BDP(A51&amp;" Corp","CPN_FREQ")</f>
+        <f>BDP(A51,"CPN_FREQ")</f>
         <v/>
       </c>
       <c r="G51">
-        <f>BDP(A51&amp;" Corp","DAY_CNT_DES")</f>
+        <f>BDP(A51,"DAY_CNT_DES")</f>
         <v/>
       </c>
       <c r="H51">
-        <f>BDP(A51&amp;" Corp","MATURITY")</f>
+        <f>BDP(A51,"MATURITY")</f>
         <v/>
       </c>
       <c r="I51">
-        <f>BDP(A51&amp;" Corp","FIRST_CPN_DT")</f>
+        <f>BDP(A51,"FIRST_CPN_DT")</f>
         <v/>
       </c>
     </row>
@@ -2951,34 +2946,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>25714PFB9 Corp</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>04/30/2025</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>195325ER2 Corp</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>25714PEF1 Corp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>PX_LAST</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
-          <t>End</t>
+          <t>05/20/2025</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3">
-        <f>BDH(A1,"PX_LAST",B1,C1,"Fill","0","Dates","1")</f>
+      <c r="A3">
+        <f>@BDH(A1,B2,B1,A2,"fill=p","days=a")</f>
+        <v/>
+      </c>
+      <c r="C3">
+        <f>@BDH(C1,B2,D2,A2,"fill=p","days=a")</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>@BDH(E1,B2,F2,A2,"fill=p","days=a")</f>
         <v/>
       </c>
     </row>

--- a/projects/02-pnl-dashboard/templates/bloomberg_prices.xlsx
+++ b/projects/02-pnl-dashboard/templates/bloomberg_prices.xlsx
@@ -2946,7 +2946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2974,59 +2974,20 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>25714PFB9 Corp</t>
+          <t>BBG Ticker</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>04/30/2025</t>
+          <t>End Date (mm/dd/yyyy)</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>195325ER2 Corp</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>25714PEF1 Corp</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>06/03/2026</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>PX_LAST</t>
         </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>05/20/2025</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>05/12/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <f>@BDH(A1,B2,B1,A2,"fill=p","days=a")</f>
-        <v/>
-      </c>
-      <c r="C3">
-        <f>@BDH(C1,B2,D2,A2,"fill=p","days=a")</f>
-        <v/>
-      </c>
-      <c r="E3">
-        <f>@BDH(E1,B2,F2,A2,"fill=p","days=a")</f>
-        <v/>
       </c>
     </row>
   </sheetData>

--- a/projects/02-pnl-dashboard/templates/bloomberg_prices.xlsx
+++ b/projects/02-pnl-dashboard/templates/bloomberg_prices.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1163,6 +1163,706 @@
         <v/>
       </c>
     </row>
+    <row r="52">
+      <c r="B52">
+        <f>BDP(A52,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C52">
+        <f>BDP(A52,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D52">
+        <f>BDP(A52,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53">
+        <f>BDP(A53,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C53">
+        <f>BDP(A53,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D53">
+        <f>BDP(A53,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54">
+        <f>BDP(A54,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C54">
+        <f>BDP(A54,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D54">
+        <f>BDP(A54,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55">
+        <f>BDP(A55,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C55">
+        <f>BDP(A55,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D55">
+        <f>BDP(A55,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56">
+        <f>BDP(A56,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C56">
+        <f>BDP(A56,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D56">
+        <f>BDP(A56,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57">
+        <f>BDP(A57,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C57">
+        <f>BDP(A57,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D57">
+        <f>BDP(A57,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58">
+        <f>BDP(A58,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C58">
+        <f>BDP(A58,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D58">
+        <f>BDP(A58,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59">
+        <f>BDP(A59,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C59">
+        <f>BDP(A59,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D59">
+        <f>BDP(A59,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60">
+        <f>BDP(A60,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C60">
+        <f>BDP(A60,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D60">
+        <f>BDP(A60,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61">
+        <f>BDP(A61,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C61">
+        <f>BDP(A61,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D61">
+        <f>BDP(A61,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62">
+        <f>BDP(A62,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C62">
+        <f>BDP(A62,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D62">
+        <f>BDP(A62,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63">
+        <f>BDP(A63,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C63">
+        <f>BDP(A63,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D63">
+        <f>BDP(A63,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64">
+        <f>BDP(A64,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C64">
+        <f>BDP(A64,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D64">
+        <f>BDP(A64,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65">
+        <f>BDP(A65,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C65">
+        <f>BDP(A65,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D65">
+        <f>BDP(A65,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66">
+        <f>BDP(A66,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C66">
+        <f>BDP(A66,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D66">
+        <f>BDP(A66,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67">
+        <f>BDP(A67,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C67">
+        <f>BDP(A67,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D67">
+        <f>BDP(A67,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68">
+        <f>BDP(A68,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C68">
+        <f>BDP(A68,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D68">
+        <f>BDP(A68,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69">
+        <f>BDP(A69,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C69">
+        <f>BDP(A69,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D69">
+        <f>BDP(A69,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70">
+        <f>BDP(A70,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C70">
+        <f>BDP(A70,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D70">
+        <f>BDP(A70,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71">
+        <f>BDP(A71,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C71">
+        <f>BDP(A71,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D71">
+        <f>BDP(A71,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72">
+        <f>BDP(A72,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C72">
+        <f>BDP(A72,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D72">
+        <f>BDP(A72,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73">
+        <f>BDP(A73,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C73">
+        <f>BDP(A73,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D73">
+        <f>BDP(A73,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74">
+        <f>BDP(A74,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C74">
+        <f>BDP(A74,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D74">
+        <f>BDP(A74,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75">
+        <f>BDP(A75,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C75">
+        <f>BDP(A75,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D75">
+        <f>BDP(A75,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76">
+        <f>BDP(A76,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C76">
+        <f>BDP(A76,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D76">
+        <f>BDP(A76,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77">
+        <f>BDP(A77,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C77">
+        <f>BDP(A77,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D77">
+        <f>BDP(A77,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78">
+        <f>BDP(A78,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C78">
+        <f>BDP(A78,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D78">
+        <f>BDP(A78,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79">
+        <f>BDP(A79,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C79">
+        <f>BDP(A79,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D79">
+        <f>BDP(A79,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80">
+        <f>BDP(A80,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C80">
+        <f>BDP(A80,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D80">
+        <f>BDP(A80,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81">
+        <f>BDP(A81,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C81">
+        <f>BDP(A81,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D81">
+        <f>BDP(A81,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82">
+        <f>BDP(A82,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C82">
+        <f>BDP(A82,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D82">
+        <f>BDP(A82,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83">
+        <f>BDP(A83,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C83">
+        <f>BDP(A83,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D83">
+        <f>BDP(A83,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84">
+        <f>BDP(A84,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C84">
+        <f>BDP(A84,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D84">
+        <f>BDP(A84,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85">
+        <f>BDP(A85,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C85">
+        <f>BDP(A85,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D85">
+        <f>BDP(A85,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86">
+        <f>BDP(A86,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C86">
+        <f>BDP(A86,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D86">
+        <f>BDP(A86,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87">
+        <f>BDP(A87,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C87">
+        <f>BDP(A87,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D87">
+        <f>BDP(A87,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88">
+        <f>BDP(A88,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C88">
+        <f>BDP(A88,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D88">
+        <f>BDP(A88,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89">
+        <f>BDP(A89,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C89">
+        <f>BDP(A89,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D89">
+        <f>BDP(A89,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90">
+        <f>BDP(A90,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C90">
+        <f>BDP(A90,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D90">
+        <f>BDP(A90,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91">
+        <f>BDP(A91,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C91">
+        <f>BDP(A91,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D91">
+        <f>BDP(A91,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92">
+        <f>BDP(A92,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C92">
+        <f>BDP(A92,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D92">
+        <f>BDP(A92,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93">
+        <f>BDP(A93,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C93">
+        <f>BDP(A93,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D93">
+        <f>BDP(A93,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94">
+        <f>BDP(A94,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C94">
+        <f>BDP(A94,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D94">
+        <f>BDP(A94,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95">
+        <f>BDP(A95,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C95">
+        <f>BDP(A95,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D95">
+        <f>BDP(A95,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96">
+        <f>BDP(A96,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C96">
+        <f>BDP(A96,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D96">
+        <f>BDP(A96,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97">
+        <f>BDP(A97,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C97">
+        <f>BDP(A97,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D97">
+        <f>BDP(A97,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98">
+        <f>BDP(A98,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C98">
+        <f>BDP(A98,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D98">
+        <f>BDP(A98,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99">
+        <f>BDP(A99,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C99">
+        <f>BDP(A99,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D99">
+        <f>BDP(A99,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100">
+        <f>BDP(A100,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C100">
+        <f>BDP(A100,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D100">
+        <f>BDP(A100,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101">
+        <f>BDP(A101,"PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="C101">
+        <f>BDP(A101,"YAS_ASW_SPREAD")</f>
+        <v/>
+      </c>
+      <c r="D101">
+        <f>BDP(A101,"YLD_YTM_MID")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1174,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1186,6 +1886,15 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1234,6 +1943,51 @@
           <t>first_coupon_date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>instrument_type</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>issuer</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>country_of_risk</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>seniority</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>rating_sp</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>rating_moody</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rating_fitch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="B2">
@@ -1268,6 +2022,38 @@
         <f>BDP(A2,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J2">
+        <f>BDP(A2,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>BDP(A2,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>BDP(A2,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M2">
+        <f>BDP(A2,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>BDP(A2,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P2">
+        <f>BDP(A2,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q2">
+        <f>BDP(A2,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R2">
+        <f>BDP(A2,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="B3">
@@ -1302,6 +2088,38 @@
         <f>BDP(A3,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J3">
+        <f>BDP(A3,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K3">
+        <f>BDP(A3,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L3">
+        <f>BDP(A3,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M3">
+        <f>BDP(A3,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N3">
+        <f>BDP(A3,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P3">
+        <f>BDP(A3,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q3">
+        <f>BDP(A3,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R3">
+        <f>BDP(A3,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="B4">
@@ -1336,6 +2154,38 @@
         <f>BDP(A4,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J4">
+        <f>BDP(A4,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K4">
+        <f>BDP(A4,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L4">
+        <f>BDP(A4,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M4">
+        <f>BDP(A4,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N4">
+        <f>BDP(A4,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P4">
+        <f>BDP(A4,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q4">
+        <f>BDP(A4,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R4">
+        <f>BDP(A4,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="B5">
@@ -1370,6 +2220,38 @@
         <f>BDP(A5,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J5">
+        <f>BDP(A5,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K5">
+        <f>BDP(A5,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L5">
+        <f>BDP(A5,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M5">
+        <f>BDP(A5,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N5">
+        <f>BDP(A5,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P5">
+        <f>BDP(A5,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q5">
+        <f>BDP(A5,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R5">
+        <f>BDP(A5,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="B6">
@@ -1404,6 +2286,38 @@
         <f>BDP(A6,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J6">
+        <f>BDP(A6,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K6">
+        <f>BDP(A6,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>BDP(A6,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M6">
+        <f>BDP(A6,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N6">
+        <f>BDP(A6,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P6">
+        <f>BDP(A6,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q6">
+        <f>BDP(A6,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R6">
+        <f>BDP(A6,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="B7">
@@ -1438,6 +2352,38 @@
         <f>BDP(A7,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J7">
+        <f>BDP(A7,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K7">
+        <f>BDP(A7,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>BDP(A7,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M7">
+        <f>BDP(A7,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N7">
+        <f>BDP(A7,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P7">
+        <f>BDP(A7,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q7">
+        <f>BDP(A7,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R7">
+        <f>BDP(A7,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="B8">
@@ -1472,6 +2418,38 @@
         <f>BDP(A8,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J8">
+        <f>BDP(A8,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>BDP(A8,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>BDP(A8,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M8">
+        <f>BDP(A8,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N8">
+        <f>BDP(A8,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P8">
+        <f>BDP(A8,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q8">
+        <f>BDP(A8,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R8">
+        <f>BDP(A8,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="B9">
@@ -1506,6 +2484,38 @@
         <f>BDP(A9,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J9">
+        <f>BDP(A9,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K9">
+        <f>BDP(A9,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L9">
+        <f>BDP(A9,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M9">
+        <f>BDP(A9,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N9">
+        <f>BDP(A9,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P9">
+        <f>BDP(A9,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q9">
+        <f>BDP(A9,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R9">
+        <f>BDP(A9,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="B10">
@@ -1540,6 +2550,38 @@
         <f>BDP(A10,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J10">
+        <f>BDP(A10,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K10">
+        <f>BDP(A10,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L10">
+        <f>BDP(A10,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M10">
+        <f>BDP(A10,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N10">
+        <f>BDP(A10,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P10">
+        <f>BDP(A10,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q10">
+        <f>BDP(A10,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R10">
+        <f>BDP(A10,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="B11">
@@ -1574,6 +2616,38 @@
         <f>BDP(A11,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J11">
+        <f>BDP(A11,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K11">
+        <f>BDP(A11,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L11">
+        <f>BDP(A11,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M11">
+        <f>BDP(A11,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N11">
+        <f>BDP(A11,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P11">
+        <f>BDP(A11,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q11">
+        <f>BDP(A11,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R11">
+        <f>BDP(A11,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="B12">
@@ -1608,6 +2682,38 @@
         <f>BDP(A12,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J12">
+        <f>BDP(A12,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K12">
+        <f>BDP(A12,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L12">
+        <f>BDP(A12,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M12">
+        <f>BDP(A12,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N12">
+        <f>BDP(A12,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P12">
+        <f>BDP(A12,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q12">
+        <f>BDP(A12,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R12">
+        <f>BDP(A12,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="B13">
@@ -1642,6 +2748,38 @@
         <f>BDP(A13,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J13">
+        <f>BDP(A13,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K13">
+        <f>BDP(A13,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L13">
+        <f>BDP(A13,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M13">
+        <f>BDP(A13,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N13">
+        <f>BDP(A13,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P13">
+        <f>BDP(A13,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q13">
+        <f>BDP(A13,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R13">
+        <f>BDP(A13,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="B14">
@@ -1676,6 +2814,38 @@
         <f>BDP(A14,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J14">
+        <f>BDP(A14,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K14">
+        <f>BDP(A14,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L14">
+        <f>BDP(A14,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M14">
+        <f>BDP(A14,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N14">
+        <f>BDP(A14,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P14">
+        <f>BDP(A14,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q14">
+        <f>BDP(A14,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R14">
+        <f>BDP(A14,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="B15">
@@ -1710,6 +2880,38 @@
         <f>BDP(A15,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J15">
+        <f>BDP(A15,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K15">
+        <f>BDP(A15,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L15">
+        <f>BDP(A15,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M15">
+        <f>BDP(A15,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N15">
+        <f>BDP(A15,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P15">
+        <f>BDP(A15,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q15">
+        <f>BDP(A15,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R15">
+        <f>BDP(A15,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="B16">
@@ -1744,6 +2946,38 @@
         <f>BDP(A16,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J16">
+        <f>BDP(A16,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K16">
+        <f>BDP(A16,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L16">
+        <f>BDP(A16,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M16">
+        <f>BDP(A16,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N16">
+        <f>BDP(A16,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P16">
+        <f>BDP(A16,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q16">
+        <f>BDP(A16,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R16">
+        <f>BDP(A16,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="B17">
@@ -1778,6 +3012,38 @@
         <f>BDP(A17,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J17">
+        <f>BDP(A17,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K17">
+        <f>BDP(A17,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L17">
+        <f>BDP(A17,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M17">
+        <f>BDP(A17,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N17">
+        <f>BDP(A17,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P17">
+        <f>BDP(A17,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q17">
+        <f>BDP(A17,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R17">
+        <f>BDP(A17,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="B18">
@@ -1812,6 +3078,38 @@
         <f>BDP(A18,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J18">
+        <f>BDP(A18,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K18">
+        <f>BDP(A18,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L18">
+        <f>BDP(A18,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M18">
+        <f>BDP(A18,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N18">
+        <f>BDP(A18,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P18">
+        <f>BDP(A18,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q18">
+        <f>BDP(A18,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R18">
+        <f>BDP(A18,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="B19">
@@ -1846,6 +3144,38 @@
         <f>BDP(A19,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J19">
+        <f>BDP(A19,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K19">
+        <f>BDP(A19,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L19">
+        <f>BDP(A19,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M19">
+        <f>BDP(A19,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N19">
+        <f>BDP(A19,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P19">
+        <f>BDP(A19,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q19">
+        <f>BDP(A19,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R19">
+        <f>BDP(A19,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="B20">
@@ -1880,6 +3210,38 @@
         <f>BDP(A20,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J20">
+        <f>BDP(A20,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K20">
+        <f>BDP(A20,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L20">
+        <f>BDP(A20,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M20">
+        <f>BDP(A20,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N20">
+        <f>BDP(A20,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P20">
+        <f>BDP(A20,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q20">
+        <f>BDP(A20,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R20">
+        <f>BDP(A20,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="B21">
@@ -1914,6 +3276,38 @@
         <f>BDP(A21,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J21">
+        <f>BDP(A21,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K21">
+        <f>BDP(A21,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L21">
+        <f>BDP(A21,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M21">
+        <f>BDP(A21,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N21">
+        <f>BDP(A21,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P21">
+        <f>BDP(A21,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q21">
+        <f>BDP(A21,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R21">
+        <f>BDP(A21,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="B22">
@@ -1948,6 +3342,38 @@
         <f>BDP(A22,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J22">
+        <f>BDP(A22,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K22">
+        <f>BDP(A22,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L22">
+        <f>BDP(A22,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M22">
+        <f>BDP(A22,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N22">
+        <f>BDP(A22,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P22">
+        <f>BDP(A22,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q22">
+        <f>BDP(A22,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R22">
+        <f>BDP(A22,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="B23">
@@ -1982,6 +3408,38 @@
         <f>BDP(A23,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J23">
+        <f>BDP(A23,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K23">
+        <f>BDP(A23,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L23">
+        <f>BDP(A23,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M23">
+        <f>BDP(A23,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N23">
+        <f>BDP(A23,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P23">
+        <f>BDP(A23,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q23">
+        <f>BDP(A23,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R23">
+        <f>BDP(A23,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="B24">
@@ -2016,6 +3474,38 @@
         <f>BDP(A24,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J24">
+        <f>BDP(A24,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K24">
+        <f>BDP(A24,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L24">
+        <f>BDP(A24,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M24">
+        <f>BDP(A24,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N24">
+        <f>BDP(A24,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P24">
+        <f>BDP(A24,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q24">
+        <f>BDP(A24,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R24">
+        <f>BDP(A24,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="B25">
@@ -2050,6 +3540,38 @@
         <f>BDP(A25,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J25">
+        <f>BDP(A25,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K25">
+        <f>BDP(A25,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L25">
+        <f>BDP(A25,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M25">
+        <f>BDP(A25,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N25">
+        <f>BDP(A25,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P25">
+        <f>BDP(A25,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q25">
+        <f>BDP(A25,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R25">
+        <f>BDP(A25,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="B26">
@@ -2084,6 +3606,38 @@
         <f>BDP(A26,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J26">
+        <f>BDP(A26,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K26">
+        <f>BDP(A26,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L26">
+        <f>BDP(A26,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M26">
+        <f>BDP(A26,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N26">
+        <f>BDP(A26,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P26">
+        <f>BDP(A26,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q26">
+        <f>BDP(A26,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R26">
+        <f>BDP(A26,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="B27">
@@ -2118,6 +3672,38 @@
         <f>BDP(A27,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J27">
+        <f>BDP(A27,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K27">
+        <f>BDP(A27,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L27">
+        <f>BDP(A27,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M27">
+        <f>BDP(A27,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N27">
+        <f>BDP(A27,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P27">
+        <f>BDP(A27,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q27">
+        <f>BDP(A27,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R27">
+        <f>BDP(A27,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="B28">
@@ -2152,6 +3738,38 @@
         <f>BDP(A28,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J28">
+        <f>BDP(A28,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K28">
+        <f>BDP(A28,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L28">
+        <f>BDP(A28,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M28">
+        <f>BDP(A28,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N28">
+        <f>BDP(A28,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P28">
+        <f>BDP(A28,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q28">
+        <f>BDP(A28,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R28">
+        <f>BDP(A28,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="B29">
@@ -2186,6 +3804,38 @@
         <f>BDP(A29,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J29">
+        <f>BDP(A29,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K29">
+        <f>BDP(A29,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L29">
+        <f>BDP(A29,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M29">
+        <f>BDP(A29,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N29">
+        <f>BDP(A29,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P29">
+        <f>BDP(A29,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q29">
+        <f>BDP(A29,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R29">
+        <f>BDP(A29,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="B30">
@@ -2220,6 +3870,38 @@
         <f>BDP(A30,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J30">
+        <f>BDP(A30,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K30">
+        <f>BDP(A30,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L30">
+        <f>BDP(A30,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M30">
+        <f>BDP(A30,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N30">
+        <f>BDP(A30,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P30">
+        <f>BDP(A30,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q30">
+        <f>BDP(A30,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R30">
+        <f>BDP(A30,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="B31">
@@ -2254,6 +3936,38 @@
         <f>BDP(A31,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J31">
+        <f>BDP(A31,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K31">
+        <f>BDP(A31,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L31">
+        <f>BDP(A31,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M31">
+        <f>BDP(A31,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N31">
+        <f>BDP(A31,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P31">
+        <f>BDP(A31,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q31">
+        <f>BDP(A31,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R31">
+        <f>BDP(A31,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="B32">
@@ -2288,6 +4002,38 @@
         <f>BDP(A32,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J32">
+        <f>BDP(A32,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K32">
+        <f>BDP(A32,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L32">
+        <f>BDP(A32,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M32">
+        <f>BDP(A32,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N32">
+        <f>BDP(A32,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P32">
+        <f>BDP(A32,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q32">
+        <f>BDP(A32,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R32">
+        <f>BDP(A32,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="B33">
@@ -2322,6 +4068,38 @@
         <f>BDP(A33,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J33">
+        <f>BDP(A33,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K33">
+        <f>BDP(A33,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L33">
+        <f>BDP(A33,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M33">
+        <f>BDP(A33,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N33">
+        <f>BDP(A33,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P33">
+        <f>BDP(A33,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q33">
+        <f>BDP(A33,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R33">
+        <f>BDP(A33,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="B34">
@@ -2356,6 +4134,38 @@
         <f>BDP(A34,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J34">
+        <f>BDP(A34,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K34">
+        <f>BDP(A34,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L34">
+        <f>BDP(A34,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M34">
+        <f>BDP(A34,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N34">
+        <f>BDP(A34,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P34">
+        <f>BDP(A34,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q34">
+        <f>BDP(A34,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R34">
+        <f>BDP(A34,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="B35">
@@ -2390,6 +4200,38 @@
         <f>BDP(A35,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J35">
+        <f>BDP(A35,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K35">
+        <f>BDP(A35,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L35">
+        <f>BDP(A35,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M35">
+        <f>BDP(A35,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N35">
+        <f>BDP(A35,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P35">
+        <f>BDP(A35,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q35">
+        <f>BDP(A35,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R35">
+        <f>BDP(A35,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="B36">
@@ -2424,6 +4266,38 @@
         <f>BDP(A36,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J36">
+        <f>BDP(A36,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K36">
+        <f>BDP(A36,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L36">
+        <f>BDP(A36,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M36">
+        <f>BDP(A36,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N36">
+        <f>BDP(A36,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P36">
+        <f>BDP(A36,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q36">
+        <f>BDP(A36,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R36">
+        <f>BDP(A36,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="B37">
@@ -2458,6 +4332,38 @@
         <f>BDP(A37,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J37">
+        <f>BDP(A37,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K37">
+        <f>BDP(A37,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L37">
+        <f>BDP(A37,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M37">
+        <f>BDP(A37,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N37">
+        <f>BDP(A37,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P37">
+        <f>BDP(A37,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q37">
+        <f>BDP(A37,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R37">
+        <f>BDP(A37,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="B38">
@@ -2492,6 +4398,38 @@
         <f>BDP(A38,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J38">
+        <f>BDP(A38,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K38">
+        <f>BDP(A38,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L38">
+        <f>BDP(A38,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M38">
+        <f>BDP(A38,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N38">
+        <f>BDP(A38,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P38">
+        <f>BDP(A38,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q38">
+        <f>BDP(A38,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R38">
+        <f>BDP(A38,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="B39">
@@ -2526,6 +4464,38 @@
         <f>BDP(A39,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J39">
+        <f>BDP(A39,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K39">
+        <f>BDP(A39,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L39">
+        <f>BDP(A39,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M39">
+        <f>BDP(A39,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N39">
+        <f>BDP(A39,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P39">
+        <f>BDP(A39,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q39">
+        <f>BDP(A39,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R39">
+        <f>BDP(A39,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="B40">
@@ -2560,6 +4530,38 @@
         <f>BDP(A40,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J40">
+        <f>BDP(A40,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K40">
+        <f>BDP(A40,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L40">
+        <f>BDP(A40,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M40">
+        <f>BDP(A40,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N40">
+        <f>BDP(A40,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P40">
+        <f>BDP(A40,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q40">
+        <f>BDP(A40,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R40">
+        <f>BDP(A40,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="B41">
@@ -2594,6 +4596,38 @@
         <f>BDP(A41,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J41">
+        <f>BDP(A41,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K41">
+        <f>BDP(A41,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L41">
+        <f>BDP(A41,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M41">
+        <f>BDP(A41,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N41">
+        <f>BDP(A41,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P41">
+        <f>BDP(A41,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q41">
+        <f>BDP(A41,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R41">
+        <f>BDP(A41,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="B42">
@@ -2628,6 +4662,38 @@
         <f>BDP(A42,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J42">
+        <f>BDP(A42,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K42">
+        <f>BDP(A42,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L42">
+        <f>BDP(A42,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M42">
+        <f>BDP(A42,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N42">
+        <f>BDP(A42,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P42">
+        <f>BDP(A42,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q42">
+        <f>BDP(A42,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R42">
+        <f>BDP(A42,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="B43">
@@ -2662,6 +4728,38 @@
         <f>BDP(A43,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J43">
+        <f>BDP(A43,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K43">
+        <f>BDP(A43,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L43">
+        <f>BDP(A43,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M43">
+        <f>BDP(A43,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N43">
+        <f>BDP(A43,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P43">
+        <f>BDP(A43,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q43">
+        <f>BDP(A43,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R43">
+        <f>BDP(A43,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="B44">
@@ -2696,6 +4794,38 @@
         <f>BDP(A44,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J44">
+        <f>BDP(A44,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K44">
+        <f>BDP(A44,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L44">
+        <f>BDP(A44,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M44">
+        <f>BDP(A44,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N44">
+        <f>BDP(A44,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P44">
+        <f>BDP(A44,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q44">
+        <f>BDP(A44,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R44">
+        <f>BDP(A44,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="B45">
@@ -2730,6 +4860,38 @@
         <f>BDP(A45,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J45">
+        <f>BDP(A45,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K45">
+        <f>BDP(A45,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L45">
+        <f>BDP(A45,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M45">
+        <f>BDP(A45,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N45">
+        <f>BDP(A45,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P45">
+        <f>BDP(A45,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q45">
+        <f>BDP(A45,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R45">
+        <f>BDP(A45,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="B46">
@@ -2764,6 +4926,38 @@
         <f>BDP(A46,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J46">
+        <f>BDP(A46,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K46">
+        <f>BDP(A46,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L46">
+        <f>BDP(A46,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M46">
+        <f>BDP(A46,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N46">
+        <f>BDP(A46,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P46">
+        <f>BDP(A46,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q46">
+        <f>BDP(A46,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R46">
+        <f>BDP(A46,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="B47">
@@ -2798,6 +4992,38 @@
         <f>BDP(A47,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J47">
+        <f>BDP(A47,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K47">
+        <f>BDP(A47,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L47">
+        <f>BDP(A47,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M47">
+        <f>BDP(A47,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N47">
+        <f>BDP(A47,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P47">
+        <f>BDP(A47,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q47">
+        <f>BDP(A47,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R47">
+        <f>BDP(A47,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="B48">
@@ -2832,6 +5058,38 @@
         <f>BDP(A48,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J48">
+        <f>BDP(A48,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K48">
+        <f>BDP(A48,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L48">
+        <f>BDP(A48,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M48">
+        <f>BDP(A48,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N48">
+        <f>BDP(A48,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P48">
+        <f>BDP(A48,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q48">
+        <f>BDP(A48,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R48">
+        <f>BDP(A48,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="B49">
@@ -2866,6 +5124,38 @@
         <f>BDP(A49,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J49">
+        <f>BDP(A49,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K49">
+        <f>BDP(A49,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L49">
+        <f>BDP(A49,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M49">
+        <f>BDP(A49,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N49">
+        <f>BDP(A49,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P49">
+        <f>BDP(A49,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q49">
+        <f>BDP(A49,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R49">
+        <f>BDP(A49,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="B50">
@@ -2900,6 +5190,38 @@
         <f>BDP(A50,"FIRST_CPN_DT")</f>
         <v/>
       </c>
+      <c r="J50">
+        <f>BDP(A50,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K50">
+        <f>BDP(A50,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L50">
+        <f>BDP(A50,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M50">
+        <f>BDP(A50,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N50">
+        <f>BDP(A50,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P50">
+        <f>BDP(A50,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q50">
+        <f>BDP(A50,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R50">
+        <f>BDP(A50,"RTG_FITCH")</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="B51">
@@ -2932,6 +5254,3338 @@
       </c>
       <c r="I51">
         <f>BDP(A51,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J51">
+        <f>BDP(A51,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K51">
+        <f>BDP(A51,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L51">
+        <f>BDP(A51,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M51">
+        <f>BDP(A51,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N51">
+        <f>BDP(A51,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P51">
+        <f>BDP(A51,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q51">
+        <f>BDP(A51,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R51">
+        <f>BDP(A51,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52">
+        <f>BDP(A52,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C52">
+        <f>BDP(A52,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D52">
+        <f>BDP(A52,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E52">
+        <f>BDP(A52,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F52">
+        <f>BDP(A52,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G52">
+        <f>BDP(A52,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H52">
+        <f>BDP(A52,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I52">
+        <f>BDP(A52,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J52">
+        <f>BDP(A52,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K52">
+        <f>BDP(A52,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L52">
+        <f>BDP(A52,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M52">
+        <f>BDP(A52,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N52">
+        <f>BDP(A52,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P52">
+        <f>BDP(A52,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q52">
+        <f>BDP(A52,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R52">
+        <f>BDP(A52,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53">
+        <f>BDP(A53,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C53">
+        <f>BDP(A53,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D53">
+        <f>BDP(A53,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E53">
+        <f>BDP(A53,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F53">
+        <f>BDP(A53,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G53">
+        <f>BDP(A53,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H53">
+        <f>BDP(A53,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I53">
+        <f>BDP(A53,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J53">
+        <f>BDP(A53,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K53">
+        <f>BDP(A53,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L53">
+        <f>BDP(A53,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M53">
+        <f>BDP(A53,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N53">
+        <f>BDP(A53,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P53">
+        <f>BDP(A53,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q53">
+        <f>BDP(A53,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R53">
+        <f>BDP(A53,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54">
+        <f>BDP(A54,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C54">
+        <f>BDP(A54,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D54">
+        <f>BDP(A54,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E54">
+        <f>BDP(A54,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F54">
+        <f>BDP(A54,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G54">
+        <f>BDP(A54,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H54">
+        <f>BDP(A54,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I54">
+        <f>BDP(A54,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J54">
+        <f>BDP(A54,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K54">
+        <f>BDP(A54,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L54">
+        <f>BDP(A54,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M54">
+        <f>BDP(A54,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N54">
+        <f>BDP(A54,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P54">
+        <f>BDP(A54,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q54">
+        <f>BDP(A54,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R54">
+        <f>BDP(A54,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55">
+        <f>BDP(A55,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C55">
+        <f>BDP(A55,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D55">
+        <f>BDP(A55,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E55">
+        <f>BDP(A55,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F55">
+        <f>BDP(A55,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G55">
+        <f>BDP(A55,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H55">
+        <f>BDP(A55,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I55">
+        <f>BDP(A55,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J55">
+        <f>BDP(A55,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K55">
+        <f>BDP(A55,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L55">
+        <f>BDP(A55,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M55">
+        <f>BDP(A55,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N55">
+        <f>BDP(A55,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P55">
+        <f>BDP(A55,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q55">
+        <f>BDP(A55,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R55">
+        <f>BDP(A55,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56">
+        <f>BDP(A56,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C56">
+        <f>BDP(A56,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D56">
+        <f>BDP(A56,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E56">
+        <f>BDP(A56,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F56">
+        <f>BDP(A56,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G56">
+        <f>BDP(A56,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H56">
+        <f>BDP(A56,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I56">
+        <f>BDP(A56,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J56">
+        <f>BDP(A56,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K56">
+        <f>BDP(A56,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L56">
+        <f>BDP(A56,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M56">
+        <f>BDP(A56,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N56">
+        <f>BDP(A56,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P56">
+        <f>BDP(A56,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q56">
+        <f>BDP(A56,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R56">
+        <f>BDP(A56,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57">
+        <f>BDP(A57,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C57">
+        <f>BDP(A57,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D57">
+        <f>BDP(A57,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E57">
+        <f>BDP(A57,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F57">
+        <f>BDP(A57,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G57">
+        <f>BDP(A57,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H57">
+        <f>BDP(A57,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I57">
+        <f>BDP(A57,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J57">
+        <f>BDP(A57,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K57">
+        <f>BDP(A57,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L57">
+        <f>BDP(A57,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M57">
+        <f>BDP(A57,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N57">
+        <f>BDP(A57,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P57">
+        <f>BDP(A57,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q57">
+        <f>BDP(A57,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R57">
+        <f>BDP(A57,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58">
+        <f>BDP(A58,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C58">
+        <f>BDP(A58,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D58">
+        <f>BDP(A58,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E58">
+        <f>BDP(A58,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F58">
+        <f>BDP(A58,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G58">
+        <f>BDP(A58,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H58">
+        <f>BDP(A58,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I58">
+        <f>BDP(A58,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J58">
+        <f>BDP(A58,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K58">
+        <f>BDP(A58,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L58">
+        <f>BDP(A58,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M58">
+        <f>BDP(A58,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N58">
+        <f>BDP(A58,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P58">
+        <f>BDP(A58,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q58">
+        <f>BDP(A58,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R58">
+        <f>BDP(A58,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59">
+        <f>BDP(A59,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C59">
+        <f>BDP(A59,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D59">
+        <f>BDP(A59,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E59">
+        <f>BDP(A59,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F59">
+        <f>BDP(A59,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G59">
+        <f>BDP(A59,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H59">
+        <f>BDP(A59,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I59">
+        <f>BDP(A59,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J59">
+        <f>BDP(A59,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K59">
+        <f>BDP(A59,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L59">
+        <f>BDP(A59,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M59">
+        <f>BDP(A59,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N59">
+        <f>BDP(A59,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P59">
+        <f>BDP(A59,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q59">
+        <f>BDP(A59,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R59">
+        <f>BDP(A59,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60">
+        <f>BDP(A60,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C60">
+        <f>BDP(A60,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D60">
+        <f>BDP(A60,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E60">
+        <f>BDP(A60,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F60">
+        <f>BDP(A60,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G60">
+        <f>BDP(A60,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H60">
+        <f>BDP(A60,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I60">
+        <f>BDP(A60,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J60">
+        <f>BDP(A60,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K60">
+        <f>BDP(A60,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L60">
+        <f>BDP(A60,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M60">
+        <f>BDP(A60,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N60">
+        <f>BDP(A60,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P60">
+        <f>BDP(A60,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q60">
+        <f>BDP(A60,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R60">
+        <f>BDP(A60,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61">
+        <f>BDP(A61,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C61">
+        <f>BDP(A61,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D61">
+        <f>BDP(A61,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E61">
+        <f>BDP(A61,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F61">
+        <f>BDP(A61,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G61">
+        <f>BDP(A61,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H61">
+        <f>BDP(A61,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I61">
+        <f>BDP(A61,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J61">
+        <f>BDP(A61,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K61">
+        <f>BDP(A61,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L61">
+        <f>BDP(A61,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M61">
+        <f>BDP(A61,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N61">
+        <f>BDP(A61,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P61">
+        <f>BDP(A61,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q61">
+        <f>BDP(A61,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R61">
+        <f>BDP(A61,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62">
+        <f>BDP(A62,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C62">
+        <f>BDP(A62,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D62">
+        <f>BDP(A62,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E62">
+        <f>BDP(A62,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F62">
+        <f>BDP(A62,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G62">
+        <f>BDP(A62,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H62">
+        <f>BDP(A62,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I62">
+        <f>BDP(A62,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J62">
+        <f>BDP(A62,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K62">
+        <f>BDP(A62,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L62">
+        <f>BDP(A62,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M62">
+        <f>BDP(A62,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N62">
+        <f>BDP(A62,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P62">
+        <f>BDP(A62,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q62">
+        <f>BDP(A62,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R62">
+        <f>BDP(A62,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63">
+        <f>BDP(A63,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C63">
+        <f>BDP(A63,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D63">
+        <f>BDP(A63,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E63">
+        <f>BDP(A63,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F63">
+        <f>BDP(A63,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G63">
+        <f>BDP(A63,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H63">
+        <f>BDP(A63,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I63">
+        <f>BDP(A63,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J63">
+        <f>BDP(A63,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K63">
+        <f>BDP(A63,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L63">
+        <f>BDP(A63,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M63">
+        <f>BDP(A63,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N63">
+        <f>BDP(A63,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P63">
+        <f>BDP(A63,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q63">
+        <f>BDP(A63,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R63">
+        <f>BDP(A63,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64">
+        <f>BDP(A64,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C64">
+        <f>BDP(A64,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D64">
+        <f>BDP(A64,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E64">
+        <f>BDP(A64,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F64">
+        <f>BDP(A64,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G64">
+        <f>BDP(A64,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H64">
+        <f>BDP(A64,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I64">
+        <f>BDP(A64,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J64">
+        <f>BDP(A64,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K64">
+        <f>BDP(A64,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L64">
+        <f>BDP(A64,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M64">
+        <f>BDP(A64,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N64">
+        <f>BDP(A64,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P64">
+        <f>BDP(A64,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q64">
+        <f>BDP(A64,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R64">
+        <f>BDP(A64,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65">
+        <f>BDP(A65,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C65">
+        <f>BDP(A65,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D65">
+        <f>BDP(A65,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E65">
+        <f>BDP(A65,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F65">
+        <f>BDP(A65,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G65">
+        <f>BDP(A65,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H65">
+        <f>BDP(A65,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I65">
+        <f>BDP(A65,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J65">
+        <f>BDP(A65,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K65">
+        <f>BDP(A65,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L65">
+        <f>BDP(A65,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M65">
+        <f>BDP(A65,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N65">
+        <f>BDP(A65,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P65">
+        <f>BDP(A65,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q65">
+        <f>BDP(A65,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R65">
+        <f>BDP(A65,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66">
+        <f>BDP(A66,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C66">
+        <f>BDP(A66,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D66">
+        <f>BDP(A66,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E66">
+        <f>BDP(A66,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F66">
+        <f>BDP(A66,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G66">
+        <f>BDP(A66,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H66">
+        <f>BDP(A66,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I66">
+        <f>BDP(A66,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J66">
+        <f>BDP(A66,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K66">
+        <f>BDP(A66,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L66">
+        <f>BDP(A66,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M66">
+        <f>BDP(A66,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N66">
+        <f>BDP(A66,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P66">
+        <f>BDP(A66,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q66">
+        <f>BDP(A66,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R66">
+        <f>BDP(A66,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67">
+        <f>BDP(A67,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C67">
+        <f>BDP(A67,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D67">
+        <f>BDP(A67,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E67">
+        <f>BDP(A67,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F67">
+        <f>BDP(A67,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G67">
+        <f>BDP(A67,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H67">
+        <f>BDP(A67,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I67">
+        <f>BDP(A67,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J67">
+        <f>BDP(A67,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K67">
+        <f>BDP(A67,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L67">
+        <f>BDP(A67,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M67">
+        <f>BDP(A67,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N67">
+        <f>BDP(A67,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P67">
+        <f>BDP(A67,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q67">
+        <f>BDP(A67,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R67">
+        <f>BDP(A67,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68">
+        <f>BDP(A68,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C68">
+        <f>BDP(A68,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D68">
+        <f>BDP(A68,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E68">
+        <f>BDP(A68,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F68">
+        <f>BDP(A68,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G68">
+        <f>BDP(A68,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H68">
+        <f>BDP(A68,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I68">
+        <f>BDP(A68,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J68">
+        <f>BDP(A68,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K68">
+        <f>BDP(A68,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L68">
+        <f>BDP(A68,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M68">
+        <f>BDP(A68,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N68">
+        <f>BDP(A68,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P68">
+        <f>BDP(A68,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q68">
+        <f>BDP(A68,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R68">
+        <f>BDP(A68,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69">
+        <f>BDP(A69,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C69">
+        <f>BDP(A69,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D69">
+        <f>BDP(A69,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E69">
+        <f>BDP(A69,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F69">
+        <f>BDP(A69,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G69">
+        <f>BDP(A69,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H69">
+        <f>BDP(A69,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I69">
+        <f>BDP(A69,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J69">
+        <f>BDP(A69,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K69">
+        <f>BDP(A69,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L69">
+        <f>BDP(A69,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M69">
+        <f>BDP(A69,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N69">
+        <f>BDP(A69,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P69">
+        <f>BDP(A69,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q69">
+        <f>BDP(A69,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R69">
+        <f>BDP(A69,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70">
+        <f>BDP(A70,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C70">
+        <f>BDP(A70,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D70">
+        <f>BDP(A70,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E70">
+        <f>BDP(A70,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F70">
+        <f>BDP(A70,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G70">
+        <f>BDP(A70,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H70">
+        <f>BDP(A70,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I70">
+        <f>BDP(A70,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J70">
+        <f>BDP(A70,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K70">
+        <f>BDP(A70,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L70">
+        <f>BDP(A70,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M70">
+        <f>BDP(A70,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N70">
+        <f>BDP(A70,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P70">
+        <f>BDP(A70,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q70">
+        <f>BDP(A70,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R70">
+        <f>BDP(A70,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71">
+        <f>BDP(A71,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C71">
+        <f>BDP(A71,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D71">
+        <f>BDP(A71,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E71">
+        <f>BDP(A71,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F71">
+        <f>BDP(A71,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G71">
+        <f>BDP(A71,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H71">
+        <f>BDP(A71,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I71">
+        <f>BDP(A71,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J71">
+        <f>BDP(A71,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K71">
+        <f>BDP(A71,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L71">
+        <f>BDP(A71,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M71">
+        <f>BDP(A71,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N71">
+        <f>BDP(A71,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P71">
+        <f>BDP(A71,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q71">
+        <f>BDP(A71,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R71">
+        <f>BDP(A71,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72">
+        <f>BDP(A72,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C72">
+        <f>BDP(A72,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D72">
+        <f>BDP(A72,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E72">
+        <f>BDP(A72,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F72">
+        <f>BDP(A72,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G72">
+        <f>BDP(A72,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H72">
+        <f>BDP(A72,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I72">
+        <f>BDP(A72,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J72">
+        <f>BDP(A72,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K72">
+        <f>BDP(A72,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L72">
+        <f>BDP(A72,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M72">
+        <f>BDP(A72,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N72">
+        <f>BDP(A72,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P72">
+        <f>BDP(A72,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q72">
+        <f>BDP(A72,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R72">
+        <f>BDP(A72,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73">
+        <f>BDP(A73,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C73">
+        <f>BDP(A73,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D73">
+        <f>BDP(A73,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E73">
+        <f>BDP(A73,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F73">
+        <f>BDP(A73,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G73">
+        <f>BDP(A73,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H73">
+        <f>BDP(A73,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I73">
+        <f>BDP(A73,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J73">
+        <f>BDP(A73,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K73">
+        <f>BDP(A73,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L73">
+        <f>BDP(A73,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M73">
+        <f>BDP(A73,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N73">
+        <f>BDP(A73,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P73">
+        <f>BDP(A73,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q73">
+        <f>BDP(A73,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R73">
+        <f>BDP(A73,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74">
+        <f>BDP(A74,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C74">
+        <f>BDP(A74,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D74">
+        <f>BDP(A74,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E74">
+        <f>BDP(A74,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F74">
+        <f>BDP(A74,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G74">
+        <f>BDP(A74,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H74">
+        <f>BDP(A74,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I74">
+        <f>BDP(A74,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J74">
+        <f>BDP(A74,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K74">
+        <f>BDP(A74,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L74">
+        <f>BDP(A74,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M74">
+        <f>BDP(A74,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N74">
+        <f>BDP(A74,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P74">
+        <f>BDP(A74,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q74">
+        <f>BDP(A74,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R74">
+        <f>BDP(A74,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75">
+        <f>BDP(A75,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C75">
+        <f>BDP(A75,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D75">
+        <f>BDP(A75,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E75">
+        <f>BDP(A75,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F75">
+        <f>BDP(A75,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G75">
+        <f>BDP(A75,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H75">
+        <f>BDP(A75,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I75">
+        <f>BDP(A75,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J75">
+        <f>BDP(A75,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K75">
+        <f>BDP(A75,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L75">
+        <f>BDP(A75,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M75">
+        <f>BDP(A75,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N75">
+        <f>BDP(A75,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P75">
+        <f>BDP(A75,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q75">
+        <f>BDP(A75,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R75">
+        <f>BDP(A75,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76">
+        <f>BDP(A76,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C76">
+        <f>BDP(A76,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D76">
+        <f>BDP(A76,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E76">
+        <f>BDP(A76,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F76">
+        <f>BDP(A76,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G76">
+        <f>BDP(A76,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H76">
+        <f>BDP(A76,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I76">
+        <f>BDP(A76,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J76">
+        <f>BDP(A76,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K76">
+        <f>BDP(A76,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L76">
+        <f>BDP(A76,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M76">
+        <f>BDP(A76,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N76">
+        <f>BDP(A76,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P76">
+        <f>BDP(A76,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q76">
+        <f>BDP(A76,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R76">
+        <f>BDP(A76,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77">
+        <f>BDP(A77,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C77">
+        <f>BDP(A77,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D77">
+        <f>BDP(A77,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E77">
+        <f>BDP(A77,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F77">
+        <f>BDP(A77,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G77">
+        <f>BDP(A77,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H77">
+        <f>BDP(A77,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I77">
+        <f>BDP(A77,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J77">
+        <f>BDP(A77,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K77">
+        <f>BDP(A77,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L77">
+        <f>BDP(A77,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M77">
+        <f>BDP(A77,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N77">
+        <f>BDP(A77,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P77">
+        <f>BDP(A77,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q77">
+        <f>BDP(A77,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R77">
+        <f>BDP(A77,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78">
+        <f>BDP(A78,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C78">
+        <f>BDP(A78,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D78">
+        <f>BDP(A78,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E78">
+        <f>BDP(A78,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F78">
+        <f>BDP(A78,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G78">
+        <f>BDP(A78,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H78">
+        <f>BDP(A78,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I78">
+        <f>BDP(A78,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J78">
+        <f>BDP(A78,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K78">
+        <f>BDP(A78,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L78">
+        <f>BDP(A78,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M78">
+        <f>BDP(A78,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N78">
+        <f>BDP(A78,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P78">
+        <f>BDP(A78,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q78">
+        <f>BDP(A78,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R78">
+        <f>BDP(A78,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79">
+        <f>BDP(A79,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C79">
+        <f>BDP(A79,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D79">
+        <f>BDP(A79,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E79">
+        <f>BDP(A79,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F79">
+        <f>BDP(A79,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G79">
+        <f>BDP(A79,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H79">
+        <f>BDP(A79,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I79">
+        <f>BDP(A79,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J79">
+        <f>BDP(A79,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K79">
+        <f>BDP(A79,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L79">
+        <f>BDP(A79,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M79">
+        <f>BDP(A79,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N79">
+        <f>BDP(A79,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P79">
+        <f>BDP(A79,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q79">
+        <f>BDP(A79,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R79">
+        <f>BDP(A79,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80">
+        <f>BDP(A80,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C80">
+        <f>BDP(A80,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D80">
+        <f>BDP(A80,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E80">
+        <f>BDP(A80,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F80">
+        <f>BDP(A80,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G80">
+        <f>BDP(A80,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H80">
+        <f>BDP(A80,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I80">
+        <f>BDP(A80,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J80">
+        <f>BDP(A80,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K80">
+        <f>BDP(A80,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L80">
+        <f>BDP(A80,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M80">
+        <f>BDP(A80,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N80">
+        <f>BDP(A80,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P80">
+        <f>BDP(A80,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q80">
+        <f>BDP(A80,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R80">
+        <f>BDP(A80,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81">
+        <f>BDP(A81,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C81">
+        <f>BDP(A81,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D81">
+        <f>BDP(A81,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E81">
+        <f>BDP(A81,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F81">
+        <f>BDP(A81,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G81">
+        <f>BDP(A81,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H81">
+        <f>BDP(A81,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I81">
+        <f>BDP(A81,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J81">
+        <f>BDP(A81,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K81">
+        <f>BDP(A81,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L81">
+        <f>BDP(A81,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M81">
+        <f>BDP(A81,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N81">
+        <f>BDP(A81,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P81">
+        <f>BDP(A81,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q81">
+        <f>BDP(A81,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R81">
+        <f>BDP(A81,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82">
+        <f>BDP(A82,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C82">
+        <f>BDP(A82,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D82">
+        <f>BDP(A82,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E82">
+        <f>BDP(A82,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F82">
+        <f>BDP(A82,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G82">
+        <f>BDP(A82,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H82">
+        <f>BDP(A82,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I82">
+        <f>BDP(A82,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J82">
+        <f>BDP(A82,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K82">
+        <f>BDP(A82,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L82">
+        <f>BDP(A82,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M82">
+        <f>BDP(A82,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N82">
+        <f>BDP(A82,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P82">
+        <f>BDP(A82,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q82">
+        <f>BDP(A82,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R82">
+        <f>BDP(A82,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83">
+        <f>BDP(A83,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C83">
+        <f>BDP(A83,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D83">
+        <f>BDP(A83,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E83">
+        <f>BDP(A83,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F83">
+        <f>BDP(A83,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G83">
+        <f>BDP(A83,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H83">
+        <f>BDP(A83,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I83">
+        <f>BDP(A83,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J83">
+        <f>BDP(A83,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K83">
+        <f>BDP(A83,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L83">
+        <f>BDP(A83,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M83">
+        <f>BDP(A83,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N83">
+        <f>BDP(A83,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P83">
+        <f>BDP(A83,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q83">
+        <f>BDP(A83,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R83">
+        <f>BDP(A83,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84">
+        <f>BDP(A84,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C84">
+        <f>BDP(A84,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D84">
+        <f>BDP(A84,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E84">
+        <f>BDP(A84,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F84">
+        <f>BDP(A84,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G84">
+        <f>BDP(A84,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H84">
+        <f>BDP(A84,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I84">
+        <f>BDP(A84,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J84">
+        <f>BDP(A84,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K84">
+        <f>BDP(A84,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L84">
+        <f>BDP(A84,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M84">
+        <f>BDP(A84,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N84">
+        <f>BDP(A84,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P84">
+        <f>BDP(A84,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q84">
+        <f>BDP(A84,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R84">
+        <f>BDP(A84,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85">
+        <f>BDP(A85,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C85">
+        <f>BDP(A85,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D85">
+        <f>BDP(A85,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E85">
+        <f>BDP(A85,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F85">
+        <f>BDP(A85,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G85">
+        <f>BDP(A85,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H85">
+        <f>BDP(A85,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I85">
+        <f>BDP(A85,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J85">
+        <f>BDP(A85,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K85">
+        <f>BDP(A85,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L85">
+        <f>BDP(A85,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M85">
+        <f>BDP(A85,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N85">
+        <f>BDP(A85,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P85">
+        <f>BDP(A85,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q85">
+        <f>BDP(A85,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R85">
+        <f>BDP(A85,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86">
+        <f>BDP(A86,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C86">
+        <f>BDP(A86,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D86">
+        <f>BDP(A86,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E86">
+        <f>BDP(A86,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F86">
+        <f>BDP(A86,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G86">
+        <f>BDP(A86,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H86">
+        <f>BDP(A86,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I86">
+        <f>BDP(A86,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J86">
+        <f>BDP(A86,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K86">
+        <f>BDP(A86,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L86">
+        <f>BDP(A86,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M86">
+        <f>BDP(A86,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N86">
+        <f>BDP(A86,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P86">
+        <f>BDP(A86,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q86">
+        <f>BDP(A86,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R86">
+        <f>BDP(A86,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87">
+        <f>BDP(A87,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C87">
+        <f>BDP(A87,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D87">
+        <f>BDP(A87,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E87">
+        <f>BDP(A87,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F87">
+        <f>BDP(A87,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G87">
+        <f>BDP(A87,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H87">
+        <f>BDP(A87,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I87">
+        <f>BDP(A87,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J87">
+        <f>BDP(A87,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K87">
+        <f>BDP(A87,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L87">
+        <f>BDP(A87,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M87">
+        <f>BDP(A87,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N87">
+        <f>BDP(A87,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P87">
+        <f>BDP(A87,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q87">
+        <f>BDP(A87,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R87">
+        <f>BDP(A87,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88">
+        <f>BDP(A88,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C88">
+        <f>BDP(A88,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D88">
+        <f>BDP(A88,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E88">
+        <f>BDP(A88,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F88">
+        <f>BDP(A88,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G88">
+        <f>BDP(A88,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H88">
+        <f>BDP(A88,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I88">
+        <f>BDP(A88,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J88">
+        <f>BDP(A88,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K88">
+        <f>BDP(A88,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L88">
+        <f>BDP(A88,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M88">
+        <f>BDP(A88,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N88">
+        <f>BDP(A88,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P88">
+        <f>BDP(A88,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q88">
+        <f>BDP(A88,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R88">
+        <f>BDP(A88,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89">
+        <f>BDP(A89,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C89">
+        <f>BDP(A89,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D89">
+        <f>BDP(A89,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E89">
+        <f>BDP(A89,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F89">
+        <f>BDP(A89,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G89">
+        <f>BDP(A89,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H89">
+        <f>BDP(A89,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I89">
+        <f>BDP(A89,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J89">
+        <f>BDP(A89,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K89">
+        <f>BDP(A89,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L89">
+        <f>BDP(A89,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M89">
+        <f>BDP(A89,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N89">
+        <f>BDP(A89,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P89">
+        <f>BDP(A89,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q89">
+        <f>BDP(A89,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R89">
+        <f>BDP(A89,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90">
+        <f>BDP(A90,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C90">
+        <f>BDP(A90,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D90">
+        <f>BDP(A90,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E90">
+        <f>BDP(A90,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F90">
+        <f>BDP(A90,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G90">
+        <f>BDP(A90,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H90">
+        <f>BDP(A90,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I90">
+        <f>BDP(A90,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J90">
+        <f>BDP(A90,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K90">
+        <f>BDP(A90,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L90">
+        <f>BDP(A90,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M90">
+        <f>BDP(A90,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N90">
+        <f>BDP(A90,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P90">
+        <f>BDP(A90,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q90">
+        <f>BDP(A90,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R90">
+        <f>BDP(A90,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91">
+        <f>BDP(A91,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C91">
+        <f>BDP(A91,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D91">
+        <f>BDP(A91,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E91">
+        <f>BDP(A91,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F91">
+        <f>BDP(A91,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G91">
+        <f>BDP(A91,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H91">
+        <f>BDP(A91,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I91">
+        <f>BDP(A91,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J91">
+        <f>BDP(A91,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K91">
+        <f>BDP(A91,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L91">
+        <f>BDP(A91,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M91">
+        <f>BDP(A91,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N91">
+        <f>BDP(A91,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P91">
+        <f>BDP(A91,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q91">
+        <f>BDP(A91,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R91">
+        <f>BDP(A91,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92">
+        <f>BDP(A92,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C92">
+        <f>BDP(A92,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D92">
+        <f>BDP(A92,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E92">
+        <f>BDP(A92,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F92">
+        <f>BDP(A92,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G92">
+        <f>BDP(A92,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H92">
+        <f>BDP(A92,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I92">
+        <f>BDP(A92,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J92">
+        <f>BDP(A92,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K92">
+        <f>BDP(A92,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L92">
+        <f>BDP(A92,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M92">
+        <f>BDP(A92,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N92">
+        <f>BDP(A92,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P92">
+        <f>BDP(A92,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q92">
+        <f>BDP(A92,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R92">
+        <f>BDP(A92,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93">
+        <f>BDP(A93,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C93">
+        <f>BDP(A93,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D93">
+        <f>BDP(A93,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E93">
+        <f>BDP(A93,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F93">
+        <f>BDP(A93,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G93">
+        <f>BDP(A93,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H93">
+        <f>BDP(A93,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I93">
+        <f>BDP(A93,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J93">
+        <f>BDP(A93,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K93">
+        <f>BDP(A93,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L93">
+        <f>BDP(A93,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M93">
+        <f>BDP(A93,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N93">
+        <f>BDP(A93,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P93">
+        <f>BDP(A93,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q93">
+        <f>BDP(A93,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R93">
+        <f>BDP(A93,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94">
+        <f>BDP(A94,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C94">
+        <f>BDP(A94,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D94">
+        <f>BDP(A94,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E94">
+        <f>BDP(A94,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F94">
+        <f>BDP(A94,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G94">
+        <f>BDP(A94,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H94">
+        <f>BDP(A94,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I94">
+        <f>BDP(A94,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J94">
+        <f>BDP(A94,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K94">
+        <f>BDP(A94,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L94">
+        <f>BDP(A94,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M94">
+        <f>BDP(A94,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N94">
+        <f>BDP(A94,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P94">
+        <f>BDP(A94,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q94">
+        <f>BDP(A94,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R94">
+        <f>BDP(A94,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95">
+        <f>BDP(A95,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C95">
+        <f>BDP(A95,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D95">
+        <f>BDP(A95,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E95">
+        <f>BDP(A95,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F95">
+        <f>BDP(A95,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G95">
+        <f>BDP(A95,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H95">
+        <f>BDP(A95,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I95">
+        <f>BDP(A95,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J95">
+        <f>BDP(A95,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K95">
+        <f>BDP(A95,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L95">
+        <f>BDP(A95,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M95">
+        <f>BDP(A95,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N95">
+        <f>BDP(A95,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P95">
+        <f>BDP(A95,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q95">
+        <f>BDP(A95,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R95">
+        <f>BDP(A95,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96">
+        <f>BDP(A96,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C96">
+        <f>BDP(A96,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D96">
+        <f>BDP(A96,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E96">
+        <f>BDP(A96,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F96">
+        <f>BDP(A96,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G96">
+        <f>BDP(A96,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H96">
+        <f>BDP(A96,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I96">
+        <f>BDP(A96,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J96">
+        <f>BDP(A96,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K96">
+        <f>BDP(A96,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L96">
+        <f>BDP(A96,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M96">
+        <f>BDP(A96,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N96">
+        <f>BDP(A96,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P96">
+        <f>BDP(A96,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q96">
+        <f>BDP(A96,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R96">
+        <f>BDP(A96,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97">
+        <f>BDP(A97,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C97">
+        <f>BDP(A97,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D97">
+        <f>BDP(A97,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E97">
+        <f>BDP(A97,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F97">
+        <f>BDP(A97,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G97">
+        <f>BDP(A97,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H97">
+        <f>BDP(A97,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I97">
+        <f>BDP(A97,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J97">
+        <f>BDP(A97,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K97">
+        <f>BDP(A97,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L97">
+        <f>BDP(A97,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M97">
+        <f>BDP(A97,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N97">
+        <f>BDP(A97,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P97">
+        <f>BDP(A97,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q97">
+        <f>BDP(A97,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R97">
+        <f>BDP(A97,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98">
+        <f>BDP(A98,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C98">
+        <f>BDP(A98,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D98">
+        <f>BDP(A98,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E98">
+        <f>BDP(A98,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F98">
+        <f>BDP(A98,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G98">
+        <f>BDP(A98,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H98">
+        <f>BDP(A98,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I98">
+        <f>BDP(A98,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J98">
+        <f>BDP(A98,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K98">
+        <f>BDP(A98,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L98">
+        <f>BDP(A98,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M98">
+        <f>BDP(A98,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N98">
+        <f>BDP(A98,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P98">
+        <f>BDP(A98,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q98">
+        <f>BDP(A98,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R98">
+        <f>BDP(A98,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99">
+        <f>BDP(A99,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C99">
+        <f>BDP(A99,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D99">
+        <f>BDP(A99,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E99">
+        <f>BDP(A99,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F99">
+        <f>BDP(A99,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G99">
+        <f>BDP(A99,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H99">
+        <f>BDP(A99,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I99">
+        <f>BDP(A99,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J99">
+        <f>BDP(A99,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K99">
+        <f>BDP(A99,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L99">
+        <f>BDP(A99,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M99">
+        <f>BDP(A99,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N99">
+        <f>BDP(A99,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P99">
+        <f>BDP(A99,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q99">
+        <f>BDP(A99,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R99">
+        <f>BDP(A99,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100">
+        <f>BDP(A100,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C100">
+        <f>BDP(A100,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D100">
+        <f>BDP(A100,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E100">
+        <f>BDP(A100,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F100">
+        <f>BDP(A100,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G100">
+        <f>BDP(A100,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H100">
+        <f>BDP(A100,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I100">
+        <f>BDP(A100,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J100">
+        <f>BDP(A100,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K100">
+        <f>BDP(A100,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L100">
+        <f>BDP(A100,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M100">
+        <f>BDP(A100,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N100">
+        <f>BDP(A100,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P100">
+        <f>BDP(A100,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q100">
+        <f>BDP(A100,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R100">
+        <f>BDP(A100,"RTG_FITCH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101">
+        <f>BDP(A101,"SECURITY_DES")</f>
+        <v/>
+      </c>
+      <c r="C101">
+        <f>BDP(A101,"CRNCY")</f>
+        <v/>
+      </c>
+      <c r="D101">
+        <f>BDP(A101,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="E101">
+        <f>BDP(A101,"CPN")/100</f>
+        <v/>
+      </c>
+      <c r="F101">
+        <f>BDP(A101,"CPN_FREQ")</f>
+        <v/>
+      </c>
+      <c r="G101">
+        <f>BDP(A101,"DAY_CNT_DES")</f>
+        <v/>
+      </c>
+      <c r="H101">
+        <f>BDP(A101,"MATURITY")</f>
+        <v/>
+      </c>
+      <c r="I101">
+        <f>BDP(A101,"FIRST_CPN_DT")</f>
+        <v/>
+      </c>
+      <c r="J101">
+        <f>BDP(A101,"MARKET_SECTOR_DES")</f>
+        <v/>
+      </c>
+      <c r="K101">
+        <f>BDP(A101,"ISSUER")</f>
+        <v/>
+      </c>
+      <c r="L101">
+        <f>BDP(A101,"CNTRY_OF_RISK")</f>
+        <v/>
+      </c>
+      <c r="M101">
+        <f>BDP(A101,"INDUSTRY_SECTOR")</f>
+        <v/>
+      </c>
+      <c r="N101">
+        <f>BDP(A101,"PAYMENT_RANK")</f>
+        <v/>
+      </c>
+      <c r="P101">
+        <f>BDP(A101,"RTG_SP")</f>
+        <v/>
+      </c>
+      <c r="Q101">
+        <f>BDP(A101,"RTG_MOODY")</f>
+        <v/>
+      </c>
+      <c r="R101">
+        <f>BDP(A101,"RTG_FITCH")</f>
         <v/>
       </c>
     </row>
@@ -2969,6 +8623,186 @@
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="22" customWidth="1" min="35" max="35"/>
+    <col width="14" customWidth="1" min="36" max="36"/>
+    <col width="22" customWidth="1" min="37" max="37"/>
+    <col width="14" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="39" max="39"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
+    <col width="22" customWidth="1" min="41" max="41"/>
+    <col width="14" customWidth="1" min="42" max="42"/>
+    <col width="22" customWidth="1" min="43" max="43"/>
+    <col width="14" customWidth="1" min="44" max="44"/>
+    <col width="22" customWidth="1" min="45" max="45"/>
+    <col width="14" customWidth="1" min="46" max="46"/>
+    <col width="22" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="48" max="48"/>
+    <col width="22" customWidth="1" min="49" max="49"/>
+    <col width="14" customWidth="1" min="50" max="50"/>
+    <col width="22" customWidth="1" min="51" max="51"/>
+    <col width="14" customWidth="1" min="52" max="52"/>
+    <col width="22" customWidth="1" min="53" max="53"/>
+    <col width="14" customWidth="1" min="54" max="54"/>
+    <col width="22" customWidth="1" min="55" max="55"/>
+    <col width="14" customWidth="1" min="56" max="56"/>
+    <col width="22" customWidth="1" min="57" max="57"/>
+    <col width="14" customWidth="1" min="58" max="58"/>
+    <col width="22" customWidth="1" min="59" max="59"/>
+    <col width="14" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="14" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="14" customWidth="1" min="64" max="64"/>
+    <col width="22" customWidth="1" min="65" max="65"/>
+    <col width="14" customWidth="1" min="66" max="66"/>
+    <col width="22" customWidth="1" min="67" max="67"/>
+    <col width="14" customWidth="1" min="68" max="68"/>
+    <col width="22" customWidth="1" min="69" max="69"/>
+    <col width="14" customWidth="1" min="70" max="70"/>
+    <col width="22" customWidth="1" min="71" max="71"/>
+    <col width="14" customWidth="1" min="72" max="72"/>
+    <col width="22" customWidth="1" min="73" max="73"/>
+    <col width="14" customWidth="1" min="74" max="74"/>
+    <col width="22" customWidth="1" min="75" max="75"/>
+    <col width="14" customWidth="1" min="76" max="76"/>
+    <col width="22" customWidth="1" min="77" max="77"/>
+    <col width="14" customWidth="1" min="78" max="78"/>
+    <col width="22" customWidth="1" min="79" max="79"/>
+    <col width="14" customWidth="1" min="80" max="80"/>
+    <col width="22" customWidth="1" min="81" max="81"/>
+    <col width="14" customWidth="1" min="82" max="82"/>
+    <col width="22" customWidth="1" min="83" max="83"/>
+    <col width="14" customWidth="1" min="84" max="84"/>
+    <col width="22" customWidth="1" min="85" max="85"/>
+    <col width="14" customWidth="1" min="86" max="86"/>
+    <col width="22" customWidth="1" min="87" max="87"/>
+    <col width="14" customWidth="1" min="88" max="88"/>
+    <col width="22" customWidth="1" min="89" max="89"/>
+    <col width="14" customWidth="1" min="90" max="90"/>
+    <col width="22" customWidth="1" min="91" max="91"/>
+    <col width="14" customWidth="1" min="92" max="92"/>
+    <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="14" customWidth="1" min="94" max="94"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="14" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="97" max="97"/>
+    <col width="14" customWidth="1" min="98" max="98"/>
+    <col width="22" customWidth="1" min="99" max="99"/>
+    <col width="14" customWidth="1" min="100" max="100"/>
+    <col width="22" customWidth="1" min="101" max="101"/>
+    <col width="14" customWidth="1" min="102" max="102"/>
+    <col width="22" customWidth="1" min="103" max="103"/>
+    <col width="14" customWidth="1" min="104" max="104"/>
+    <col width="22" customWidth="1" min="105" max="105"/>
+    <col width="14" customWidth="1" min="106" max="106"/>
+    <col width="22" customWidth="1" min="107" max="107"/>
+    <col width="14" customWidth="1" min="108" max="108"/>
+    <col width="22" customWidth="1" min="109" max="109"/>
+    <col width="14" customWidth="1" min="110" max="110"/>
+    <col width="22" customWidth="1" min="111" max="111"/>
+    <col width="14" customWidth="1" min="112" max="112"/>
+    <col width="22" customWidth="1" min="113" max="113"/>
+    <col width="14" customWidth="1" min="114" max="114"/>
+    <col width="22" customWidth="1" min="115" max="115"/>
+    <col width="14" customWidth="1" min="116" max="116"/>
+    <col width="22" customWidth="1" min="117" max="117"/>
+    <col width="14" customWidth="1" min="118" max="118"/>
+    <col width="22" customWidth="1" min="119" max="119"/>
+    <col width="14" customWidth="1" min="120" max="120"/>
+    <col width="22" customWidth="1" min="121" max="121"/>
+    <col width="14" customWidth="1" min="122" max="122"/>
+    <col width="22" customWidth="1" min="123" max="123"/>
+    <col width="14" customWidth="1" min="124" max="124"/>
+    <col width="22" customWidth="1" min="125" max="125"/>
+    <col width="14" customWidth="1" min="126" max="126"/>
+    <col width="22" customWidth="1" min="127" max="127"/>
+    <col width="14" customWidth="1" min="128" max="128"/>
+    <col width="22" customWidth="1" min="129" max="129"/>
+    <col width="14" customWidth="1" min="130" max="130"/>
+    <col width="22" customWidth="1" min="131" max="131"/>
+    <col width="14" customWidth="1" min="132" max="132"/>
+    <col width="22" customWidth="1" min="133" max="133"/>
+    <col width="14" customWidth="1" min="134" max="134"/>
+    <col width="22" customWidth="1" min="135" max="135"/>
+    <col width="14" customWidth="1" min="136" max="136"/>
+    <col width="22" customWidth="1" min="137" max="137"/>
+    <col width="14" customWidth="1" min="138" max="138"/>
+    <col width="22" customWidth="1" min="139" max="139"/>
+    <col width="14" customWidth="1" min="140" max="140"/>
+    <col width="22" customWidth="1" min="141" max="141"/>
+    <col width="14" customWidth="1" min="142" max="142"/>
+    <col width="22" customWidth="1" min="143" max="143"/>
+    <col width="14" customWidth="1" min="144" max="144"/>
+    <col width="22" customWidth="1" min="145" max="145"/>
+    <col width="14" customWidth="1" min="146" max="146"/>
+    <col width="22" customWidth="1" min="147" max="147"/>
+    <col width="14" customWidth="1" min="148" max="148"/>
+    <col width="22" customWidth="1" min="149" max="149"/>
+    <col width="14" customWidth="1" min="150" max="150"/>
+    <col width="22" customWidth="1" min="151" max="151"/>
+    <col width="14" customWidth="1" min="152" max="152"/>
+    <col width="22" customWidth="1" min="153" max="153"/>
+    <col width="14" customWidth="1" min="154" max="154"/>
+    <col width="22" customWidth="1" min="155" max="155"/>
+    <col width="14" customWidth="1" min="156" max="156"/>
+    <col width="22" customWidth="1" min="157" max="157"/>
+    <col width="14" customWidth="1" min="158" max="158"/>
+    <col width="22" customWidth="1" min="159" max="159"/>
+    <col width="14" customWidth="1" min="160" max="160"/>
+    <col width="22" customWidth="1" min="161" max="161"/>
+    <col width="14" customWidth="1" min="162" max="162"/>
+    <col width="22" customWidth="1" min="163" max="163"/>
+    <col width="14" customWidth="1" min="164" max="164"/>
+    <col width="22" customWidth="1" min="165" max="165"/>
+    <col width="14" customWidth="1" min="166" max="166"/>
+    <col width="22" customWidth="1" min="167" max="167"/>
+    <col width="14" customWidth="1" min="168" max="168"/>
+    <col width="22" customWidth="1" min="169" max="169"/>
+    <col width="14" customWidth="1" min="170" max="170"/>
+    <col width="22" customWidth="1" min="171" max="171"/>
+    <col width="14" customWidth="1" min="172" max="172"/>
+    <col width="22" customWidth="1" min="173" max="173"/>
+    <col width="14" customWidth="1" min="174" max="174"/>
+    <col width="22" customWidth="1" min="175" max="175"/>
+    <col width="14" customWidth="1" min="176" max="176"/>
+    <col width="22" customWidth="1" min="177" max="177"/>
+    <col width="14" customWidth="1" min="178" max="178"/>
+    <col width="22" customWidth="1" min="179" max="179"/>
+    <col width="14" customWidth="1" min="180" max="180"/>
+    <col width="22" customWidth="1" min="181" max="181"/>
+    <col width="14" customWidth="1" min="182" max="182"/>
+    <col width="22" customWidth="1" min="183" max="183"/>
+    <col width="14" customWidth="1" min="184" max="184"/>
+    <col width="22" customWidth="1" min="185" max="185"/>
+    <col width="14" customWidth="1" min="186" max="186"/>
+    <col width="22" customWidth="1" min="187" max="187"/>
+    <col width="14" customWidth="1" min="188" max="188"/>
+    <col width="22" customWidth="1" min="189" max="189"/>
+    <col width="14" customWidth="1" min="190" max="190"/>
+    <col width="22" customWidth="1" min="191" max="191"/>
+    <col width="14" customWidth="1" min="192" max="192"/>
+    <col width="22" customWidth="1" min="193" max="193"/>
+    <col width="14" customWidth="1" min="194" max="194"/>
+    <col width="22" customWidth="1" min="195" max="195"/>
+    <col width="14" customWidth="1" min="196" max="196"/>
+    <col width="22" customWidth="1" min="197" max="197"/>
+    <col width="14" customWidth="1" min="198" max="198"/>
+    <col width="22" customWidth="1" min="199" max="199"/>
+    <col width="14" customWidth="1" min="200" max="200"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/projects/02-pnl-dashboard/templates/bloomberg_prices.xlsx
+++ b/projects/02-pnl-dashboard/templates/bloomberg_prices.xlsx
@@ -1874,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R101"/>
+  <dimension ref="A1:S101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1895,6 +1895,7 @@
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1945,45 +1946,50 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>isin</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>instrument_type</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>issuer</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>country_of_risk</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>seniority</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rating_sp</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rating_moody</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>rating_fitch</t>
         </is>
@@ -2023,34 +2029,38 @@
         <v/>
       </c>
       <c r="J2">
+        <f>BDP(A2,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K2">
         <f>BDP(A2,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K2">
+      <c r="L2">
         <f>BDP(A2,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L2">
+      <c r="M2">
         <f>BDP(A2,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M2">
+      <c r="N2">
         <f>BDP(A2,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N2">
+      <c r="O2">
         <f>BDP(A2,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <f>BDP(A2,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <f>BDP(A2,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R2">
+      <c r="S2">
         <f>BDP(A2,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -2089,34 +2099,38 @@
         <v/>
       </c>
       <c r="J3">
+        <f>BDP(A3,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K3">
         <f>BDP(A3,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K3">
+      <c r="L3">
         <f>BDP(A3,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L3">
+      <c r="M3">
         <f>BDP(A3,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M3">
+      <c r="N3">
         <f>BDP(A3,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N3">
+      <c r="O3">
         <f>BDP(A3,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <f>BDP(A3,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <f>BDP(A3,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R3">
+      <c r="S3">
         <f>BDP(A3,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -2155,34 +2169,38 @@
         <v/>
       </c>
       <c r="J4">
+        <f>BDP(A4,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K4">
         <f>BDP(A4,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K4">
+      <c r="L4">
         <f>BDP(A4,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L4">
+      <c r="M4">
         <f>BDP(A4,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M4">
+      <c r="N4">
         <f>BDP(A4,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N4">
+      <c r="O4">
         <f>BDP(A4,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <f>BDP(A4,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <f>BDP(A4,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R4">
+      <c r="S4">
         <f>BDP(A4,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -2221,34 +2239,38 @@
         <v/>
       </c>
       <c r="J5">
+        <f>BDP(A5,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K5">
         <f>BDP(A5,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K5">
+      <c r="L5">
         <f>BDP(A5,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L5">
+      <c r="M5">
         <f>BDP(A5,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M5">
+      <c r="N5">
         <f>BDP(A5,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N5">
+      <c r="O5">
         <f>BDP(A5,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <f>BDP(A5,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <f>BDP(A5,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R5">
+      <c r="S5">
         <f>BDP(A5,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -2287,34 +2309,38 @@
         <v/>
       </c>
       <c r="J6">
+        <f>BDP(A6,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K6">
         <f>BDP(A6,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K6">
+      <c r="L6">
         <f>BDP(A6,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L6">
+      <c r="M6">
         <f>BDP(A6,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M6">
+      <c r="N6">
         <f>BDP(A6,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N6">
+      <c r="O6">
         <f>BDP(A6,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <f>BDP(A6,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <f>BDP(A6,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R6">
+      <c r="S6">
         <f>BDP(A6,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -2353,34 +2379,38 @@
         <v/>
       </c>
       <c r="J7">
+        <f>BDP(A7,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K7">
         <f>BDP(A7,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K7">
+      <c r="L7">
         <f>BDP(A7,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L7">
+      <c r="M7">
         <f>BDP(A7,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M7">
+      <c r="N7">
         <f>BDP(A7,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N7">
+      <c r="O7">
         <f>BDP(A7,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <f>BDP(A7,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <f>BDP(A7,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R7">
+      <c r="S7">
         <f>BDP(A7,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -2419,34 +2449,38 @@
         <v/>
       </c>
       <c r="J8">
+        <f>BDP(A8,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K8">
         <f>BDP(A8,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K8">
+      <c r="L8">
         <f>BDP(A8,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L8">
+      <c r="M8">
         <f>BDP(A8,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M8">
+      <c r="N8">
         <f>BDP(A8,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N8">
+      <c r="O8">
         <f>BDP(A8,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <f>BDP(A8,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <f>BDP(A8,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R8">
+      <c r="S8">
         <f>BDP(A8,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -2485,34 +2519,38 @@
         <v/>
       </c>
       <c r="J9">
+        <f>BDP(A9,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K9">
         <f>BDP(A9,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K9">
+      <c r="L9">
         <f>BDP(A9,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L9">
+      <c r="M9">
         <f>BDP(A9,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M9">
+      <c r="N9">
         <f>BDP(A9,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N9">
+      <c r="O9">
         <f>BDP(A9,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <f>BDP(A9,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <f>BDP(A9,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R9">
+      <c r="S9">
         <f>BDP(A9,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -2551,34 +2589,38 @@
         <v/>
       </c>
       <c r="J10">
+        <f>BDP(A10,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K10">
         <f>BDP(A10,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K10">
+      <c r="L10">
         <f>BDP(A10,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L10">
+      <c r="M10">
         <f>BDP(A10,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M10">
+      <c r="N10">
         <f>BDP(A10,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N10">
+      <c r="O10">
         <f>BDP(A10,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <f>BDP(A10,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <f>BDP(A10,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R10">
+      <c r="S10">
         <f>BDP(A10,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -2617,34 +2659,38 @@
         <v/>
       </c>
       <c r="J11">
+        <f>BDP(A11,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K11">
         <f>BDP(A11,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K11">
+      <c r="L11">
         <f>BDP(A11,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L11">
+      <c r="M11">
         <f>BDP(A11,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M11">
+      <c r="N11">
         <f>BDP(A11,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N11">
+      <c r="O11">
         <f>BDP(A11,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <f>BDP(A11,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <f>BDP(A11,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R11">
+      <c r="S11">
         <f>BDP(A11,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -2683,34 +2729,38 @@
         <v/>
       </c>
       <c r="J12">
+        <f>BDP(A12,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K12">
         <f>BDP(A12,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K12">
+      <c r="L12">
         <f>BDP(A12,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L12">
+      <c r="M12">
         <f>BDP(A12,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M12">
+      <c r="N12">
         <f>BDP(A12,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N12">
+      <c r="O12">
         <f>BDP(A12,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <f>BDP(A12,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <f>BDP(A12,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R12">
+      <c r="S12">
         <f>BDP(A12,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -2749,34 +2799,38 @@
         <v/>
       </c>
       <c r="J13">
+        <f>BDP(A13,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K13">
         <f>BDP(A13,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K13">
+      <c r="L13">
         <f>BDP(A13,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L13">
+      <c r="M13">
         <f>BDP(A13,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M13">
+      <c r="N13">
         <f>BDP(A13,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N13">
+      <c r="O13">
         <f>BDP(A13,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <f>BDP(A13,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <f>BDP(A13,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R13">
+      <c r="S13">
         <f>BDP(A13,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -2815,34 +2869,38 @@
         <v/>
       </c>
       <c r="J14">
+        <f>BDP(A14,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K14">
         <f>BDP(A14,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K14">
+      <c r="L14">
         <f>BDP(A14,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L14">
+      <c r="M14">
         <f>BDP(A14,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M14">
+      <c r="N14">
         <f>BDP(A14,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N14">
+      <c r="O14">
         <f>BDP(A14,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <f>BDP(A14,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <f>BDP(A14,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R14">
+      <c r="S14">
         <f>BDP(A14,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -2881,34 +2939,38 @@
         <v/>
       </c>
       <c r="J15">
+        <f>BDP(A15,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K15">
         <f>BDP(A15,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K15">
+      <c r="L15">
         <f>BDP(A15,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L15">
+      <c r="M15">
         <f>BDP(A15,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M15">
+      <c r="N15">
         <f>BDP(A15,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N15">
+      <c r="O15">
         <f>BDP(A15,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <f>BDP(A15,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <f>BDP(A15,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R15">
+      <c r="S15">
         <f>BDP(A15,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -2947,34 +3009,38 @@
         <v/>
       </c>
       <c r="J16">
+        <f>BDP(A16,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K16">
         <f>BDP(A16,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K16">
+      <c r="L16">
         <f>BDP(A16,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L16">
+      <c r="M16">
         <f>BDP(A16,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M16">
+      <c r="N16">
         <f>BDP(A16,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N16">
+      <c r="O16">
         <f>BDP(A16,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <f>BDP(A16,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <f>BDP(A16,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R16">
+      <c r="S16">
         <f>BDP(A16,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -3013,34 +3079,38 @@
         <v/>
       </c>
       <c r="J17">
+        <f>BDP(A17,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K17">
         <f>BDP(A17,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K17">
+      <c r="L17">
         <f>BDP(A17,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L17">
+      <c r="M17">
         <f>BDP(A17,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M17">
+      <c r="N17">
         <f>BDP(A17,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N17">
+      <c r="O17">
         <f>BDP(A17,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <f>BDP(A17,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <f>BDP(A17,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R17">
+      <c r="S17">
         <f>BDP(A17,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -3079,34 +3149,38 @@
         <v/>
       </c>
       <c r="J18">
+        <f>BDP(A18,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K18">
         <f>BDP(A18,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K18">
+      <c r="L18">
         <f>BDP(A18,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L18">
+      <c r="M18">
         <f>BDP(A18,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M18">
+      <c r="N18">
         <f>BDP(A18,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N18">
+      <c r="O18">
         <f>BDP(A18,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <f>BDP(A18,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <f>BDP(A18,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R18">
+      <c r="S18">
         <f>BDP(A18,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -3145,34 +3219,38 @@
         <v/>
       </c>
       <c r="J19">
+        <f>BDP(A19,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K19">
         <f>BDP(A19,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K19">
+      <c r="L19">
         <f>BDP(A19,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L19">
+      <c r="M19">
         <f>BDP(A19,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M19">
+      <c r="N19">
         <f>BDP(A19,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N19">
+      <c r="O19">
         <f>BDP(A19,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <f>BDP(A19,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <f>BDP(A19,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R19">
+      <c r="S19">
         <f>BDP(A19,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -3211,34 +3289,38 @@
         <v/>
       </c>
       <c r="J20">
+        <f>BDP(A20,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K20">
         <f>BDP(A20,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K20">
+      <c r="L20">
         <f>BDP(A20,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L20">
+      <c r="M20">
         <f>BDP(A20,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M20">
+      <c r="N20">
         <f>BDP(A20,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N20">
+      <c r="O20">
         <f>BDP(A20,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <f>BDP(A20,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <f>BDP(A20,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R20">
+      <c r="S20">
         <f>BDP(A20,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -3277,34 +3359,38 @@
         <v/>
       </c>
       <c r="J21">
+        <f>BDP(A21,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K21">
         <f>BDP(A21,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K21">
+      <c r="L21">
         <f>BDP(A21,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L21">
+      <c r="M21">
         <f>BDP(A21,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M21">
+      <c r="N21">
         <f>BDP(A21,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N21">
+      <c r="O21">
         <f>BDP(A21,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <f>BDP(A21,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <f>BDP(A21,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R21">
+      <c r="S21">
         <f>BDP(A21,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -3343,34 +3429,38 @@
         <v/>
       </c>
       <c r="J22">
+        <f>BDP(A22,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K22">
         <f>BDP(A22,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K22">
+      <c r="L22">
         <f>BDP(A22,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L22">
+      <c r="M22">
         <f>BDP(A22,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M22">
+      <c r="N22">
         <f>BDP(A22,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N22">
+      <c r="O22">
         <f>BDP(A22,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <f>BDP(A22,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <f>BDP(A22,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R22">
+      <c r="S22">
         <f>BDP(A22,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -3409,34 +3499,38 @@
         <v/>
       </c>
       <c r="J23">
+        <f>BDP(A23,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K23">
         <f>BDP(A23,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K23">
+      <c r="L23">
         <f>BDP(A23,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L23">
+      <c r="M23">
         <f>BDP(A23,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M23">
+      <c r="N23">
         <f>BDP(A23,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N23">
+      <c r="O23">
         <f>BDP(A23,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <f>BDP(A23,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <f>BDP(A23,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R23">
+      <c r="S23">
         <f>BDP(A23,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -3475,34 +3569,38 @@
         <v/>
       </c>
       <c r="J24">
+        <f>BDP(A24,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K24">
         <f>BDP(A24,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K24">
+      <c r="L24">
         <f>BDP(A24,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L24">
+      <c r="M24">
         <f>BDP(A24,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M24">
+      <c r="N24">
         <f>BDP(A24,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N24">
+      <c r="O24">
         <f>BDP(A24,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <f>BDP(A24,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <f>BDP(A24,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R24">
+      <c r="S24">
         <f>BDP(A24,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -3541,34 +3639,38 @@
         <v/>
       </c>
       <c r="J25">
+        <f>BDP(A25,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K25">
         <f>BDP(A25,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K25">
+      <c r="L25">
         <f>BDP(A25,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L25">
+      <c r="M25">
         <f>BDP(A25,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M25">
+      <c r="N25">
         <f>BDP(A25,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N25">
+      <c r="O25">
         <f>BDP(A25,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <f>BDP(A25,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <f>BDP(A25,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R25">
+      <c r="S25">
         <f>BDP(A25,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -3607,34 +3709,38 @@
         <v/>
       </c>
       <c r="J26">
+        <f>BDP(A26,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K26">
         <f>BDP(A26,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K26">
+      <c r="L26">
         <f>BDP(A26,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L26">
+      <c r="M26">
         <f>BDP(A26,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M26">
+      <c r="N26">
         <f>BDP(A26,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N26">
+      <c r="O26">
         <f>BDP(A26,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <f>BDP(A26,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <f>BDP(A26,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R26">
+      <c r="S26">
         <f>BDP(A26,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -3673,34 +3779,38 @@
         <v/>
       </c>
       <c r="J27">
+        <f>BDP(A27,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K27">
         <f>BDP(A27,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K27">
+      <c r="L27">
         <f>BDP(A27,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L27">
+      <c r="M27">
         <f>BDP(A27,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M27">
+      <c r="N27">
         <f>BDP(A27,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N27">
+      <c r="O27">
         <f>BDP(A27,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <f>BDP(A27,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <f>BDP(A27,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R27">
+      <c r="S27">
         <f>BDP(A27,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -3739,34 +3849,38 @@
         <v/>
       </c>
       <c r="J28">
+        <f>BDP(A28,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K28">
         <f>BDP(A28,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K28">
+      <c r="L28">
         <f>BDP(A28,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L28">
+      <c r="M28">
         <f>BDP(A28,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M28">
+      <c r="N28">
         <f>BDP(A28,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N28">
+      <c r="O28">
         <f>BDP(A28,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <f>BDP(A28,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <f>BDP(A28,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R28">
+      <c r="S28">
         <f>BDP(A28,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -3805,34 +3919,38 @@
         <v/>
       </c>
       <c r="J29">
+        <f>BDP(A29,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K29">
         <f>BDP(A29,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K29">
+      <c r="L29">
         <f>BDP(A29,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L29">
+      <c r="M29">
         <f>BDP(A29,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M29">
+      <c r="N29">
         <f>BDP(A29,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N29">
+      <c r="O29">
         <f>BDP(A29,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <f>BDP(A29,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <f>BDP(A29,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R29">
+      <c r="S29">
         <f>BDP(A29,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -3871,34 +3989,38 @@
         <v/>
       </c>
       <c r="J30">
+        <f>BDP(A30,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K30">
         <f>BDP(A30,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K30">
+      <c r="L30">
         <f>BDP(A30,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L30">
+      <c r="M30">
         <f>BDP(A30,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M30">
+      <c r="N30">
         <f>BDP(A30,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N30">
+      <c r="O30">
         <f>BDP(A30,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <f>BDP(A30,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <f>BDP(A30,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R30">
+      <c r="S30">
         <f>BDP(A30,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -3937,34 +4059,38 @@
         <v/>
       </c>
       <c r="J31">
+        <f>BDP(A31,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K31">
         <f>BDP(A31,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K31">
+      <c r="L31">
         <f>BDP(A31,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L31">
+      <c r="M31">
         <f>BDP(A31,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M31">
+      <c r="N31">
         <f>BDP(A31,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N31">
+      <c r="O31">
         <f>BDP(A31,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <f>BDP(A31,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <f>BDP(A31,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R31">
+      <c r="S31">
         <f>BDP(A31,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -4003,34 +4129,38 @@
         <v/>
       </c>
       <c r="J32">
+        <f>BDP(A32,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K32">
         <f>BDP(A32,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K32">
+      <c r="L32">
         <f>BDP(A32,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L32">
+      <c r="M32">
         <f>BDP(A32,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M32">
+      <c r="N32">
         <f>BDP(A32,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N32">
+      <c r="O32">
         <f>BDP(A32,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <f>BDP(A32,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <f>BDP(A32,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R32">
+      <c r="S32">
         <f>BDP(A32,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -4069,34 +4199,38 @@
         <v/>
       </c>
       <c r="J33">
+        <f>BDP(A33,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K33">
         <f>BDP(A33,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K33">
+      <c r="L33">
         <f>BDP(A33,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L33">
+      <c r="M33">
         <f>BDP(A33,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M33">
+      <c r="N33">
         <f>BDP(A33,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N33">
+      <c r="O33">
         <f>BDP(A33,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <f>BDP(A33,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <f>BDP(A33,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R33">
+      <c r="S33">
         <f>BDP(A33,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -4135,34 +4269,38 @@
         <v/>
       </c>
       <c r="J34">
+        <f>BDP(A34,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K34">
         <f>BDP(A34,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K34">
+      <c r="L34">
         <f>BDP(A34,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L34">
+      <c r="M34">
         <f>BDP(A34,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M34">
+      <c r="N34">
         <f>BDP(A34,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N34">
+      <c r="O34">
         <f>BDP(A34,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <f>BDP(A34,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <f>BDP(A34,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R34">
+      <c r="S34">
         <f>BDP(A34,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -4201,34 +4339,38 @@
         <v/>
       </c>
       <c r="J35">
+        <f>BDP(A35,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K35">
         <f>BDP(A35,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K35">
+      <c r="L35">
         <f>BDP(A35,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L35">
+      <c r="M35">
         <f>BDP(A35,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M35">
+      <c r="N35">
         <f>BDP(A35,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N35">
+      <c r="O35">
         <f>BDP(A35,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <f>BDP(A35,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q35">
+      <c r="R35">
         <f>BDP(A35,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R35">
+      <c r="S35">
         <f>BDP(A35,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -4267,34 +4409,38 @@
         <v/>
       </c>
       <c r="J36">
+        <f>BDP(A36,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K36">
         <f>BDP(A36,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K36">
+      <c r="L36">
         <f>BDP(A36,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L36">
+      <c r="M36">
         <f>BDP(A36,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M36">
+      <c r="N36">
         <f>BDP(A36,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N36">
+      <c r="O36">
         <f>BDP(A36,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <f>BDP(A36,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q36">
+      <c r="R36">
         <f>BDP(A36,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R36">
+      <c r="S36">
         <f>BDP(A36,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -4333,34 +4479,38 @@
         <v/>
       </c>
       <c r="J37">
+        <f>BDP(A37,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K37">
         <f>BDP(A37,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K37">
+      <c r="L37">
         <f>BDP(A37,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L37">
+      <c r="M37">
         <f>BDP(A37,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M37">
+      <c r="N37">
         <f>BDP(A37,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N37">
+      <c r="O37">
         <f>BDP(A37,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P37">
+      <c r="Q37">
         <f>BDP(A37,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q37">
+      <c r="R37">
         <f>BDP(A37,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R37">
+      <c r="S37">
         <f>BDP(A37,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -4399,34 +4549,38 @@
         <v/>
       </c>
       <c r="J38">
+        <f>BDP(A38,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K38">
         <f>BDP(A38,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K38">
+      <c r="L38">
         <f>BDP(A38,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L38">
+      <c r="M38">
         <f>BDP(A38,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M38">
+      <c r="N38">
         <f>BDP(A38,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N38">
+      <c r="O38">
         <f>BDP(A38,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P38">
+      <c r="Q38">
         <f>BDP(A38,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q38">
+      <c r="R38">
         <f>BDP(A38,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R38">
+      <c r="S38">
         <f>BDP(A38,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -4465,34 +4619,38 @@
         <v/>
       </c>
       <c r="J39">
+        <f>BDP(A39,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K39">
         <f>BDP(A39,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K39">
+      <c r="L39">
         <f>BDP(A39,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L39">
+      <c r="M39">
         <f>BDP(A39,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M39">
+      <c r="N39">
         <f>BDP(A39,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N39">
+      <c r="O39">
         <f>BDP(A39,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P39">
+      <c r="Q39">
         <f>BDP(A39,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q39">
+      <c r="R39">
         <f>BDP(A39,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R39">
+      <c r="S39">
         <f>BDP(A39,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -4531,34 +4689,38 @@
         <v/>
       </c>
       <c r="J40">
+        <f>BDP(A40,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K40">
         <f>BDP(A40,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K40">
+      <c r="L40">
         <f>BDP(A40,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L40">
+      <c r="M40">
         <f>BDP(A40,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M40">
+      <c r="N40">
         <f>BDP(A40,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N40">
+      <c r="O40">
         <f>BDP(A40,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P40">
+      <c r="Q40">
         <f>BDP(A40,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q40">
+      <c r="R40">
         <f>BDP(A40,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R40">
+      <c r="S40">
         <f>BDP(A40,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -4597,34 +4759,38 @@
         <v/>
       </c>
       <c r="J41">
+        <f>BDP(A41,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K41">
         <f>BDP(A41,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K41">
+      <c r="L41">
         <f>BDP(A41,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L41">
+      <c r="M41">
         <f>BDP(A41,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M41">
+      <c r="N41">
         <f>BDP(A41,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N41">
+      <c r="O41">
         <f>BDP(A41,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P41">
+      <c r="Q41">
         <f>BDP(A41,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q41">
+      <c r="R41">
         <f>BDP(A41,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R41">
+      <c r="S41">
         <f>BDP(A41,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -4663,34 +4829,38 @@
         <v/>
       </c>
       <c r="J42">
+        <f>BDP(A42,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K42">
         <f>BDP(A42,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K42">
+      <c r="L42">
         <f>BDP(A42,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L42">
+      <c r="M42">
         <f>BDP(A42,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M42">
+      <c r="N42">
         <f>BDP(A42,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N42">
+      <c r="O42">
         <f>BDP(A42,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P42">
+      <c r="Q42">
         <f>BDP(A42,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q42">
+      <c r="R42">
         <f>BDP(A42,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R42">
+      <c r="S42">
         <f>BDP(A42,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -4729,34 +4899,38 @@
         <v/>
       </c>
       <c r="J43">
+        <f>BDP(A43,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K43">
         <f>BDP(A43,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K43">
+      <c r="L43">
         <f>BDP(A43,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L43">
+      <c r="M43">
         <f>BDP(A43,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M43">
+      <c r="N43">
         <f>BDP(A43,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N43">
+      <c r="O43">
         <f>BDP(A43,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P43">
+      <c r="Q43">
         <f>BDP(A43,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q43">
+      <c r="R43">
         <f>BDP(A43,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R43">
+      <c r="S43">
         <f>BDP(A43,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -4795,34 +4969,38 @@
         <v/>
       </c>
       <c r="J44">
+        <f>BDP(A44,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K44">
         <f>BDP(A44,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K44">
+      <c r="L44">
         <f>BDP(A44,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L44">
+      <c r="M44">
         <f>BDP(A44,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M44">
+      <c r="N44">
         <f>BDP(A44,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N44">
+      <c r="O44">
         <f>BDP(A44,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P44">
+      <c r="Q44">
         <f>BDP(A44,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q44">
+      <c r="R44">
         <f>BDP(A44,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R44">
+      <c r="S44">
         <f>BDP(A44,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -4861,34 +5039,38 @@
         <v/>
       </c>
       <c r="J45">
+        <f>BDP(A45,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K45">
         <f>BDP(A45,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K45">
+      <c r="L45">
         <f>BDP(A45,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L45">
+      <c r="M45">
         <f>BDP(A45,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M45">
+      <c r="N45">
         <f>BDP(A45,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N45">
+      <c r="O45">
         <f>BDP(A45,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P45">
+      <c r="Q45">
         <f>BDP(A45,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q45">
+      <c r="R45">
         <f>BDP(A45,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R45">
+      <c r="S45">
         <f>BDP(A45,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -4927,34 +5109,38 @@
         <v/>
       </c>
       <c r="J46">
+        <f>BDP(A46,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K46">
         <f>BDP(A46,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K46">
+      <c r="L46">
         <f>BDP(A46,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L46">
+      <c r="M46">
         <f>BDP(A46,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M46">
+      <c r="N46">
         <f>BDP(A46,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N46">
+      <c r="O46">
         <f>BDP(A46,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P46">
+      <c r="Q46">
         <f>BDP(A46,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q46">
+      <c r="R46">
         <f>BDP(A46,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R46">
+      <c r="S46">
         <f>BDP(A46,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -4993,34 +5179,38 @@
         <v/>
       </c>
       <c r="J47">
+        <f>BDP(A47,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K47">
         <f>BDP(A47,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K47">
+      <c r="L47">
         <f>BDP(A47,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L47">
+      <c r="M47">
         <f>BDP(A47,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M47">
+      <c r="N47">
         <f>BDP(A47,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N47">
+      <c r="O47">
         <f>BDP(A47,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P47">
+      <c r="Q47">
         <f>BDP(A47,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q47">
+      <c r="R47">
         <f>BDP(A47,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R47">
+      <c r="S47">
         <f>BDP(A47,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -5059,34 +5249,38 @@
         <v/>
       </c>
       <c r="J48">
+        <f>BDP(A48,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K48">
         <f>BDP(A48,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K48">
+      <c r="L48">
         <f>BDP(A48,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L48">
+      <c r="M48">
         <f>BDP(A48,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M48">
+      <c r="N48">
         <f>BDP(A48,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N48">
+      <c r="O48">
         <f>BDP(A48,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P48">
+      <c r="Q48">
         <f>BDP(A48,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q48">
+      <c r="R48">
         <f>BDP(A48,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R48">
+      <c r="S48">
         <f>BDP(A48,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -5125,34 +5319,38 @@
         <v/>
       </c>
       <c r="J49">
+        <f>BDP(A49,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K49">
         <f>BDP(A49,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K49">
+      <c r="L49">
         <f>BDP(A49,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L49">
+      <c r="M49">
         <f>BDP(A49,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M49">
+      <c r="N49">
         <f>BDP(A49,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N49">
+      <c r="O49">
         <f>BDP(A49,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P49">
+      <c r="Q49">
         <f>BDP(A49,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q49">
+      <c r="R49">
         <f>BDP(A49,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R49">
+      <c r="S49">
         <f>BDP(A49,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -5191,34 +5389,38 @@
         <v/>
       </c>
       <c r="J50">
+        <f>BDP(A50,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K50">
         <f>BDP(A50,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K50">
+      <c r="L50">
         <f>BDP(A50,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L50">
+      <c r="M50">
         <f>BDP(A50,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M50">
+      <c r="N50">
         <f>BDP(A50,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N50">
+      <c r="O50">
         <f>BDP(A50,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P50">
+      <c r="Q50">
         <f>BDP(A50,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q50">
+      <c r="R50">
         <f>BDP(A50,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R50">
+      <c r="S50">
         <f>BDP(A50,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -5257,34 +5459,38 @@
         <v/>
       </c>
       <c r="J51">
+        <f>BDP(A51,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K51">
         <f>BDP(A51,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K51">
+      <c r="L51">
         <f>BDP(A51,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L51">
+      <c r="M51">
         <f>BDP(A51,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M51">
+      <c r="N51">
         <f>BDP(A51,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N51">
+      <c r="O51">
         <f>BDP(A51,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P51">
+      <c r="Q51">
         <f>BDP(A51,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q51">
+      <c r="R51">
         <f>BDP(A51,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R51">
+      <c r="S51">
         <f>BDP(A51,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -5323,34 +5529,38 @@
         <v/>
       </c>
       <c r="J52">
+        <f>BDP(A52,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K52">
         <f>BDP(A52,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K52">
+      <c r="L52">
         <f>BDP(A52,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L52">
+      <c r="M52">
         <f>BDP(A52,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M52">
+      <c r="N52">
         <f>BDP(A52,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N52">
+      <c r="O52">
         <f>BDP(A52,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P52">
+      <c r="Q52">
         <f>BDP(A52,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q52">
+      <c r="R52">
         <f>BDP(A52,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R52">
+      <c r="S52">
         <f>BDP(A52,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -5389,34 +5599,38 @@
         <v/>
       </c>
       <c r="J53">
+        <f>BDP(A53,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K53">
         <f>BDP(A53,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K53">
+      <c r="L53">
         <f>BDP(A53,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L53">
+      <c r="M53">
         <f>BDP(A53,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M53">
+      <c r="N53">
         <f>BDP(A53,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N53">
+      <c r="O53">
         <f>BDP(A53,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P53">
+      <c r="Q53">
         <f>BDP(A53,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q53">
+      <c r="R53">
         <f>BDP(A53,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R53">
+      <c r="S53">
         <f>BDP(A53,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -5455,34 +5669,38 @@
         <v/>
       </c>
       <c r="J54">
+        <f>BDP(A54,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K54">
         <f>BDP(A54,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K54">
+      <c r="L54">
         <f>BDP(A54,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L54">
+      <c r="M54">
         <f>BDP(A54,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M54">
+      <c r="N54">
         <f>BDP(A54,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N54">
+      <c r="O54">
         <f>BDP(A54,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P54">
+      <c r="Q54">
         <f>BDP(A54,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q54">
+      <c r="R54">
         <f>BDP(A54,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R54">
+      <c r="S54">
         <f>BDP(A54,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -5521,34 +5739,38 @@
         <v/>
       </c>
       <c r="J55">
+        <f>BDP(A55,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K55">
         <f>BDP(A55,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K55">
+      <c r="L55">
         <f>BDP(A55,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L55">
+      <c r="M55">
         <f>BDP(A55,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M55">
+      <c r="N55">
         <f>BDP(A55,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N55">
+      <c r="O55">
         <f>BDP(A55,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P55">
+      <c r="Q55">
         <f>BDP(A55,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q55">
+      <c r="R55">
         <f>BDP(A55,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R55">
+      <c r="S55">
         <f>BDP(A55,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -5587,34 +5809,38 @@
         <v/>
       </c>
       <c r="J56">
+        <f>BDP(A56,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K56">
         <f>BDP(A56,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K56">
+      <c r="L56">
         <f>BDP(A56,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L56">
+      <c r="M56">
         <f>BDP(A56,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M56">
+      <c r="N56">
         <f>BDP(A56,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N56">
+      <c r="O56">
         <f>BDP(A56,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P56">
+      <c r="Q56">
         <f>BDP(A56,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q56">
+      <c r="R56">
         <f>BDP(A56,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R56">
+      <c r="S56">
         <f>BDP(A56,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -5653,34 +5879,38 @@
         <v/>
       </c>
       <c r="J57">
+        <f>BDP(A57,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K57">
         <f>BDP(A57,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K57">
+      <c r="L57">
         <f>BDP(A57,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L57">
+      <c r="M57">
         <f>BDP(A57,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M57">
+      <c r="N57">
         <f>BDP(A57,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N57">
+      <c r="O57">
         <f>BDP(A57,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P57">
+      <c r="Q57">
         <f>BDP(A57,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q57">
+      <c r="R57">
         <f>BDP(A57,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R57">
+      <c r="S57">
         <f>BDP(A57,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -5719,34 +5949,38 @@
         <v/>
       </c>
       <c r="J58">
+        <f>BDP(A58,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K58">
         <f>BDP(A58,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K58">
+      <c r="L58">
         <f>BDP(A58,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L58">
+      <c r="M58">
         <f>BDP(A58,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M58">
+      <c r="N58">
         <f>BDP(A58,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N58">
+      <c r="O58">
         <f>BDP(A58,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P58">
+      <c r="Q58">
         <f>BDP(A58,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q58">
+      <c r="R58">
         <f>BDP(A58,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R58">
+      <c r="S58">
         <f>BDP(A58,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -5785,34 +6019,38 @@
         <v/>
       </c>
       <c r="J59">
+        <f>BDP(A59,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K59">
         <f>BDP(A59,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K59">
+      <c r="L59">
         <f>BDP(A59,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L59">
+      <c r="M59">
         <f>BDP(A59,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M59">
+      <c r="N59">
         <f>BDP(A59,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N59">
+      <c r="O59">
         <f>BDP(A59,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P59">
+      <c r="Q59">
         <f>BDP(A59,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q59">
+      <c r="R59">
         <f>BDP(A59,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R59">
+      <c r="S59">
         <f>BDP(A59,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -5851,34 +6089,38 @@
         <v/>
       </c>
       <c r="J60">
+        <f>BDP(A60,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K60">
         <f>BDP(A60,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K60">
+      <c r="L60">
         <f>BDP(A60,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L60">
+      <c r="M60">
         <f>BDP(A60,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M60">
+      <c r="N60">
         <f>BDP(A60,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N60">
+      <c r="O60">
         <f>BDP(A60,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P60">
+      <c r="Q60">
         <f>BDP(A60,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q60">
+      <c r="R60">
         <f>BDP(A60,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R60">
+      <c r="S60">
         <f>BDP(A60,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -5917,34 +6159,38 @@
         <v/>
       </c>
       <c r="J61">
+        <f>BDP(A61,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K61">
         <f>BDP(A61,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K61">
+      <c r="L61">
         <f>BDP(A61,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L61">
+      <c r="M61">
         <f>BDP(A61,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M61">
+      <c r="N61">
         <f>BDP(A61,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N61">
+      <c r="O61">
         <f>BDP(A61,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P61">
+      <c r="Q61">
         <f>BDP(A61,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q61">
+      <c r="R61">
         <f>BDP(A61,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R61">
+      <c r="S61">
         <f>BDP(A61,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -5983,34 +6229,38 @@
         <v/>
       </c>
       <c r="J62">
+        <f>BDP(A62,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K62">
         <f>BDP(A62,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K62">
+      <c r="L62">
         <f>BDP(A62,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L62">
+      <c r="M62">
         <f>BDP(A62,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M62">
+      <c r="N62">
         <f>BDP(A62,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N62">
+      <c r="O62">
         <f>BDP(A62,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P62">
+      <c r="Q62">
         <f>BDP(A62,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q62">
+      <c r="R62">
         <f>BDP(A62,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R62">
+      <c r="S62">
         <f>BDP(A62,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -6049,34 +6299,38 @@
         <v/>
       </c>
       <c r="J63">
+        <f>BDP(A63,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K63">
         <f>BDP(A63,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K63">
+      <c r="L63">
         <f>BDP(A63,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L63">
+      <c r="M63">
         <f>BDP(A63,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M63">
+      <c r="N63">
         <f>BDP(A63,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N63">
+      <c r="O63">
         <f>BDP(A63,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P63">
+      <c r="Q63">
         <f>BDP(A63,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q63">
+      <c r="R63">
         <f>BDP(A63,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R63">
+      <c r="S63">
         <f>BDP(A63,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -6115,34 +6369,38 @@
         <v/>
       </c>
       <c r="J64">
+        <f>BDP(A64,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K64">
         <f>BDP(A64,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K64">
+      <c r="L64">
         <f>BDP(A64,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L64">
+      <c r="M64">
         <f>BDP(A64,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M64">
+      <c r="N64">
         <f>BDP(A64,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N64">
+      <c r="O64">
         <f>BDP(A64,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P64">
+      <c r="Q64">
         <f>BDP(A64,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q64">
+      <c r="R64">
         <f>BDP(A64,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R64">
+      <c r="S64">
         <f>BDP(A64,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -6181,34 +6439,38 @@
         <v/>
       </c>
       <c r="J65">
+        <f>BDP(A65,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K65">
         <f>BDP(A65,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K65">
+      <c r="L65">
         <f>BDP(A65,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L65">
+      <c r="M65">
         <f>BDP(A65,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M65">
+      <c r="N65">
         <f>BDP(A65,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N65">
+      <c r="O65">
         <f>BDP(A65,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P65">
+      <c r="Q65">
         <f>BDP(A65,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q65">
+      <c r="R65">
         <f>BDP(A65,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R65">
+      <c r="S65">
         <f>BDP(A65,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -6247,34 +6509,38 @@
         <v/>
       </c>
       <c r="J66">
+        <f>BDP(A66,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K66">
         <f>BDP(A66,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K66">
+      <c r="L66">
         <f>BDP(A66,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L66">
+      <c r="M66">
         <f>BDP(A66,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M66">
+      <c r="N66">
         <f>BDP(A66,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N66">
+      <c r="O66">
         <f>BDP(A66,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P66">
+      <c r="Q66">
         <f>BDP(A66,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q66">
+      <c r="R66">
         <f>BDP(A66,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R66">
+      <c r="S66">
         <f>BDP(A66,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -6313,34 +6579,38 @@
         <v/>
       </c>
       <c r="J67">
+        <f>BDP(A67,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K67">
         <f>BDP(A67,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K67">
+      <c r="L67">
         <f>BDP(A67,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L67">
+      <c r="M67">
         <f>BDP(A67,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M67">
+      <c r="N67">
         <f>BDP(A67,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N67">
+      <c r="O67">
         <f>BDP(A67,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P67">
+      <c r="Q67">
         <f>BDP(A67,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q67">
+      <c r="R67">
         <f>BDP(A67,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R67">
+      <c r="S67">
         <f>BDP(A67,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -6379,34 +6649,38 @@
         <v/>
       </c>
       <c r="J68">
+        <f>BDP(A68,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K68">
         <f>BDP(A68,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K68">
+      <c r="L68">
         <f>BDP(A68,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L68">
+      <c r="M68">
         <f>BDP(A68,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M68">
+      <c r="N68">
         <f>BDP(A68,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N68">
+      <c r="O68">
         <f>BDP(A68,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P68">
+      <c r="Q68">
         <f>BDP(A68,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q68">
+      <c r="R68">
         <f>BDP(A68,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R68">
+      <c r="S68">
         <f>BDP(A68,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -6445,34 +6719,38 @@
         <v/>
       </c>
       <c r="J69">
+        <f>BDP(A69,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K69">
         <f>BDP(A69,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K69">
+      <c r="L69">
         <f>BDP(A69,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L69">
+      <c r="M69">
         <f>BDP(A69,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M69">
+      <c r="N69">
         <f>BDP(A69,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N69">
+      <c r="O69">
         <f>BDP(A69,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P69">
+      <c r="Q69">
         <f>BDP(A69,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q69">
+      <c r="R69">
         <f>BDP(A69,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R69">
+      <c r="S69">
         <f>BDP(A69,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -6511,34 +6789,38 @@
         <v/>
       </c>
       <c r="J70">
+        <f>BDP(A70,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K70">
         <f>BDP(A70,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K70">
+      <c r="L70">
         <f>BDP(A70,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L70">
+      <c r="M70">
         <f>BDP(A70,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M70">
+      <c r="N70">
         <f>BDP(A70,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N70">
+      <c r="O70">
         <f>BDP(A70,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P70">
+      <c r="Q70">
         <f>BDP(A70,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q70">
+      <c r="R70">
         <f>BDP(A70,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R70">
+      <c r="S70">
         <f>BDP(A70,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -6577,34 +6859,38 @@
         <v/>
       </c>
       <c r="J71">
+        <f>BDP(A71,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K71">
         <f>BDP(A71,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K71">
+      <c r="L71">
         <f>BDP(A71,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L71">
+      <c r="M71">
         <f>BDP(A71,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M71">
+      <c r="N71">
         <f>BDP(A71,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N71">
+      <c r="O71">
         <f>BDP(A71,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P71">
+      <c r="Q71">
         <f>BDP(A71,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q71">
+      <c r="R71">
         <f>BDP(A71,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R71">
+      <c r="S71">
         <f>BDP(A71,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -6643,34 +6929,38 @@
         <v/>
       </c>
       <c r="J72">
+        <f>BDP(A72,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K72">
         <f>BDP(A72,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K72">
+      <c r="L72">
         <f>BDP(A72,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L72">
+      <c r="M72">
         <f>BDP(A72,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M72">
+      <c r="N72">
         <f>BDP(A72,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N72">
+      <c r="O72">
         <f>BDP(A72,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P72">
+      <c r="Q72">
         <f>BDP(A72,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q72">
+      <c r="R72">
         <f>BDP(A72,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R72">
+      <c r="S72">
         <f>BDP(A72,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -6709,34 +6999,38 @@
         <v/>
       </c>
       <c r="J73">
+        <f>BDP(A73,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K73">
         <f>BDP(A73,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K73">
+      <c r="L73">
         <f>BDP(A73,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L73">
+      <c r="M73">
         <f>BDP(A73,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M73">
+      <c r="N73">
         <f>BDP(A73,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N73">
+      <c r="O73">
         <f>BDP(A73,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P73">
+      <c r="Q73">
         <f>BDP(A73,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q73">
+      <c r="R73">
         <f>BDP(A73,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R73">
+      <c r="S73">
         <f>BDP(A73,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -6775,34 +7069,38 @@
         <v/>
       </c>
       <c r="J74">
+        <f>BDP(A74,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K74">
         <f>BDP(A74,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K74">
+      <c r="L74">
         <f>BDP(A74,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L74">
+      <c r="M74">
         <f>BDP(A74,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M74">
+      <c r="N74">
         <f>BDP(A74,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N74">
+      <c r="O74">
         <f>BDP(A74,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P74">
+      <c r="Q74">
         <f>BDP(A74,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q74">
+      <c r="R74">
         <f>BDP(A74,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R74">
+      <c r="S74">
         <f>BDP(A74,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -6841,34 +7139,38 @@
         <v/>
       </c>
       <c r="J75">
+        <f>BDP(A75,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K75">
         <f>BDP(A75,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K75">
+      <c r="L75">
         <f>BDP(A75,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L75">
+      <c r="M75">
         <f>BDP(A75,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M75">
+      <c r="N75">
         <f>BDP(A75,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N75">
+      <c r="O75">
         <f>BDP(A75,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P75">
+      <c r="Q75">
         <f>BDP(A75,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q75">
+      <c r="R75">
         <f>BDP(A75,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R75">
+      <c r="S75">
         <f>BDP(A75,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -6907,34 +7209,38 @@
         <v/>
       </c>
       <c r="J76">
+        <f>BDP(A76,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K76">
         <f>BDP(A76,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K76">
+      <c r="L76">
         <f>BDP(A76,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L76">
+      <c r="M76">
         <f>BDP(A76,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M76">
+      <c r="N76">
         <f>BDP(A76,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N76">
+      <c r="O76">
         <f>BDP(A76,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P76">
+      <c r="Q76">
         <f>BDP(A76,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q76">
+      <c r="R76">
         <f>BDP(A76,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R76">
+      <c r="S76">
         <f>BDP(A76,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -6973,34 +7279,38 @@
         <v/>
       </c>
       <c r="J77">
+        <f>BDP(A77,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K77">
         <f>BDP(A77,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K77">
+      <c r="L77">
         <f>BDP(A77,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L77">
+      <c r="M77">
         <f>BDP(A77,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M77">
+      <c r="N77">
         <f>BDP(A77,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N77">
+      <c r="O77">
         <f>BDP(A77,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P77">
+      <c r="Q77">
         <f>BDP(A77,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q77">
+      <c r="R77">
         <f>BDP(A77,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R77">
+      <c r="S77">
         <f>BDP(A77,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -7039,34 +7349,38 @@
         <v/>
       </c>
       <c r="J78">
+        <f>BDP(A78,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K78">
         <f>BDP(A78,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K78">
+      <c r="L78">
         <f>BDP(A78,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L78">
+      <c r="M78">
         <f>BDP(A78,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M78">
+      <c r="N78">
         <f>BDP(A78,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N78">
+      <c r="O78">
         <f>BDP(A78,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P78">
+      <c r="Q78">
         <f>BDP(A78,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q78">
+      <c r="R78">
         <f>BDP(A78,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R78">
+      <c r="S78">
         <f>BDP(A78,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -7105,34 +7419,38 @@
         <v/>
       </c>
       <c r="J79">
+        <f>BDP(A79,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K79">
         <f>BDP(A79,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K79">
+      <c r="L79">
         <f>BDP(A79,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L79">
+      <c r="M79">
         <f>BDP(A79,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M79">
+      <c r="N79">
         <f>BDP(A79,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N79">
+      <c r="O79">
         <f>BDP(A79,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P79">
+      <c r="Q79">
         <f>BDP(A79,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q79">
+      <c r="R79">
         <f>BDP(A79,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R79">
+      <c r="S79">
         <f>BDP(A79,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -7171,34 +7489,38 @@
         <v/>
       </c>
       <c r="J80">
+        <f>BDP(A80,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K80">
         <f>BDP(A80,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K80">
+      <c r="L80">
         <f>BDP(A80,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L80">
+      <c r="M80">
         <f>BDP(A80,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M80">
+      <c r="N80">
         <f>BDP(A80,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N80">
+      <c r="O80">
         <f>BDP(A80,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P80">
+      <c r="Q80">
         <f>BDP(A80,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q80">
+      <c r="R80">
         <f>BDP(A80,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R80">
+      <c r="S80">
         <f>BDP(A80,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -7237,34 +7559,38 @@
         <v/>
       </c>
       <c r="J81">
+        <f>BDP(A81,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K81">
         <f>BDP(A81,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K81">
+      <c r="L81">
         <f>BDP(A81,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L81">
+      <c r="M81">
         <f>BDP(A81,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M81">
+      <c r="N81">
         <f>BDP(A81,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N81">
+      <c r="O81">
         <f>BDP(A81,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P81">
+      <c r="Q81">
         <f>BDP(A81,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q81">
+      <c r="R81">
         <f>BDP(A81,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R81">
+      <c r="S81">
         <f>BDP(A81,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -7303,34 +7629,38 @@
         <v/>
       </c>
       <c r="J82">
+        <f>BDP(A82,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K82">
         <f>BDP(A82,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K82">
+      <c r="L82">
         <f>BDP(A82,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L82">
+      <c r="M82">
         <f>BDP(A82,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M82">
+      <c r="N82">
         <f>BDP(A82,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N82">
+      <c r="O82">
         <f>BDP(A82,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P82">
+      <c r="Q82">
         <f>BDP(A82,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q82">
+      <c r="R82">
         <f>BDP(A82,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R82">
+      <c r="S82">
         <f>BDP(A82,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -7369,34 +7699,38 @@
         <v/>
       </c>
       <c r="J83">
+        <f>BDP(A83,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K83">
         <f>BDP(A83,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K83">
+      <c r="L83">
         <f>BDP(A83,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L83">
+      <c r="M83">
         <f>BDP(A83,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M83">
+      <c r="N83">
         <f>BDP(A83,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N83">
+      <c r="O83">
         <f>BDP(A83,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P83">
+      <c r="Q83">
         <f>BDP(A83,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q83">
+      <c r="R83">
         <f>BDP(A83,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R83">
+      <c r="S83">
         <f>BDP(A83,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -7435,34 +7769,38 @@
         <v/>
       </c>
       <c r="J84">
+        <f>BDP(A84,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K84">
         <f>BDP(A84,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K84">
+      <c r="L84">
         <f>BDP(A84,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L84">
+      <c r="M84">
         <f>BDP(A84,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M84">
+      <c r="N84">
         <f>BDP(A84,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N84">
+      <c r="O84">
         <f>BDP(A84,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P84">
+      <c r="Q84">
         <f>BDP(A84,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q84">
+      <c r="R84">
         <f>BDP(A84,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R84">
+      <c r="S84">
         <f>BDP(A84,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -7501,34 +7839,38 @@
         <v/>
       </c>
       <c r="J85">
+        <f>BDP(A85,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K85">
         <f>BDP(A85,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K85">
+      <c r="L85">
         <f>BDP(A85,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L85">
+      <c r="M85">
         <f>BDP(A85,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M85">
+      <c r="N85">
         <f>BDP(A85,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N85">
+      <c r="O85">
         <f>BDP(A85,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P85">
+      <c r="Q85">
         <f>BDP(A85,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q85">
+      <c r="R85">
         <f>BDP(A85,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R85">
+      <c r="S85">
         <f>BDP(A85,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -7567,34 +7909,38 @@
         <v/>
       </c>
       <c r="J86">
+        <f>BDP(A86,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K86">
         <f>BDP(A86,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K86">
+      <c r="L86">
         <f>BDP(A86,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L86">
+      <c r="M86">
         <f>BDP(A86,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M86">
+      <c r="N86">
         <f>BDP(A86,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N86">
+      <c r="O86">
         <f>BDP(A86,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P86">
+      <c r="Q86">
         <f>BDP(A86,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q86">
+      <c r="R86">
         <f>BDP(A86,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R86">
+      <c r="S86">
         <f>BDP(A86,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -7633,34 +7979,38 @@
         <v/>
       </c>
       <c r="J87">
+        <f>BDP(A87,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K87">
         <f>BDP(A87,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K87">
+      <c r="L87">
         <f>BDP(A87,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L87">
+      <c r="M87">
         <f>BDP(A87,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M87">
+      <c r="N87">
         <f>BDP(A87,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N87">
+      <c r="O87">
         <f>BDP(A87,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P87">
+      <c r="Q87">
         <f>BDP(A87,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q87">
+      <c r="R87">
         <f>BDP(A87,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R87">
+      <c r="S87">
         <f>BDP(A87,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -7699,34 +8049,38 @@
         <v/>
       </c>
       <c r="J88">
+        <f>BDP(A88,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K88">
         <f>BDP(A88,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K88">
+      <c r="L88">
         <f>BDP(A88,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L88">
+      <c r="M88">
         <f>BDP(A88,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M88">
+      <c r="N88">
         <f>BDP(A88,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N88">
+      <c r="O88">
         <f>BDP(A88,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P88">
+      <c r="Q88">
         <f>BDP(A88,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q88">
+      <c r="R88">
         <f>BDP(A88,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R88">
+      <c r="S88">
         <f>BDP(A88,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -7765,34 +8119,38 @@
         <v/>
       </c>
       <c r="J89">
+        <f>BDP(A89,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K89">
         <f>BDP(A89,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K89">
+      <c r="L89">
         <f>BDP(A89,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L89">
+      <c r="M89">
         <f>BDP(A89,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M89">
+      <c r="N89">
         <f>BDP(A89,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N89">
+      <c r="O89">
         <f>BDP(A89,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P89">
+      <c r="Q89">
         <f>BDP(A89,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q89">
+      <c r="R89">
         <f>BDP(A89,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R89">
+      <c r="S89">
         <f>BDP(A89,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -7831,34 +8189,38 @@
         <v/>
       </c>
       <c r="J90">
+        <f>BDP(A90,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K90">
         <f>BDP(A90,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K90">
+      <c r="L90">
         <f>BDP(A90,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L90">
+      <c r="M90">
         <f>BDP(A90,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M90">
+      <c r="N90">
         <f>BDP(A90,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N90">
+      <c r="O90">
         <f>BDP(A90,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P90">
+      <c r="Q90">
         <f>BDP(A90,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q90">
+      <c r="R90">
         <f>BDP(A90,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R90">
+      <c r="S90">
         <f>BDP(A90,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -7897,34 +8259,38 @@
         <v/>
       </c>
       <c r="J91">
+        <f>BDP(A91,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K91">
         <f>BDP(A91,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K91">
+      <c r="L91">
         <f>BDP(A91,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L91">
+      <c r="M91">
         <f>BDP(A91,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M91">
+      <c r="N91">
         <f>BDP(A91,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N91">
+      <c r="O91">
         <f>BDP(A91,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P91">
+      <c r="Q91">
         <f>BDP(A91,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q91">
+      <c r="R91">
         <f>BDP(A91,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R91">
+      <c r="S91">
         <f>BDP(A91,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -7963,34 +8329,38 @@
         <v/>
       </c>
       <c r="J92">
+        <f>BDP(A92,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K92">
         <f>BDP(A92,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K92">
+      <c r="L92">
         <f>BDP(A92,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L92">
+      <c r="M92">
         <f>BDP(A92,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M92">
+      <c r="N92">
         <f>BDP(A92,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N92">
+      <c r="O92">
         <f>BDP(A92,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P92">
+      <c r="Q92">
         <f>BDP(A92,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q92">
+      <c r="R92">
         <f>BDP(A92,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R92">
+      <c r="S92">
         <f>BDP(A92,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -8029,34 +8399,38 @@
         <v/>
       </c>
       <c r="J93">
+        <f>BDP(A93,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K93">
         <f>BDP(A93,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K93">
+      <c r="L93">
         <f>BDP(A93,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L93">
+      <c r="M93">
         <f>BDP(A93,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M93">
+      <c r="N93">
         <f>BDP(A93,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N93">
+      <c r="O93">
         <f>BDP(A93,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P93">
+      <c r="Q93">
         <f>BDP(A93,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q93">
+      <c r="R93">
         <f>BDP(A93,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R93">
+      <c r="S93">
         <f>BDP(A93,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -8095,34 +8469,38 @@
         <v/>
       </c>
       <c r="J94">
+        <f>BDP(A94,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K94">
         <f>BDP(A94,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K94">
+      <c r="L94">
         <f>BDP(A94,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L94">
+      <c r="M94">
         <f>BDP(A94,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M94">
+      <c r="N94">
         <f>BDP(A94,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N94">
+      <c r="O94">
         <f>BDP(A94,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P94">
+      <c r="Q94">
         <f>BDP(A94,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q94">
+      <c r="R94">
         <f>BDP(A94,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R94">
+      <c r="S94">
         <f>BDP(A94,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -8161,34 +8539,38 @@
         <v/>
       </c>
       <c r="J95">
+        <f>BDP(A95,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K95">
         <f>BDP(A95,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K95">
+      <c r="L95">
         <f>BDP(A95,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L95">
+      <c r="M95">
         <f>BDP(A95,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M95">
+      <c r="N95">
         <f>BDP(A95,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N95">
+      <c r="O95">
         <f>BDP(A95,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P95">
+      <c r="Q95">
         <f>BDP(A95,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q95">
+      <c r="R95">
         <f>BDP(A95,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R95">
+      <c r="S95">
         <f>BDP(A95,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -8227,34 +8609,38 @@
         <v/>
       </c>
       <c r="J96">
+        <f>BDP(A96,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K96">
         <f>BDP(A96,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K96">
+      <c r="L96">
         <f>BDP(A96,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L96">
+      <c r="M96">
         <f>BDP(A96,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M96">
+      <c r="N96">
         <f>BDP(A96,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N96">
+      <c r="O96">
         <f>BDP(A96,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P96">
+      <c r="Q96">
         <f>BDP(A96,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q96">
+      <c r="R96">
         <f>BDP(A96,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R96">
+      <c r="S96">
         <f>BDP(A96,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -8293,34 +8679,38 @@
         <v/>
       </c>
       <c r="J97">
+        <f>BDP(A97,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K97">
         <f>BDP(A97,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K97">
+      <c r="L97">
         <f>BDP(A97,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L97">
+      <c r="M97">
         <f>BDP(A97,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M97">
+      <c r="N97">
         <f>BDP(A97,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N97">
+      <c r="O97">
         <f>BDP(A97,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P97">
+      <c r="Q97">
         <f>BDP(A97,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q97">
+      <c r="R97">
         <f>BDP(A97,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R97">
+      <c r="S97">
         <f>BDP(A97,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -8359,34 +8749,38 @@
         <v/>
       </c>
       <c r="J98">
+        <f>BDP(A98,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K98">
         <f>BDP(A98,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K98">
+      <c r="L98">
         <f>BDP(A98,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L98">
+      <c r="M98">
         <f>BDP(A98,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M98">
+      <c r="N98">
         <f>BDP(A98,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N98">
+      <c r="O98">
         <f>BDP(A98,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P98">
+      <c r="Q98">
         <f>BDP(A98,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q98">
+      <c r="R98">
         <f>BDP(A98,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R98">
+      <c r="S98">
         <f>BDP(A98,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -8425,34 +8819,38 @@
         <v/>
       </c>
       <c r="J99">
+        <f>BDP(A99,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K99">
         <f>BDP(A99,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K99">
+      <c r="L99">
         <f>BDP(A99,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L99">
+      <c r="M99">
         <f>BDP(A99,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M99">
+      <c r="N99">
         <f>BDP(A99,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N99">
+      <c r="O99">
         <f>BDP(A99,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P99">
+      <c r="Q99">
         <f>BDP(A99,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q99">
+      <c r="R99">
         <f>BDP(A99,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R99">
+      <c r="S99">
         <f>BDP(A99,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -8491,34 +8889,38 @@
         <v/>
       </c>
       <c r="J100">
+        <f>BDP(A100,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K100">
         <f>BDP(A100,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K100">
+      <c r="L100">
         <f>BDP(A100,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L100">
+      <c r="M100">
         <f>BDP(A100,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M100">
+      <c r="N100">
         <f>BDP(A100,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N100">
+      <c r="O100">
         <f>BDP(A100,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P100">
+      <c r="Q100">
         <f>BDP(A100,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q100">
+      <c r="R100">
         <f>BDP(A100,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R100">
+      <c r="S100">
         <f>BDP(A100,"RTG_FITCH")</f>
         <v/>
       </c>
@@ -8557,34 +8959,38 @@
         <v/>
       </c>
       <c r="J101">
+        <f>BDP(A101,"ID_ISIN")</f>
+        <v/>
+      </c>
+      <c r="K101">
         <f>BDP(A101,"MARKET_SECTOR_DES")</f>
         <v/>
       </c>
-      <c r="K101">
+      <c r="L101">
         <f>BDP(A101,"ISSUER")</f>
         <v/>
       </c>
-      <c r="L101">
+      <c r="M101">
         <f>BDP(A101,"CNTRY_OF_RISK")</f>
         <v/>
       </c>
-      <c r="M101">
+      <c r="N101">
         <f>BDP(A101,"INDUSTRY_SECTOR")</f>
         <v/>
       </c>
-      <c r="N101">
+      <c r="O101">
         <f>BDP(A101,"PAYMENT_RANK")</f>
         <v/>
       </c>
-      <c r="P101">
+      <c r="Q101">
         <f>BDP(A101,"RTG_SP")</f>
         <v/>
       </c>
-      <c r="Q101">
+      <c r="R101">
         <f>BDP(A101,"RTG_MOODY")</f>
         <v/>
       </c>
-      <c r="R101">
+      <c r="S101">
         <f>BDP(A101,"RTG_FITCH")</f>
         <v/>
       </c>
